--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.879500</v>
+        <v>7724.853539</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915793290.73</v>
+        <v>1915786852.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.153682</v>
+        <v>29.184550</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5067539442.75</v>
+        <v>5072905054.60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.632109</v>
+        <v>0.609371</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>316054.63</v>
+        <v>304685.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11305.019628</v>
+        <v>11298.359416</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3335139060.68</v>
+        <v>3333174204.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5353.990804</v>
+        <v>5354.266895</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52201410.34</v>
+        <v>52204102.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24431.361918</v>
+        <v>24456.537248</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2020473630.62</v>
+        <v>2022555630.40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.560541</v>
+        <v>9968.130832</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72929988.92</v>
+        <v>72926845.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,21 +460,21 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.199456</v>
+        <v>2.198903</v>
       </c>
       <c r="E10" s="66">
-        <v>573629966.00</v>
+        <v>575359508.00</v>
       </c>
       <c r="F10" s="65">
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1261674136.53</v>
+        <v>1265159686.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1140.697126</v>
+        <v>1141.046258</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893395129.99</v>
+        <v>893668570.21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>361.090977</v>
+        <v>362.809497</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>373368.07</v>
+        <v>375145.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.357010</v>
+        <v>23.356045</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333467587.43</v>
+        <v>2333371177.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.497004</v>
+        <v>24.493670</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701097318.20</v>
+        <v>2700729756.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340043</v>
+        <v>8.340034</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506793.49</v>
+        <v>94506684.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.462684</v>
+        <v>7.463030</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>548689121.24</v>
+        <v>548714566.40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.818621</v>
+        <v>10.814837</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164719022.85</v>
+        <v>164661415.40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,21 +676,21 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>970.056582</v>
+        <v>968.431430</v>
       </c>
       <c r="E18" s="66">
-        <v>42534.00</v>
+        <v>43048.00</v>
       </c>
       <c r="F18" s="65">
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41260386.66</v>
+        <v>41689036.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1216.158278</v>
+        <v>1219.066184</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11554719.80</v>
+        <v>11582347.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.617621</v>
+        <v>13.624116</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1565927500.88</v>
+        <v>1566674414.70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999890</v>
+        <v>0.999504</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99989.04</v>
+        <v>99950.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1012.645663</v>
+        <v>1014.533277</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20252913.26</v>
+        <v>20290665.54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.624693</v>
+        <v>724.577387</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3005211350.48</v>
+        <v>3005015160.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,21 +865,21 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.606119</v>
+        <v>1124.576883</v>
       </c>
       <c r="E25" s="66">
-        <v>2433685.00</v>
+        <v>2422126.00</v>
       </c>
       <c r="F25" s="65">
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2736937042.65</v>
+        <v>2723866908.50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999890</v>
+        <v>0.999504</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99989.04</v>
+        <v>99950.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.631997</v>
+        <v>1.646948</v>
       </c>
       <c r="E27" s="66">
-        <v>280939198.00</v>
+        <v>292286905.00</v>
       </c>
       <c r="F27" s="65">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G27" s="66">
-        <v>458491977.48</v>
+        <v>481381384.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>935.167449</v>
+        <v>906.642372</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4674902.08</v>
+        <v>4532305.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1113.774228</v>
+        <v>1179.967010</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>55688711.42</v>
+        <v>58998350.50</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809114</v>
+        <v>1.809168</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361822856.22</v>
+        <v>361833577.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1358.135760</v>
+        <v>1361.056603</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5432543.04</v>
+        <v>5444226.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7323.761125</v>
+        <v>7322.029756</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533792329.60</v>
+        <v>533666138.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6962.716762</v>
+        <v>6961.870050</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>172905145.34</v>
+        <v>172884118.94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20484.988870</v>
+        <v>20485.614173</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>333249798.94</v>
+        <v>333259971.37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1173.735176</v>
+        <v>1175.357436</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5868675.88</v>
+        <v>5876787.18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1173.735176</v>
+        <v>1175.357436</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5868675.88</v>
+        <v>5876787.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1030.944215</v>
+        <v>1033.387485</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>25876699.80</v>
+        <v>25938025.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.699409</v>
+        <v>1.694824</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>77</v>
       </c>
       <c r="G38" s="66">
-        <v>232259598.42</v>
+        <v>231633003.80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1215.155398</v>
+        <v>1221.016346</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>323917898.62</v>
+        <v>325480222.25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3687.528181</v>
+        <v>3687.112364</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>752255748.91</v>
+        <v>752170922.17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3394.161714</v>
+        <v>3642.054226</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>238147962.49</v>
+        <v>255541092.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6673.379351</v>
+        <v>6827.429705</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>186958332.81</v>
+        <v>191274136.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.109287</v>
+        <v>0.110108</v>
       </c>
       <c r="E43" s="66">
-        <v>43822151.00</v>
+        <v>315837238.00</v>
       </c>
       <c r="F43" s="65">
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>4789177.94</v>
+        <v>34776218.15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.946547</v>
+        <v>1.946602</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242580936.60</v>
+        <v>242587724.60</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.587222</v>
+        <v>5.579060</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59251815.05</v>
+        <v>59165260.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465219</v>
+        <v>0.465172</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652059713.37</v>
+        <v>1651893583.16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008815</v>
+        <v>0.008861</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>599673248.59</v>
+        <v>602792419.72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.144704</v>
+        <v>0.135345</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>208198.89</v>
+        <v>194732.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.476039</v>
+        <v>0.449781</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>651212.93</v>
+        <v>615293.35</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1760.153763</v>
+        <v>1769.299851</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>505077882.56</v>
+        <v>507702361.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16740.705265</v>
+        <v>16723.043832</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>366571223.18</v>
+        <v>366184490.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.274840</v>
+        <v>1.277191</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12764974.92</v>
+        <v>12788518.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7531.584014</v>
+        <v>7527.997719</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44579445.78</v>
+        <v>44558218.50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.313898</v>
+        <v>7.322687</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>241535499.35</v>
+        <v>241825776.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.172600</v>
+        <v>0.111325</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>195077.08</v>
+        <v>125822.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.325248</v>
+        <v>6.342926</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>108998354.49</v>
+        <v>109302981.48</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990268</v>
+        <v>0.990155</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59416071.09</v>
+        <v>59409311.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591441</v>
+        <v>1.591277</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137673197.77</v>
+        <v>137659030.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.624555</v>
+        <v>8.622554</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344982187.16</v>
+        <v>344902144.90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.715259</v>
+        <v>0.706591</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>715259.11</v>
+        <v>706590.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.893743</v>
+        <v>0.884579</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>772136.88</v>
+        <v>764219.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.246452</v>
+        <v>2.245634</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170772671.20</v>
+        <v>170710527.19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.710392</v>
+        <v>5.711433</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1622638479.51</v>
+        <v>1622934050.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.356759</v>
+        <v>1.360480</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2676380058.56</v>
+        <v>2683720930.09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296477</v>
+        <v>1.296374</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744934880.37</v>
+        <v>1744795895.46</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>1.002791</v>
+        <v>1.005901</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>157939553.01</v>
+        <v>158429359.74</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>5.975666</v>
+        <v>5.970833</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6559443968.73</v>
+        <v>6554138686.90</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1517.630019</v>
+        <v>1518.174190</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1372370061.71</v>
+        <v>1372862147.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.170460</v>
+        <v>6.172027</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2612354523.80</v>
+        <v>2613017587.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.075760</v>
+        <v>4.079396</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2582238628.89</v>
+        <v>2584541965.56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.735630</v>
+        <v>6.751705</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>317112197.98</v>
+        <v>317868983.59</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792308</v>
+        <v>1.792181</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444754266.78</v>
+        <v>444722772.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.466779</v>
+        <v>18.456934</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20273660.56</v>
+        <v>20262852.21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.143772</v>
+        <v>3.147783</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>551029816.77</v>
+        <v>551732859.77</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.581773</v>
+        <v>14.585364</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>91</v>
       </c>
       <c r="G75" s="66">
-        <v>6448870938.45</v>
+        <v>6450458755.43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.592452</v>
+        <v>6.592345</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2910451138.51</v>
+        <v>2910403668.49</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1359.346249</v>
+        <v>1361.823890</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>392324998.95</v>
+        <v>393040078.36</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.233156</v>
+        <v>5.232674</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355970791.75</v>
+        <v>355937989.92</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>548.521800</v>
+        <v>546.828700</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>54852.18</v>
+        <v>54682.87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7119.674000</v>
+        <v>7102.167000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>71196.74</v>
+        <v>71021.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>291.120200</v>
+        <v>289.520600</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>29112.02</v>
+        <v>28952.06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.295817</v>
+        <v>46.386391</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1624473.91</v>
+        <v>1627652.06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1203.327957</v>
+        <v>1208.493167</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>111909500.01</v>
+        <v>112389864.55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.028575</v>
+        <v>21.024133</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671873726.18</v>
+        <v>1671520560.88</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.451668</v>
+        <v>31.441277</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>979353344.15</v>
+        <v>979029779.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.274909</v>
+        <v>46.365602</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1623740.27</v>
+        <v>1626922.61</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.073902</v>
+        <v>1.077717</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>606754854.26</v>
+        <v>608909933.38</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.500428</v>
+        <v>20.565743</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>206209360.75</v>
+        <v>206866342.17</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.674477</v>
+        <v>19.695705</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3067447667.72</v>
+        <v>3070757332.54</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014566</v>
+        <v>0.014913</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8021.54</v>
+        <v>8212.16</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5671.442982</v>
+        <v>5674.113787</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5426436645.50</v>
+        <v>5428992071.68</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.319740</v>
+        <v>1.328432</v>
       </c>
       <c r="E92" s="66">
         <v>50000000.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>65986982.88</v>
+        <v>66421615.13</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.779341</v>
+        <v>0.778910</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>136000523.48</v>
+        <v>135925219.93</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.600056</v>
+        <v>30.596839</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1549917822.07</v>
+        <v>1549754901.51</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094785</v>
+        <v>1.094769</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55495774.30</v>
+        <v>55494962.19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208974</v>
+        <v>1.208805</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298616463.84</v>
+        <v>298574914.84</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599788</v>
+        <v>0.599464</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70378042.69</v>
+        <v>70340028.16</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.540463</v>
+        <v>52.523881</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39022747.81</v>
+        <v>39010431.98</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.950413</v>
+        <v>19.948255</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109620416.80</v>
+        <v>109608560.10</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1010.954170</v>
+        <v>1010.828249</v>
       </c>
       <c r="E100" s="66">
         <v>22861.00</v>
@@ -2899,12 +2899,12 @@
         <v>2</v>
       </c>
       <c r="G100" s="66">
-        <v>23111423.28</v>
+        <v>23108544.60</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,21 +2917,21 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.579489</v>
+        <v>0.579472</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
       </c>
       <c r="F101" s="65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1216926.64</v>
+        <v>1216891.84</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c t="n" r="D102">
-        <v>0.002692</v>
+        <v>0.002669</v>
       </c>
       <c r="E102" s="66">
         <v>689971183082.00</v>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1857188187.12</v>
+        <v>1841237766.00</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.906141</v>
+        <v>4.920411</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>65760071.58</v>
+        <v>65951350.09</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.946449</v>
+        <v>13.945106</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174658895.77</v>
+        <v>174642080.52</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.369650</v>
+        <v>9.367833</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78560956.68</v>
+        <v>78545719.58</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.408576</v>
+        <v>14.407611</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933658091.41</v>
+        <v>933595577.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.810807</v>
+        <v>8.809613</v>
       </c>
       <c r="E107" s="66">
         <v>78003587.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>687274564.06</v>
+        <v>687181410.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.924206</v>
+        <v>8.930847</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2905512301.05</v>
+        <v>2907674490.59</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.777080</v>
+        <v>29.797583</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661147081.24</v>
+        <v>661602321.19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.753363</v>
+        <v>2.763934</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>291649639.88</v>
+        <v>292769370.51</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.261538</v>
+        <v>48.281596</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1835087851.15</v>
+        <v>1835850524.09</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.616820</v>
+        <v>11.615511</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147497206.30</v>
+        <v>147480586.71</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.895985</v>
+        <v>4.895926</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>875555536.61</v>
+        <v>875545128.68</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.225598</v>
+        <v>39.277539</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40510393.22</v>
+        <v>40564035.70</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>158.056429</v>
+        <v>145.106193</v>
       </c>
       <c r="E115" s="66">
-        <v>3943.00</v>
+        <v>3843.00</v>
       </c>
       <c r="F115" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>623216.50</v>
+        <v>557643.10</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.162289</v>
+        <v>34.136938</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102486866.26</v>
+        <v>102410813.39</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002282</v>
+        <v>0.002289</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>258239152.43</v>
+        <v>259026011.86</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956411</v>
+        <v>31.954170</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355115103.98</v>
+        <v>355090203.39</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>399.735654</v>
+        <v>399.997382</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>299590680.13</v>
+        <v>299786837.66</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.318064</v>
+        <v>2.383114</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>478149565.98</v>
+        <v>491567672.81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.913831</v>
+        <v>0.912571</v>
       </c>
       <c r="E121" s="66">
         <v>229647810.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>209859258.97</v>
+        <v>209569984.75</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.503064</v>
+        <v>1.502651</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55169877.73</v>
+        <v>55154719.76</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.010045</v>
+        <v>27.010604</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391198967.37</v>
+        <v>391207062.62</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.028024</v>
+        <v>2.027765</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59055916.27</v>
+        <v>59048381.48</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.648880</v>
+        <v>21.666741</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119288491.73</v>
+        <v>119386908.31</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.665024</v>
+        <v>7.663309</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178603599.99</v>
+        <v>178563631.90</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.025420</v>
+        <v>5.024424</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214532555.25</v>
+        <v>214490005.04</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723805</v>
+        <v>2.723505</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368753337.97</v>
+        <v>368712791.93</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.840833</v>
+        <v>23.841180</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451192170.45</v>
+        <v>451198733.96</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.414502</v>
+        <v>5.412095</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44249947.43</v>
+        <v>44230278.66</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348380</v>
+        <v>1.348231</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1021132352.36</v>
+        <v>1021019984.86</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.950183</v>
+        <v>0.949878</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87063702.63</v>
+        <v>87035756.86</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.216733</v>
+        <v>12.219016</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172020759.10</v>
+        <v>172052910.28</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.293313</v>
+        <v>2.214224</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>163290520.77</v>
+        <v>157659191.53</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.383492</v>
+        <v>13.398854</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101138098.34</v>
+        <v>101254185.46</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.201492</v>
+        <v>94.156282</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24321883.25</v>
+        <v>24310210.47</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.656010</v>
+        <v>4.657168</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425051861.66</v>
+        <v>425157596.66</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.406153</v>
+        <v>18.407696</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>442115796.54</v>
+        <v>442152850.88</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27612.554195</v>
+        <v>27608.851934</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125195320.72</v>
+        <v>125178534.67</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4852.647584</v>
+        <v>4852.083518</v>
       </c>
       <c r="E141" s="66">
-        <v>709751.00</v>
+        <v>874610.00</v>
       </c>
       <c r="F141" s="65">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>3444171475.11</v>
+        <v>4243680765.59</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.231855</v>
+        <v>0.210852</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>231855.15</v>
+        <v>210851.74</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.382783</v>
+        <v>1.383825</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149563416.36</v>
+        <v>149676155.61</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.917464</v>
+        <v>15.918327</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156372820.34</v>
+        <v>1156435509.65</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.097444</v>
+        <v>16.094563</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5746971982.74</v>
+        <v>5745943573.54</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3291.545190</v>
+        <v>3291.481573</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193585647.26</v>
+        <v>193581905.78</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c t="n" r="D147">
-        <v>0.978053</v>
+        <v>0.977860</v>
       </c>
       <c r="E147" s="66">
         <v>431000000.00</v>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421540742.79</v>
+        <v>421457630.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.303726</v>
+        <v>1.307799</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>522008181.65</v>
+        <v>523639092.09</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.037807</v>
+        <v>1.036645</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13529600876.50</v>
+        <v>13514445511.11</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.923936</v>
+        <v>0.922594</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13670427290.59</v>
+        <v>13650574276.18</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1930.400826</v>
+        <v>1930.684888</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41093886.33</v>
+        <v>41099933.36</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.583640</v>
+        <v>1.584339</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60921842.72</v>
+        <v>60948739.59</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6764.114057</v>
+        <v>6764.005801</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964224458.78</v>
+        <v>964209026.91</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.306358</v>
+        <v>1926.278766</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337752777.88</v>
+        <v>337747939.99</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17330.690481</v>
+        <v>17332.147058</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2503678200.29</v>
+        <v>2503888624.77</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20299.367051</v>
+        <v>20301.274871</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185008431.30</v>
+        <v>185025819.17</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15348.870563</v>
+        <v>15348.994527</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320330928.65</v>
+        <v>320333515.77</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1151.112882</v>
+        <v>1152.918656</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5860315.68</v>
+        <v>5869508.88</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3677.625577</v>
+        <v>3677.835881</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719531121.74</v>
+        <v>719572267.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200855.641193</v>
+        <v>200855.076193</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602205306.65</v>
+        <v>4602192360.80</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.347766</v>
+        <v>33.391801</v>
       </c>
       <c r="E162" s="66">
         <v>16759003.00</v>
@@ -4573,12 +4573,12 @@
         <v>25</v>
       </c>
       <c r="G162" s="66">
-        <v>558875314.81</v>
+        <v>559613287.23</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.955876</v>
+        <v>80.951402</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>398742255.16</v>
+        <v>398720223.08</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.399922</v>
+        <v>1.400126</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154315797.40</v>
+        <v>154338368.30</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.107220</v>
+        <v>2579.188419</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438450806.55</v>
+        <v>438464610.50</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.913215</v>
+        <v>1678.731279</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927193254.42</v>
+        <v>927092778.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027368</v>
+        <v>1.027177</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970855113.14</v>
+        <v>970674514.40</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1047.902040</v>
+        <v>1047.573240</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114553507.26</v>
+        <v>114517563.84</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.758317</v>
+        <v>75.777555</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65808143.50</v>
+        <v>65824855.10</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188222</v>
+        <v>3.188104</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977132979.68</v>
+        <v>977096701.48</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2979.059223</v>
+        <v>2979.185330</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2193704735.57</v>
+        <v>2193797597.05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4235.514606</v>
+        <v>4280.378196</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>18805684.85</v>
+        <v>19004879.19</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63387.594208</v>
+        <v>63325.162362</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1176030035.35</v>
+        <v>1174871737.31</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8195.019724</v>
+        <v>8193.763114</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>149010043.65</v>
+        <v>148987194.71</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>45465.663936</v>
+        <v>45479.164462</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>2976318758.24</v>
+        <v>2977202543.19</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11593.430410</v>
+        <v>11591.691586</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2676111541.64</v>
+        <v>2675710168.90</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2485.595651</v>
+        <v>2485.838226</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92849425.54</v>
+        <v>92858486.94</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2707.805372</v>
+        <v>2705.989542</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>460023639.11</v>
+        <v>459715151.25</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3498.325040</v>
+        <v>3495.837583</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20769555.76</v>
+        <v>20754787.73</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3287.714820</v>
+        <v>3287.205308</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6836204604.95</v>
+        <v>6835145165.91</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994986</v>
+        <v>0.994842</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928715018.66</v>
+        <v>928579903.93</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4662.178533</v>
+        <v>4661.251895</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70277679.20</v>
+        <v>70263711.07</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,21 +5131,21 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.176633</v>
+        <v>1.176336</v>
       </c>
       <c r="E183" s="66">
-        <v>2020455.00</v>
+        <v>2023351.00</v>
       </c>
       <c r="F183" s="65">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G183" s="66">
-        <v>2377333.78</v>
+        <v>2380139.95</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3593.127295</v>
+        <v>3592.725170</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917350550.24</v>
+        <v>917247884.89</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211783</v>
+        <v>1.211637</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226685152.25</v>
+        <v>226657919.08</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1330.893380</v>
+        <v>1330.962448</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502424228.91</v>
+        <v>502450302.80</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1110.597104</v>
+        <v>1110.547441</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1723100291.27</v>
+        <v>1723023239.81</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.955073</v>
+        <v>74.939709</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>873076544.33</v>
+        <v>872897584.61</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.161524</v>
+        <v>10.243574</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>450263604.34</v>
+        <v>453899275.86</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.203973</v>
+        <v>13.761796</v>
       </c>
       <c r="E190" s="66">
         <v>159085884.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2259651534.02</v>
+        <v>2189307545.35</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7461.487565</v>
+        <v>7572.996887</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
       </c>
       <c r="F191" s="65">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>279492401.21</v>
+        <v>283669317.40</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>2.250547</v>
+        <v>2.198676</v>
       </c>
       <c r="E192" s="66">
         <v>5273240.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>11867674.97</v>
+        <v>11594144.96</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.442858</v>
+        <v>2.441687</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206204183.00</v>
+        <v>206105349.42</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.418287</v>
+        <v>44.427630</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>565619805.40</v>
+        <v>565738776.58</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14891.596171</v>
+        <v>14891.353588</v>
       </c>
       <c r="E195" s="66">
-        <v>408257.00</v>
+        <v>416820.00</v>
       </c>
       <c r="F195" s="65">
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6079598377.80</v>
+        <v>6207014002.36</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6272.216964</v>
+        <v>6271.747448</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39765855.55</v>
+        <v>39762878.82</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c t="n" r="D197">
-        <v>14783.542590</v>
+        <v>14783.142199</v>
       </c>
       <c r="E197" s="66">
         <v>12800.00</v>
@@ -5518,12 +5518,12 @@
         <v>3</v>
       </c>
       <c r="G197" s="66">
-        <v>189229345.15</v>
+        <v>189224220.15</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.279269</v>
+        <v>2933.243091</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077519606.33</v>
+        <v>1077506316.64</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c t="n" r="D199">
-        <v>1.224069</v>
+        <v>1.223996</v>
       </c>
       <c r="E199" s="66">
         <v>427328964.00</v>
@@ -5572,12 +5572,12 @@
         <v>3</v>
       </c>
       <c r="G199" s="66">
-        <v>523080341.43</v>
+        <v>523049061.19</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.323243</v>
+        <v>1.323189</v>
       </c>
       <c r="E200" s="66">
         <v>92000000.00</v>
@@ -5599,12 +5599,12 @@
         <v>1</v>
       </c>
       <c r="G200" s="66">
-        <v>121738380.93</v>
+        <v>121733407.85</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>7.298552</v>
+        <v>7.351407</v>
       </c>
       <c r="E201" s="66">
         <v>381640102.00</v>
@@ -5626,12 +5626,12 @@
         <v>2</v>
       </c>
       <c r="G201" s="66">
-        <v>2785420140.55</v>
+        <v>2805591877.71</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>998.254204</v>
+        <v>998.147371</v>
       </c>
       <c r="E202" s="66">
         <v>448820.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>448036451.91</v>
+        <v>447988502.88</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>2482.734624</v>
+        <v>2494.953241</v>
       </c>
       <c r="E203" s="66">
         <v>205132.00</v>
@@ -5680,12 +5680,12 @@
         <v>4</v>
       </c>
       <c r="G203" s="66">
-        <v>509288318.98</v>
+        <v>511794748.33</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>0.004329</v>
+        <v>0.004375</v>
       </c>
       <c r="E204" s="66">
         <v>67618383967.00</v>
@@ -5707,12 +5707,12 @@
         <v>1</v>
       </c>
       <c r="G204" s="66">
-        <v>292714715.76</v>
+        <v>295805667.53</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>20.900608</v>
+        <v>20.815424</v>
       </c>
       <c r="E205" s="66">
         <v>81092133.00</v>
@@ -5734,12 +5734,12 @@
         <v>1</v>
       </c>
       <c r="G205" s="66">
-        <v>1694874895.84</v>
+        <v>1687967153.33</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>3.364808</v>
+        <v>3.365203</v>
       </c>
       <c r="E206" s="66">
         <v>21323550.00</v>
@@ -5761,12 +5761,12 @@
         <v>2</v>
       </c>
       <c r="G206" s="66">
-        <v>71749641.29</v>
+        <v>71758074.59</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,21 +5779,21 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>7683.472991</v>
+        <v>7687.516053</v>
       </c>
       <c r="E207" s="66">
         <v>197052.47</v>
       </c>
       <c r="F207" s="65">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G207" s="66">
-        <v>1514047361.83</v>
+        <v>1514844057.22</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>1.845022</v>
+        <v>1.844713</v>
       </c>
       <c r="E208" s="66">
         <v>601179729.00</v>
@@ -5815,12 +5815,12 @@
         <v>16</v>
       </c>
       <c r="G208" s="66">
-        <v>1109189914.92</v>
+        <v>1109004288.24</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>58.730027</v>
+        <v>26.493103</v>
       </c>
       <c r="E209" s="66">
         <v>377.00</v>
@@ -5842,12 +5842,12 @@
         <v>1</v>
       </c>
       <c r="G209" s="66">
-        <v>22141.22</v>
+        <v>9987.90</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.728335</v>
+        <v>1.735238</v>
       </c>
       <c r="E210" s="66">
         <v>100000.00</v>
@@ -5869,12 +5869,12 @@
         <v>1</v>
       </c>
       <c r="G210" s="66">
-        <v>172833.47</v>
+        <v>173523.79</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>1.728493</v>
+        <v>1.735396</v>
       </c>
       <c r="E211" s="66">
         <v>100000.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>172849.30</v>
+        <v>173539.62</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,21 +5914,21 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>62.130972</v>
+        <v>61.335495</v>
       </c>
       <c r="E212" s="66">
-        <v>2325785.00</v>
+        <v>2554914.00</v>
       </c>
       <c r="F212" s="65">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G212" s="66">
-        <v>144503282.59</v>
+        <v>156706914.84</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>15.343140</v>
+        <v>15.286899</v>
       </c>
       <c r="E213" s="66">
         <v>248000220.00</v>
@@ -5950,12 +5950,12 @@
         <v>2</v>
       </c>
       <c r="G213" s="66">
-        <v>3805102216.97</v>
+        <v>3791154382.68</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>1.758815</v>
+        <v>1.756418</v>
       </c>
       <c r="E214" s="66">
         <v>437816172.00</v>
@@ -5977,12 +5977,12 @@
         <v>7</v>
       </c>
       <c r="G214" s="66">
-        <v>770037820.43</v>
+        <v>768988116.84</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>0.390701</v>
+        <v>0.390804</v>
       </c>
       <c r="E215" s="66">
         <v>402507.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>157259.71</v>
+        <v>157301.52</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>9.883969</v>
+        <v>9.880946</v>
       </c>
       <c r="E216" s="66">
         <v>27178800.00</v>
@@ -6031,12 +6031,12 @@
         <v>1</v>
       </c>
       <c r="G216" s="66">
-        <v>268634426.60</v>
+        <v>268552245.91</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>15.652568</v>
+        <v>15.620625</v>
       </c>
       <c r="E217" s="66">
         <v>10371838.00</v>
@@ -6058,12 +6058,12 @@
         <v>34</v>
       </c>
       <c r="G217" s="66">
-        <v>162345902.34</v>
+        <v>162014588.79</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>15.336597</v>
+        <v>15.329164</v>
       </c>
       <c r="E218" s="66">
         <v>19475841.00</v>
@@ -6085,12 +6085,12 @@
         <v>26</v>
       </c>
       <c r="G218" s="66">
-        <v>298693119.21</v>
+        <v>298548360.88</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>31.109818</v>
+        <v>31.096886</v>
       </c>
       <c r="E219" s="66">
         <v>9712281.00</v>
@@ -6112,12 +6112,12 @@
         <v>13</v>
       </c>
       <c r="G219" s="66">
-        <v>302147291.37</v>
+        <v>302021690.82</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>7.984796</v>
+        <v>7.981511</v>
       </c>
       <c r="E220" s="66">
         <v>12818249.00</v>
@@ -6139,12 +6139,12 @@
         <v>23</v>
       </c>
       <c r="G220" s="66">
-        <v>102351103.43</v>
+        <v>102308994.42</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>1659.823134</v>
+        <v>1659.792804</v>
       </c>
       <c r="E221" s="66">
         <v>330000.00</v>
@@ -6166,12 +6166,12 @@
         <v>2</v>
       </c>
       <c r="G221" s="66">
-        <v>547741634.30</v>
+        <v>547731625.30</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>5.173355</v>
+        <v>5.170240</v>
       </c>
       <c r="E222" s="66">
         <v>11867933.00</v>
@@ -6193,12 +6193,12 @@
         <v>3</v>
       </c>
       <c r="G222" s="66">
-        <v>61397029.99</v>
+        <v>61360060.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>0.946397</v>
+        <v>0.946461</v>
       </c>
       <c r="E223" s="66">
         <v>130000000.00</v>
@@ -6220,12 +6220,12 @@
         <v>3</v>
       </c>
       <c r="G223" s="66">
-        <v>123031563.46</v>
+        <v>123039892.84</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.506503</v>
+        <v>5.531262</v>
       </c>
       <c r="E224" s="66">
         <v>103852814.00</v>
@@ -6247,12 +6247,12 @@
         <v>29</v>
       </c>
       <c r="G224" s="66">
-        <v>571865829.17</v>
+        <v>574437072.92</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6274,12 +6274,12 @@
         <v>2</v>
       </c>
       <c r="G225" s="66">
-        <v>6077.83</v>
+        <v>6077.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>6.609939</v>
+        <v>6.607497</v>
       </c>
       <c r="E226" s="66">
         <v>11104667.00</v>
@@ -6301,12 +6301,12 @@
         <v>2</v>
       </c>
       <c r="G226" s="66">
-        <v>73401170.71</v>
+        <v>73374054.73</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c t="n" r="D227">
-        <v>26.546010</v>
+        <v>26.532834</v>
       </c>
       <c r="E227" s="66">
         <v>1038884.00</v>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>27578225.21</v>
+        <v>27564536.67</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>0.851321</v>
+        <v>0.850873</v>
       </c>
       <c r="E228" s="66">
         <v>73432275.00</v>
@@ -6355,12 +6355,12 @@
         <v>4</v>
       </c>
       <c r="G228" s="66">
-        <v>62514446.11</v>
+        <v>62481540.32</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>0.712087</v>
+        <v>0.711793</v>
       </c>
       <c r="E229" s="66">
         <v>801655137.00</v>
@@ -6382,12 +6382,12 @@
         <v>28</v>
       </c>
       <c r="G229" s="66">
-        <v>570848570.90</v>
+        <v>570612496.78</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>11.954850</v>
+        <v>11.954564</v>
       </c>
       <c r="E230" s="66">
         <v>26235742.00</v>
@@ -6409,12 +6409,12 @@
         <v>5</v>
       </c>
       <c r="G230" s="66">
-        <v>313644353.98</v>
+        <v>313636851.71</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.004711</v>
+        <v>0.004710</v>
       </c>
       <c r="E231" s="66">
         <v>100000.00</v>
@@ -6436,12 +6436,12 @@
         <v>1</v>
       </c>
       <c r="G231" s="66">
-        <v>471.07</v>
+        <v>471.04</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>1.538290</v>
+        <v>1.543718</v>
       </c>
       <c r="E232" s="66">
         <v>24022001.00</v>
@@ -6463,12 +6463,12 @@
         <v>2</v>
       </c>
       <c r="G232" s="66">
-        <v>36952809.60</v>
+        <v>37083199.61</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c t="n" r="D233">
-        <v>2.572480</v>
+        <v>2.571827</v>
       </c>
       <c r="E233" s="66">
         <v>68085562.00</v>
@@ -6490,12 +6490,12 @@
         <v>6</v>
       </c>
       <c r="G233" s="66">
-        <v>175148751.26</v>
+        <v>175104270.97</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,21 +6508,21 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1049.385555</v>
+        <v>1054.599490</v>
       </c>
       <c r="E234" s="66">
-        <v>10500.00</v>
+        <v>20029.00</v>
       </c>
       <c r="F234" s="65">
         <v>1</v>
       </c>
       <c r="G234" s="66">
-        <v>11018548.33</v>
+        <v>21122573.19</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>3.241831</v>
+        <v>3.243073</v>
       </c>
       <c r="E235" s="66">
         <v>1427155857.00</v>
@@ -6544,12 +6544,12 @@
         <v>2</v>
       </c>
       <c r="G235" s="66">
-        <v>4626598508.17</v>
+        <v>4628371012.66</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1656.049564</v>
+        <v>1687.447784</v>
       </c>
       <c r="E236" s="66">
         <v>97333.00</v>
@@ -6571,12 +6571,12 @@
         <v>2</v>
       </c>
       <c r="G236" s="66">
-        <v>161188272.26</v>
+        <v>164244355.19</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>1.161613</v>
+        <v>1.161333</v>
       </c>
       <c r="E237" s="66">
         <v>1103857956.00</v>
@@ -6598,12 +6598,12 @@
         <v>3</v>
       </c>
       <c r="G237" s="66">
-        <v>1282255863.57</v>
+        <v>1281946250.58</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>2.209651</v>
+        <v>2.265050</v>
       </c>
       <c r="E238" s="66">
         <v>296754544.00</v>
@@ -6625,88 +6625,115 @@
         <v>3</v>
       </c>
       <c r="G238" s="66">
-        <v>655723851.20</v>
+        <v>672164003.71</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">ZUC</t>
         </is>
       </c>
       <c t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D239">
-        <v>4.999698</v>
+        <v>999.816406</v>
       </c>
       <c r="E239" s="66">
-        <v>395532870.00</v>
+        <v>1431712.00</v>
       </c>
       <c r="F239" s="65">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="G239" s="66">
-        <v>1977544753.26</v>
+        <v>1431449145.60</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D240">
-        <v>1304.083753</v>
+        <v>5.001647</v>
       </c>
       <c r="E240" s="66">
-        <v>1467447.00</v>
+        <v>395532870.00</v>
       </c>
       <c r="F240" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G240" s="66">
-        <v>1913673790.75</v>
+        <v>1978315951.70</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46120</v>
+        <v>46125</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
+          <t xml:space="preserve">ZVD</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C241">
+        <is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D241">
+        <v>1303.876849</v>
+      </c>
+      <c r="E241" s="66">
+        <v>1467447.00</v>
+      </c>
+      <c r="F241" s="65">
+        <v>1</v>
+      </c>
+      <c r="G241" s="66">
+        <v>1913370170.80</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="67">
+        <v>46125</v>
+      </c>
+      <c t="inlineStr" r="B242">
+        <is>
           <t xml:space="preserve">ZVE</t>
         </is>
       </c>
-      <c t="inlineStr" r="C241">
+      <c t="inlineStr" r="C242">
         <is>
           <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="D241">
-        <v>26993.756903</v>
-      </c>
-      <c r="E241" s="66">
+      <c t="n" r="D242">
+        <v>26995.730390</v>
+      </c>
+      <c r="E242" s="66">
         <v>40026.00</v>
       </c>
-      <c r="F241" s="65">
-        <v>1</v>
-      </c>
-      <c r="G241" s="66">
-        <v>1080452113.81</v>
+      <c r="F242" s="65">
+        <v>1</v>
+      </c>
+      <c r="G242" s="66">
+        <v>1080531104.59</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.853539</v>
+        <v>7724.858706</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915786852.19</v>
+        <v>1915788133.73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.184550</v>
+        <v>29.209084</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5072905054.60</v>
+        <v>5077169618.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.609371</v>
+        <v>0.606727</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>304685.49</v>
+        <v>303363.34</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11298.359416</v>
+        <v>11302.007220</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3333174204.79</v>
+        <v>3334250357.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5354.266895</v>
+        <v>5355.081826</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52204102.23</v>
+        <v>52212047.80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24456.537248</v>
+        <v>24478.936678</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2022555630.40</v>
+        <v>2024408063.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.130832</v>
+        <v>9968.419347</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72926845.17</v>
+        <v>72928955.94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198903</v>
+        <v>2.198852</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1265159686.88</v>
+        <v>1265130221.31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.046258</v>
+        <v>1141.113557</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893668570.21</v>
+        <v>893721279.20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>362.809497</v>
+        <v>364.470010</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>375145.02</v>
+        <v>376861.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.356045</v>
+        <v>23.357193</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333371177.26</v>
+        <v>2333485940.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.493670</v>
+        <v>24.494933</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2700729756.52</v>
+        <v>2700868981.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340034</v>
+        <v>8.340039</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506684.95</v>
+        <v>94506743.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.463030</v>
+        <v>7.464816</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>548714566.40</v>
+        <v>548845904.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.814837</v>
+        <v>10.815195</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164661415.40</v>
+        <v>164666863.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>968.431430</v>
+        <v>968.166491</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41689036.21</v>
+        <v>41677631.10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1219.066184</v>
+        <v>1223.496571</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11582347.81</v>
+        <v>11624440.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.624116</v>
+        <v>13.647387</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1566674414.70</v>
+        <v>1569350408.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999504</v>
+        <v>0.999449</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99950.35</v>
+        <v>99944.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1014.533277</v>
+        <v>1012.796113</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20290665.54</v>
+        <v>20255922.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.577387</v>
+        <v>724.569782</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3005015160.29</v>
+        <v>3004983620.97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.576883</v>
+        <v>1124.456601</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723866908.50</v>
+        <v>2723575569.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999504</v>
+        <v>0.999449</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99950.35</v>
+        <v>99944.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.646948</v>
+        <v>1.649672</v>
       </c>
       <c r="E27" s="66">
         <v>292286905.00</v>
@@ -928,12 +928,12 @@
         <v>18</v>
       </c>
       <c r="G27" s="66">
-        <v>481381384.94</v>
+        <v>482177653.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>906.642372</v>
+        <v>904.367149</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4532305.22</v>
+        <v>4520931.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1179.967010</v>
+        <v>1165.347757</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>58998350.50</v>
+        <v>58267387.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809168</v>
+        <v>1.809404</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361833577.55</v>
+        <v>361880748.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1361.056603</v>
+        <v>1365.293130</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5444226.41</v>
+        <v>5461172.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7322.029756</v>
+        <v>7322.249033</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533666138.79</v>
+        <v>533682120.78</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6961.870050</v>
+        <v>6962.358506</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>172884118.94</v>
+        <v>172896248.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20485.614173</v>
+        <v>20486.719749</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>333259971.37</v>
+        <v>333277956.87</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1175.357436</v>
+        <v>1156.625280</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5876787.18</v>
+        <v>5783126.40</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1175.357436</v>
+        <v>1155.625280</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5876787.18</v>
+        <v>5778126.40</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1033.387485</v>
+        <v>1036.813813</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>25938025.87</v>
+        <v>26024026.70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694824</v>
+        <v>1.694918</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
       </c>
       <c r="F38" s="65">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231633003.80</v>
+        <v>231645829.73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1221.016346</v>
+        <v>1222.568134</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>325480222.25</v>
+        <v>325893874.75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3687.112364</v>
+        <v>3687.258108</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>752170922.17</v>
+        <v>752200654.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3642.054226</v>
+        <v>3603.114280</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>255541092.68</v>
+        <v>252808910.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6827.429705</v>
+        <v>6947.906945</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>191274136.83</v>
+        <v>194649371.89</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110108</v>
+        <v>0.110094</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34776218.15</v>
+        <v>34771886.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.946602</v>
+        <v>1.947006</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242587724.60</v>
+        <v>242638084.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.579060</v>
+        <v>5.579909</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59165260.98</v>
+        <v>59174261.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465172</v>
+        <v>0.465218</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1651893583.16</v>
+        <v>1652058801.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008861</v>
+        <v>0.008878</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>602792419.72</v>
+        <v>603982921.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.135345</v>
+        <v>0.128066</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>194732.74</v>
+        <v>184260.35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.449781</v>
+        <v>0.443289</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>615293.35</v>
+        <v>606411.92</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1769.299851</v>
+        <v>1771.121864</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>507702361.51</v>
+        <v>508225190.08</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16723.043832</v>
+        <v>16910.440262</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>366184490.78</v>
+        <v>370287910.42</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.277191</v>
+        <v>1.280951</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12788518.33</v>
+        <v>12826165.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7527.997719</v>
+        <v>7527.282603</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44558218.50</v>
+        <v>44553985.73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.322687</v>
+        <v>7.325092</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>241825776.45</v>
+        <v>241905181.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.111325</v>
+        <v>0.101992</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>125822.48</v>
+        <v>115274.31</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.342926</v>
+        <v>6.355416</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109302981.48</v>
+        <v>109518223.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990155</v>
+        <v>0.990331</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59409311.75</v>
+        <v>59419885.98</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591277</v>
+        <v>1.591250</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137659030.74</v>
+        <v>137656675.60</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.622554</v>
+        <v>8.623411</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344902144.90</v>
+        <v>344936447.47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.706591</v>
+        <v>0.706756</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>706590.53</v>
+        <v>706755.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.884579</v>
+        <v>0.884961</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>764219.73</v>
+        <v>764549.82</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.245634</v>
+        <v>2.245482</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170710527.19</v>
+        <v>170698933.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.711433</v>
+        <v>5.711416</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1622934050.51</v>
+        <v>1622929479.83</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.360480</v>
+        <v>1.363228</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2683720930.09</v>
+        <v>2689140658.63</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296374</v>
+        <v>1.296354</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744795895.46</v>
+        <v>1744769583.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>1.005901</v>
+        <v>0.974979</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>158429359.74</v>
+        <v>153559246.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>5.970833</v>
+        <v>5.974278</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6554138686.90</v>
+        <v>6557920269.43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1518.174190</v>
+        <v>1518.874410</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1372862147.23</v>
+        <v>1373495345.86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.172027</v>
+        <v>6.173281</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613017587.12</v>
+        <v>2613548452.90</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.079396</v>
+        <v>4.088429</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2584541965.56</v>
+        <v>2590265054.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.751705</v>
+        <v>6.754810</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>317868983.59</v>
+        <v>318015201.65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792181</v>
+        <v>1.792171</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444722772.43</v>
+        <v>444720383.14</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.456934</v>
+        <v>18.455082</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20262852.21</v>
+        <v>20260820.01</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.147783</v>
+        <v>3.151584</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>551732859.77</v>
+        <v>552399058.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.585364</v>
+        <v>14.589675</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>91</v>
       </c>
       <c r="G75" s="66">
-        <v>6450458755.43</v>
+        <v>6452365247.94</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.592345</v>
+        <v>6.592812</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2910403668.49</v>
+        <v>2910609971.30</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1361.823890</v>
+        <v>1361.814050</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393040078.36</v>
+        <v>393037238.28</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232674</v>
+        <v>5.232811</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355937989.92</v>
+        <v>355947304.12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>546.828700</v>
+        <v>441.473300</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>54682.87</v>
+        <v>44147.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7102.167000</v>
+        <v>7098.666000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>71021.67</v>
+        <v>70986.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>289.520600</v>
+        <v>184.183500</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>28952.06</v>
+        <v>18418.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.386391</v>
+        <v>46.512428</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1627652.06</v>
+        <v>1632074.59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1208.493167</v>
+        <v>1213.237567</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>112389864.55</v>
+        <v>112831093.74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.024133</v>
+        <v>21.025097</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671520560.88</v>
+        <v>1671597145.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.441277</v>
+        <v>31.439534</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>979029779.44</v>
+        <v>978975506.18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.365602</v>
+        <v>46.491636</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1626922.61</v>
+        <v>1631345.01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.077717</v>
+        <v>1.081114</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>608909933.38</v>
+        <v>610829388.95</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.565743</v>
+        <v>20.624129</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>206866342.17</v>
+        <v>207453639.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.695705</v>
+        <v>19.737714</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3070757332.54</v>
+        <v>3077306929.89</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014913</v>
+        <v>0.015292</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8212.16</v>
+        <v>8420.91</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5674.113787</v>
+        <v>5675.718378</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5428992071.68</v>
+        <v>5430527344.28</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,21 +2674,21 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.328432</v>
+        <v>1.328652</v>
       </c>
       <c r="E92" s="66">
-        <v>50000000.00</v>
+        <v>162915080.00</v>
       </c>
       <c r="F92" s="65">
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>66421615.13</v>
+        <v>216457392.19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778910</v>
+        <v>0.779013</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135925219.93</v>
+        <v>135943277.19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.596839</v>
+        <v>30.596452</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1549754901.51</v>
+        <v>1549735290.84</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094769</v>
+        <v>1.094689</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55494962.19</v>
+        <v>55490932.45</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208805</v>
+        <v>1.208885</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298574914.84</v>
+        <v>298594541.62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599464</v>
+        <v>0.599406</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70340028.16</v>
+        <v>70333212.21</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.523881</v>
+        <v>52.521250</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39010431.98</v>
+        <v>39008478.07</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.948255</v>
+        <v>19.947831</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109608560.10</v>
+        <v>109606229.87</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1010.828249</v>
+        <v>1013.576313</v>
       </c>
       <c r="E100" s="66">
         <v>22861.00</v>
@@ -2899,12 +2899,12 @@
         <v>2</v>
       </c>
       <c r="G100" s="66">
-        <v>23108544.60</v>
+        <v>23171368.10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.579472</v>
+        <v>0.580638</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1216891.84</v>
+        <v>1219340.83</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841237766.00</v>
+        <v>1841316506.59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.920411</v>
+        <v>4.935758</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>65951350.09</v>
+        <v>66157048.70</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.945106</v>
+        <v>13.945283</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174642080.52</v>
+        <v>174644300.15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.367833</v>
+        <v>9.367471</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78545719.58</v>
+        <v>78542685.30</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.407611</v>
+        <v>14.407463</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933595577.42</v>
+        <v>933585971.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.809613</v>
+        <v>8.808957</v>
       </c>
       <c r="E107" s="66">
         <v>78003587.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>687181410.45</v>
+        <v>687130230.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.930847</v>
+        <v>8.930566</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2907674490.59</v>
+        <v>2907582879.83</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.797583</v>
+        <v>29.799564</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661602321.19</v>
+        <v>661646301.24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.763934</v>
+        <v>2.771741</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>292769370.51</v>
+        <v>293596351.57</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.281596</v>
+        <v>48.329830</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1835850524.09</v>
+        <v>1837684558.80</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.615511</v>
+        <v>11.612307</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147480586.71</v>
+        <v>147439899.94</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.895926</v>
+        <v>4.903215</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>875545128.68</v>
+        <v>876848490.02</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.277539</v>
+        <v>39.341978</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40564035.70</v>
+        <v>40630585.23</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>145.106193</v>
+        <v>145.374543</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>557643.10</v>
+        <v>558674.37</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.136938</v>
+        <v>34.139967</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102410813.39</v>
+        <v>102419899.52</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002289</v>
+        <v>0.002296</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>259026011.86</v>
+        <v>259839274.83</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.954170</v>
+        <v>31.955972</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355090203.39</v>
+        <v>355110232.93</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>399.997382</v>
+        <v>400.297232</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>299786837.66</v>
+        <v>300011567.01</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.383114</v>
+        <v>2.374263</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>491567672.81</v>
+        <v>489741869.10</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912571</v>
+        <v>0.912534</v>
       </c>
       <c r="E121" s="66">
         <v>229647810.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>209569984.75</v>
+        <v>209561325.29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.502651</v>
+        <v>1.500318</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55154719.76</v>
+        <v>55069092.06</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.010604</v>
+        <v>27.022722</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391207062.62</v>
+        <v>391382565.20</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027765</v>
+        <v>2.027965</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59048381.48</v>
+        <v>59054206.13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.666741</v>
+        <v>21.686875</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119386908.31</v>
+        <v>119497849.15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.663309</v>
+        <v>7.662968</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178563631.90</v>
+        <v>178555687.24</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.024424</v>
+        <v>5.024291</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214490005.04</v>
+        <v>214484330.10</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723505</v>
+        <v>2.723468</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368712791.93</v>
+        <v>368707683.90</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.841180</v>
+        <v>23.843299</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451198733.96</v>
+        <v>451238836.33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.412095</v>
+        <v>5.411614</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44230278.66</v>
+        <v>44226345.30</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348231</v>
+        <v>1.348258</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1021019984.86</v>
+        <v>1021039931.30</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949878</v>
+        <v>0.949817</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87035756.86</v>
+        <v>87030192.60</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.219016</v>
+        <v>12.221770</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172052910.28</v>
+        <v>172091691.33</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.214224</v>
+        <v>2.215836</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157659191.53</v>
+        <v>157773918.14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.398854</v>
+        <v>13.414370</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101254185.46</v>
+        <v>101371438.89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.156282</v>
+        <v>94.172814</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24310210.47</v>
+        <v>24314478.84</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.657168</v>
+        <v>4.658652</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425157596.66</v>
+        <v>425293064.02</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.407696</v>
+        <v>18.437581</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>442152850.88</v>
+        <v>442870693.95</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27608.851934</v>
+        <v>27609.881928</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125178534.67</v>
+        <v>125183204.66</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4852.083518</v>
+        <v>4852.671834</v>
       </c>
       <c r="E141" s="66">
         <v>874610.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>4243680765.59</v>
+        <v>4244195312.37</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.210852</v>
+        <v>0.208752</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>210851.74</v>
+        <v>208751.62</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.383825</v>
+        <v>1.385205</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149676155.61</v>
+        <v>149825425.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.918327</v>
+        <v>15.918223</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156435509.65</v>
+        <v>1156428005.57</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.094563</v>
+        <v>16.094435</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5745943573.54</v>
+        <v>5745897680.78</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3291.481573</v>
+        <v>3292.726611</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193581905.78</v>
+        <v>193655130.18</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421457630.02</v>
+        <v>421457667.74</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.307799</v>
+        <v>1.312028</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>523639092.09</v>
+        <v>525332313.61</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.036645</v>
+        <v>1.036426</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13514445511.11</v>
+        <v>13511601958.70</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.922594</v>
+        <v>0.922338</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13650574276.18</v>
+        <v>13646790261.06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1930.684888</v>
+        <v>1930.489084</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41099933.36</v>
+        <v>41095765.14</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.584339</v>
+        <v>1.585926</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60948739.59</v>
+        <v>61009786.50</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6764.005801</v>
+        <v>6765.028072</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964209026.91</v>
+        <v>964354751.70</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.278766</v>
+        <v>1926.283120</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337747939.99</v>
+        <v>337748703.35</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17332.147058</v>
+        <v>17334.522537</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2503888624.77</v>
+        <v>2504231798.30</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20301.274871</v>
+        <v>20303.516431</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185025819.17</v>
+        <v>185046248.75</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15348.994527</v>
+        <v>15349.384965</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320333515.77</v>
+        <v>320341664.22</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1152.918656</v>
+        <v>1157.117509</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5869508.88</v>
+        <v>5890885.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3677.835881</v>
+        <v>3678.078622</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719572267.88</v>
+        <v>719619760.43</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200855.076193</v>
+        <v>200851.360126</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602192360.80</v>
+        <v>4602107214.56</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.391801</v>
+        <v>33.423683</v>
       </c>
       <c r="E162" s="66">
         <v>16759003.00</v>
@@ -4573,12 +4573,12 @@
         <v>25</v>
       </c>
       <c r="G162" s="66">
-        <v>559613287.23</v>
+        <v>560147596.55</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.951402</v>
+        <v>81.007314</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>398720223.08</v>
+        <v>398995611.12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400126</v>
+        <v>1.400356</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154338368.30</v>
+        <v>154363679.81</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.188419</v>
+        <v>2579.344347</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438464610.50</v>
+        <v>438491118.28</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731279</v>
+        <v>1678.731286</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092778.87</v>
+        <v>927092782.64</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027177</v>
+        <v>1.027192</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970674514.40</v>
+        <v>970688236.35</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1047.573240</v>
+        <v>1047.538588</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114517563.84</v>
+        <v>114513775.85</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.777555</v>
+        <v>75.827676</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65824855.10</v>
+        <v>65868393.20</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188104</v>
+        <v>3.188133</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977096701.48</v>
+        <v>977105752.35</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2979.185330</v>
+        <v>2979.636201</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2193797597.05</v>
+        <v>2194129607.24</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4280.378196</v>
+        <v>4309.742248</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19004879.19</v>
+        <v>19135255.58</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63325.162362</v>
+        <v>63325.732908</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174871737.31</v>
+        <v>1174882322.65</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.763114</v>
+        <v>8193.689523</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148987194.71</v>
+        <v>148985856.59</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>45479.164462</v>
+        <v>45494.283681</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>2977202543.19</v>
+        <v>2978192292.59</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11591.691586</v>
+        <v>11591.553747</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675710168.90</v>
+        <v>2675678351.41</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2485.838226</v>
+        <v>2488.282390</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92858486.94</v>
+        <v>92949788.67</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.989542</v>
+        <v>2705.837286</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459715151.25</v>
+        <v>459689284.84</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3495.837583</v>
+        <v>3496.380473</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20754787.73</v>
+        <v>20758010.87</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3287.205308</v>
+        <v>3287.178274</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6835145165.91</v>
+        <v>6835088954.22</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994842</v>
+        <v>0.994822</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928579903.93</v>
+        <v>928561962.19</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4661.251895</v>
+        <v>4661.207199</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70263711.07</v>
+        <v>70263037.32</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,21 +5131,21 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.176336</v>
+        <v>1.179001</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
       </c>
       <c r="F183" s="65">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="G183" s="66">
-        <v>2380139.95</v>
+        <v>2385531.93</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.725170</v>
+        <v>3592.722614</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917247884.89</v>
+        <v>917247232.52</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211637</v>
+        <v>1.211609</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226657919.08</v>
+        <v>226652552.64</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1330.962448</v>
+        <v>1331.098772</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502450302.80</v>
+        <v>502501766.39</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1110.547441</v>
+        <v>1109.391634</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1723023239.81</v>
+        <v>1721229995.02</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.939709</v>
+        <v>74.939440</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872897584.61</v>
+        <v>872894446.24</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.243574</v>
+        <v>10.308253</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>453899275.86</v>
+        <v>456765276.61</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>13.761796</v>
+        <v>13.762573</v>
       </c>
       <c r="E190" s="66">
         <v>159085884.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2189307545.35</v>
+        <v>2189431072.86</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7572.996887</v>
+        <v>7672.607081</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>283669317.40</v>
+        <v>287400516.05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,21 +5374,21 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>2.198676</v>
+        <v>1.921307</v>
       </c>
       <c r="E192" s="66">
-        <v>5273240.00</v>
+        <v>13687396.00</v>
       </c>
       <c r="F192" s="65">
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>11594144.96</v>
+        <v>26297683.72</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441687</v>
+        <v>2.441795</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206105349.42</v>
+        <v>206114450.55</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.427630</v>
+        <v>44.456295</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>565738776.58</v>
+        <v>566103796.94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14891.353588</v>
+        <v>14892.885054</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6207014002.36</v>
+        <v>6207652348.27</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6271.747448</v>
+        <v>6273.231309</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39762878.82</v>
+        <v>39772286.50</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.243091</v>
+        <v>2933.321327</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,349 +5545,349 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077506316.64</v>
+        <v>1077535056.31</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
-          <t xml:space="preserve">SGG</t>
+          <t xml:space="preserve">RZB</t>
         </is>
       </c>
       <c t="inlineStr" r="C199">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ROTA PORTFÖY YÖNETİMİ A.Ş. SEBA CENTER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D199">
-        <v>1.223996</v>
+        <v>0.000000</v>
       </c>
       <c r="E199" s="66">
-        <v>427328964.00</v>
+        <v>0.00</v>
       </c>
       <c r="F199" s="65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G199" s="66">
-        <v>523049061.19</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
-          <t xml:space="preserve">TCE</t>
+          <t xml:space="preserve">SGG</t>
         </is>
       </c>
       <c t="inlineStr" r="C200">
         <is>
-          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. SEKİZİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.323189</v>
+        <v>1.223987</v>
       </c>
       <c r="E200" s="66">
-        <v>92000000.00</v>
+        <v>427328964.00</v>
       </c>
       <c r="F200" s="65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>121733407.85</v>
+        <v>523045189.11</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
-          <t xml:space="preserve">TGI</t>
+          <t xml:space="preserve">TCE</t>
         </is>
       </c>
       <c t="inlineStr" r="C201">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TACİRLER PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D201">
-        <v>7.351407</v>
+        <v>1.323392</v>
       </c>
       <c r="E201" s="66">
-        <v>381640102.00</v>
+        <v>92000000.00</v>
       </c>
       <c r="F201" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>2805591877.71</v>
+        <v>121752106.65</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
-          <t xml:space="preserve">TLG</t>
+          <t xml:space="preserve">TGI</t>
         </is>
       </c>
       <c t="inlineStr" r="C202">
         <is>
-          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D202">
-        <v>998.147371</v>
+        <v>7.345621</v>
       </c>
       <c r="E202" s="66">
-        <v>448820.00</v>
+        <v>381640102.00</v>
       </c>
       <c r="F202" s="65">
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>447988502.88</v>
+        <v>2803383713.97</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
-          <t xml:space="preserve">TNG</t>
+          <t xml:space="preserve">TLG</t>
         </is>
       </c>
       <c t="inlineStr" r="C203">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ANATOLIA GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BEŞİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D203">
-        <v>2494.953241</v>
+        <v>998.171481</v>
       </c>
       <c r="E203" s="66">
-        <v>205132.00</v>
+        <v>448820.00</v>
       </c>
       <c r="F203" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>511794748.33</v>
+        <v>447999324.32</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">TNG</t>
         </is>
       </c>
       <c t="inlineStr" r="C204">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. TUNA PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D204">
-        <v>0.004375</v>
+        <v>2501.372884</v>
       </c>
       <c r="E204" s="66">
-        <v>67618383967.00</v>
+        <v>205132.00</v>
       </c>
       <c r="F204" s="65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>295805667.53</v>
+        <v>513111622.49</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D205">
-        <v>20.815424</v>
+        <v>0.004367</v>
       </c>
       <c r="E205" s="66">
-        <v>81092133.00</v>
+        <v>67618383967.00</v>
       </c>
       <c r="F205" s="65">
         <v>1</v>
       </c>
       <c r="G205" s="66">
-        <v>1687967153.33</v>
+        <v>295315427.46</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D206">
-        <v>3.365203</v>
+        <v>20.815058</v>
       </c>
       <c r="E206" s="66">
-        <v>21323550.00</v>
+        <v>81092133.00</v>
       </c>
       <c r="F206" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>71758074.59</v>
+        <v>1687937461.77</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D207">
-        <v>7687.516053</v>
+        <v>3.358518</v>
       </c>
       <c r="E207" s="66">
-        <v>197052.47</v>
+        <v>21323550.00</v>
       </c>
       <c r="F207" s="65">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G207" s="66">
-        <v>1514844057.22</v>
+        <v>71615530.62</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D208">
-        <v>1.844713</v>
+        <v>7691.356354</v>
       </c>
       <c r="E208" s="66">
-        <v>601179729.00</v>
+        <v>197052.47</v>
       </c>
       <c r="F208" s="65">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="G208" s="66">
-        <v>1109004288.24</v>
+        <v>1515600797.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">UUG</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D209">
-        <v>26.493103</v>
+        <v>1.844847</v>
       </c>
       <c r="E209" s="66">
-        <v>377.00</v>
+        <v>601179729.00</v>
       </c>
       <c r="F209" s="65">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G209" s="66">
-        <v>9987.90</v>
+        <v>1109084807.66</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">VBI</t>
+          <t xml:space="preserve">UUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.735238</v>
+        <v>25.855676</v>
       </c>
       <c r="E210" s="66">
-        <v>100000.00</v>
+        <v>377.00</v>
       </c>
       <c r="F210" s="65">
         <v>1</v>
       </c>
       <c r="G210" s="66">
-        <v>173523.79</v>
+        <v>9747.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">VIK</t>
+          <t xml:space="preserve">VBI</t>
         </is>
       </c>
       <c t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D211">
-        <v>1.735396</v>
+        <v>1.741412</v>
       </c>
       <c r="E211" s="66">
         <v>100000.00</v>
@@ -5896,844 +5896,871 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>173539.62</v>
+        <v>174141.22</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">VIK</t>
         </is>
       </c>
       <c t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D212">
-        <v>61.335495</v>
+        <v>1.741570</v>
       </c>
       <c r="E212" s="66">
-        <v>2554914.00</v>
+        <v>100000.00</v>
       </c>
       <c r="F212" s="65">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>156706914.84</v>
+        <v>174157.05</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">VVF</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D213">
-        <v>15.286899</v>
+        <v>61.330970</v>
       </c>
       <c r="E213" s="66">
-        <v>248000220.00</v>
+        <v>2554914.00</v>
       </c>
       <c r="F213" s="65">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G213" s="66">
-        <v>3791154382.68</v>
+        <v>156695354.34</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">VVF</t>
         </is>
       </c>
       <c t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D214">
-        <v>1.756418</v>
+        <v>15.232528</v>
       </c>
       <c r="E214" s="66">
-        <v>437816172.00</v>
+        <v>248000220.00</v>
       </c>
       <c r="F214" s="65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G214" s="66">
-        <v>768988116.84</v>
+        <v>3777670362.02</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D215">
-        <v>0.390804</v>
+        <v>1.801055</v>
       </c>
       <c r="E215" s="66">
-        <v>402507.00</v>
+        <v>437816172.00</v>
       </c>
       <c r="F215" s="65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G215" s="66">
-        <v>157301.52</v>
+        <v>788531058.38</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D216">
-        <v>9.880946</v>
+        <v>0.390420</v>
       </c>
       <c r="E216" s="66">
-        <v>27178800.00</v>
+        <v>402507.00</v>
       </c>
       <c r="F216" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G216" s="66">
-        <v>268552245.91</v>
+        <v>157146.80</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D217">
-        <v>15.620625</v>
+        <v>9.880374</v>
       </c>
       <c r="E217" s="66">
-        <v>10371838.00</v>
+        <v>27178800.00</v>
       </c>
       <c r="F217" s="65">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G217" s="66">
-        <v>162014588.79</v>
+        <v>268536703.54</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D218">
-        <v>15.329164</v>
+        <v>15.619395</v>
       </c>
       <c r="E218" s="66">
-        <v>19475841.00</v>
+        <v>10371838.00</v>
       </c>
       <c r="F218" s="65">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G218" s="66">
-        <v>298548360.88</v>
+        <v>162001829.63</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D219">
-        <v>31.096886</v>
+        <v>15.328343</v>
       </c>
       <c r="E219" s="66">
-        <v>9712281.00</v>
+        <v>19475841.00</v>
       </c>
       <c r="F219" s="65">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G219" s="66">
-        <v>302021690.82</v>
+        <v>298532371.15</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D220">
-        <v>7.981511</v>
+        <v>31.092413</v>
       </c>
       <c r="E220" s="66">
-        <v>12818249.00</v>
+        <v>9712281.00</v>
       </c>
       <c r="F220" s="65">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G220" s="66">
-        <v>102308994.42</v>
+        <v>301978254.67</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">YE3</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D221">
-        <v>1659.792804</v>
+        <v>7.980646</v>
       </c>
       <c r="E221" s="66">
-        <v>330000.00</v>
+        <v>12818249.00</v>
       </c>
       <c r="F221" s="65">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G221" s="66">
-        <v>547731625.30</v>
+        <v>102297902.88</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">YE6</t>
+          <t xml:space="preserve">YE3</t>
         </is>
       </c>
       <c t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D222">
-        <v>5.170240</v>
+        <v>1659.786738</v>
       </c>
       <c r="E222" s="66">
-        <v>11867933.00</v>
+        <v>330000.00</v>
       </c>
       <c r="F222" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G222" s="66">
-        <v>61360060.18</v>
+        <v>547729623.51</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">YGG</t>
+          <t xml:space="preserve">YE6</t>
         </is>
       </c>
       <c t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D223">
-        <v>0.946461</v>
+        <v>5.169473</v>
       </c>
       <c r="E223" s="66">
-        <v>130000000.00</v>
+        <v>11867933.00</v>
       </c>
       <c r="F223" s="65">
         <v>3</v>
       </c>
       <c r="G223" s="66">
-        <v>123039892.84</v>
+        <v>61350962.94</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">YGG</t>
         </is>
       </c>
       <c t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.531262</v>
+        <v>0.946555</v>
       </c>
       <c r="E224" s="66">
-        <v>103852814.00</v>
+        <v>130000000.00</v>
       </c>
       <c r="F224" s="65">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>574437072.92</v>
+        <v>123052106.67</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">YG2</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.000007</v>
+        <v>5.531297</v>
       </c>
       <c r="E225" s="66">
-        <v>869111122.00</v>
+        <v>103852814.00</v>
       </c>
       <c r="F225" s="65">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G225" s="66">
-        <v>6077.78</v>
+        <v>574440741.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">YG2</t>
         </is>
       </c>
       <c t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D226">
-        <v>6.607497</v>
+        <v>0.000007</v>
       </c>
       <c r="E226" s="66">
-        <v>11104667.00</v>
+        <v>869111122.00</v>
       </c>
       <c r="F226" s="65">
         <v>2</v>
       </c>
       <c r="G226" s="66">
-        <v>73374054.73</v>
+        <v>6077.77</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D227">
-        <v>26.532834</v>
+        <v>6.607009</v>
       </c>
       <c r="E227" s="66">
-        <v>1038884.00</v>
+        <v>11104667.00</v>
       </c>
       <c r="F227" s="65">
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>27564536.67</v>
+        <v>73368631.54</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D228">
-        <v>0.850873</v>
+        <v>26.526370</v>
       </c>
       <c r="E228" s="66">
-        <v>73432275.00</v>
+        <v>1038884.00</v>
       </c>
       <c r="F228" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>62481540.32</v>
+        <v>27557820.91</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D229">
-        <v>0.711793</v>
+        <v>0.850656</v>
       </c>
       <c r="E229" s="66">
-        <v>801655137.00</v>
+        <v>73432275.00</v>
       </c>
       <c r="F229" s="65">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G229" s="66">
-        <v>570612496.78</v>
+        <v>62465568.95</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">YG8</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D230">
-        <v>11.954564</v>
+        <v>0.711714</v>
       </c>
       <c r="E230" s="66">
-        <v>26235742.00</v>
+        <v>801655137.00</v>
       </c>
       <c r="F230" s="65">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G230" s="66">
-        <v>313636851.71</v>
+        <v>570549372.53</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">YOR</t>
+          <t xml:space="preserve">YG8</t>
         </is>
       </c>
       <c t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.004710</v>
+        <v>11.954510</v>
       </c>
       <c r="E231" s="66">
-        <v>100000.00</v>
+        <v>26235742.00</v>
       </c>
       <c r="F231" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G231" s="66">
-        <v>471.04</v>
+        <v>313635436.14</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">YOR</t>
         </is>
       </c>
       <c t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D232">
-        <v>1.543718</v>
+        <v>0.004710</v>
       </c>
       <c r="E232" s="66">
-        <v>24022001.00</v>
+        <v>100000.00</v>
       </c>
       <c r="F232" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G232" s="66">
-        <v>37083199.61</v>
+        <v>471.03</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">YZA</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D233">
-        <v>2.571827</v>
+        <v>1.548570</v>
       </c>
       <c r="E233" s="66">
-        <v>68085562.00</v>
+        <v>24022001.00</v>
       </c>
       <c r="F233" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G233" s="66">
-        <v>175104270.97</v>
+        <v>37199738.57</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">ZEP</t>
+          <t xml:space="preserve">YZA</t>
         </is>
       </c>
       <c t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1054.599490</v>
+        <v>2.572183</v>
       </c>
       <c r="E234" s="66">
-        <v>20029.00</v>
+        <v>68085562.00</v>
       </c>
       <c r="F234" s="65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G234" s="66">
-        <v>21122573.19</v>
+        <v>175128491.85</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">ZGG</t>
+          <t xml:space="preserve">ZEP</t>
         </is>
       </c>
       <c t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D235">
-        <v>3.243073</v>
+        <v>1055.699910</v>
       </c>
       <c r="E235" s="66">
-        <v>1427155857.00</v>
+        <v>20029.00</v>
       </c>
       <c r="F235" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G235" s="66">
-        <v>4628371012.66</v>
+        <v>21144613.49</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">ZGG</t>
         </is>
       </c>
       <c t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1687.447784</v>
+        <v>3.244653</v>
       </c>
       <c r="E236" s="66">
-        <v>97333.00</v>
+        <v>1427155857.00</v>
       </c>
       <c r="F236" s="65">
         <v>2</v>
       </c>
       <c r="G236" s="66">
-        <v>164244355.19</v>
+        <v>4630625042.39</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D237">
-        <v>1.161333</v>
+        <v>1687.747603</v>
       </c>
       <c r="E237" s="66">
-        <v>1103857956.00</v>
+        <v>97333.00</v>
       </c>
       <c r="F237" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>1281946250.58</v>
+        <v>164273537.48</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D238">
-        <v>2.265050</v>
+        <v>1.161302</v>
       </c>
       <c r="E238" s="66">
-        <v>296754544.00</v>
+        <v>1103857956.00</v>
       </c>
       <c r="F238" s="65">
         <v>3</v>
       </c>
       <c r="G238" s="66">
-        <v>672164003.71</v>
+        <v>1281912225.28</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">ZUC</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="D239">
-        <v>999.816406</v>
+        <v>2.254758</v>
       </c>
       <c r="E239" s="66">
-        <v>1431712.00</v>
+        <v>296754544.00</v>
       </c>
       <c r="F239" s="65">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1431449145.60</v>
+        <v>669109607.95</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">ZUC</t>
         </is>
       </c>
       <c t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D240">
-        <v>5.001647</v>
+        <v>1002.962975</v>
       </c>
       <c r="E240" s="66">
-        <v>395532870.00</v>
+        <v>1431712.00</v>
       </c>
       <c r="F240" s="65">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="G240" s="66">
-        <v>1978315951.70</v>
+        <v>1435954126.95</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1303.876849</v>
+        <v>5.001709</v>
       </c>
       <c r="E241" s="66">
-        <v>1467447.00</v>
+        <v>395532870.00</v>
       </c>
       <c r="F241" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G241" s="66">
-        <v>1913370170.80</v>
+        <v>1978340366.64</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
+          <t xml:space="preserve">ZVD</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C242">
+        <is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D242">
+        <v>1303.866195</v>
+      </c>
+      <c r="E242" s="66">
+        <v>1467447.00</v>
+      </c>
+      <c r="F242" s="65">
+        <v>1</v>
+      </c>
+      <c r="G242" s="66">
+        <v>1913354536.00</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="67">
+        <v>46126</v>
+      </c>
+      <c t="inlineStr" r="B243">
+        <is>
           <t xml:space="preserve">ZVE</t>
         </is>
       </c>
-      <c t="inlineStr" r="C242">
+      <c t="inlineStr" r="C243">
         <is>
           <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="D242">
-        <v>26995.730390</v>
-      </c>
-      <c r="E242" s="66">
+      <c t="n" r="D243">
+        <v>27000.729074</v>
+      </c>
+      <c r="E243" s="66">
         <v>40026.00</v>
       </c>
-      <c r="F242" s="65">
-        <v>1</v>
-      </c>
-      <c r="G242" s="66">
-        <v>1080531104.59</v>
+      <c r="F243" s="65">
+        <v>1</v>
+      </c>
+      <c r="G243" s="66">
+        <v>1080731181.92</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.858706</v>
+        <v>7724.860434</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915788133.73</v>
+        <v>1915788562.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.209084</v>
+        <v>29.248129</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5077169618.61</v>
+        <v>5083956452.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.606727</v>
+        <v>0.602396</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>303363.34</v>
+        <v>301197.90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11302.007220</v>
+        <v>11302.995364</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3334250357.94</v>
+        <v>3334541874.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5355.081826</v>
+        <v>5355.354298</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52212047.80</v>
+        <v>52214704.41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24478.936678</v>
+        <v>24466.328517</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2024408063.26</v>
+        <v>2023365368.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.419347</v>
+        <v>9968.515813</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72928955.94</v>
+        <v>72929661.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198852</v>
+        <v>2.198792</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1265130221.31</v>
+        <v>1265096022.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.113557</v>
+        <v>1141.410523</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893721279.20</v>
+        <v>893953863.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>364.470010</v>
+        <v>365.014778</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>376861.99</v>
+        <v>377425.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.357193</v>
+        <v>23.356023</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333485940.76</v>
+        <v>2333368985.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.494933</v>
+        <v>24.490216</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2700868981.99</v>
+        <v>2700348949.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340039</v>
+        <v>8.340041</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506743.45</v>
+        <v>94506762.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.464816</v>
+        <v>7.462377</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>548845904.42</v>
+        <v>548666604.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.815195</v>
+        <v>10.815095</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164666863.71</v>
+        <v>164665332.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>968.166491</v>
+        <v>967.894140</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41677631.10</v>
+        <v>41665906.93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1223.496571</v>
+        <v>1224.937338</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11624440.92</v>
+        <v>11638129.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.647387</v>
+        <v>13.647834</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569350408.64</v>
+        <v>1569401806.80</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999449</v>
+        <v>0.999394</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99944.87</v>
+        <v>99939.39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1012.796113</v>
+        <v>1013.305815</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20255922.25</v>
+        <v>20266116.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.569782</v>
+        <v>724.562202</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004983620.97</v>
+        <v>3004952186.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.456601</v>
+        <v>1124.449178</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723575569.31</v>
+        <v>2723557589.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999449</v>
+        <v>0.999394</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99944.87</v>
+        <v>99939.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.649672</v>
+        <v>1.650551</v>
       </c>
       <c r="E27" s="66">
         <v>292286905.00</v>
@@ -928,12 +928,12 @@
         <v>18</v>
       </c>
       <c r="G27" s="66">
-        <v>482177653.09</v>
+        <v>482434396.45</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>904.367149</v>
+        <v>899.610862</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4520931.38</v>
+        <v>4497154.70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1165.347757</v>
+        <v>1165.843841</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>58267387.86</v>
+        <v>58292192.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809404</v>
+        <v>1.809471</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361880748.35</v>
+        <v>361894118.29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1365.293130</v>
+        <v>1366.286835</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5461172.52</v>
+        <v>5465147.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7322.249033</v>
+        <v>7322.123477</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533682120.78</v>
+        <v>533672969.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6962.358506</v>
+        <v>6974.922642</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>172896248.77</v>
+        <v>173208253.98</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20486.719749</v>
+        <v>20487.031559</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>333277956.87</v>
+        <v>333283029.40</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1156.625280</v>
+        <v>1157.477318</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5783126.40</v>
+        <v>5787386.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1155.625280</v>
+        <v>1156.477318</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5778126.40</v>
+        <v>5782386.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1036.813813</v>
+        <v>1036.567009</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26024026.70</v>
+        <v>26017831.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694918</v>
+        <v>1.694887</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231645829.73</v>
+        <v>231641639.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1222.568134</v>
+        <v>1223.786812</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>325893874.75</v>
+        <v>326218731.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3687.258108</v>
+        <v>3687.278062</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>752200654.11</v>
+        <v>752204724.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3603.114280</v>
+        <v>3610.053203</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>252808910.36</v>
+        <v>253295772.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6947.906945</v>
+        <v>6858.177737</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>194649371.89</v>
+        <v>192135559.57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110094</v>
+        <v>0.110081</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34771886.31</v>
+        <v>34767535.54</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947006</v>
+        <v>1.947066</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242638084.38</v>
+        <v>242645627.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.579909</v>
+        <v>5.605009</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59174261.89</v>
+        <v>59440445.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465218</v>
+        <v>0.465212</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652058801.25</v>
+        <v>1652035072.01</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008878</v>
+        <v>0.008870</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>603982921.87</v>
+        <v>603409912.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.128066</v>
+        <v>0.127817</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>184260.35</v>
+        <v>183901.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.443289</v>
+        <v>0.443370</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>606411.92</v>
+        <v>606522.19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1771.121864</v>
+        <v>1773.014709</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>508225190.08</v>
+        <v>508768343.75</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16910.440262</v>
+        <v>16912.112169</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370287910.42</v>
+        <v>370324520.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.280951</v>
+        <v>1.281821</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12826165.91</v>
+        <v>12834870.90</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7527.282603</v>
+        <v>7526.567511</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44553985.73</v>
+        <v>44549753.10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.325092</v>
+        <v>7.326962</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>241905181.28</v>
+        <v>241966932.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.101992</v>
+        <v>0.091796</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>115274.31</v>
+        <v>103750.76</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.355416</v>
+        <v>6.359054</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109518223.76</v>
+        <v>109580910.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990331</v>
+        <v>0.990292</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59419885.98</v>
+        <v>59417524.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591250</v>
+        <v>1.591116</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137656675.60</v>
+        <v>137645062.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.623411</v>
+        <v>8.623220</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344936447.47</v>
+        <v>344928812.70</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.706756</v>
+        <v>0.696508</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>706755.58</v>
+        <v>696507.64</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.884961</v>
+        <v>0.873006</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>764549.82</v>
+        <v>754221.32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.245482</v>
+        <v>2.245204</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170698933.11</v>
+        <v>170677838.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.711416</v>
+        <v>5.711643</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1622929479.83</v>
+        <v>1622993759.87</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.363228</v>
+        <v>1.364112</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2689140658.63</v>
+        <v>2690884325.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296354</v>
+        <v>1.296334</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744769583.65</v>
+        <v>1744742035.11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.974979</v>
+        <v>0.975078</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153559246.51</v>
+        <v>153574706.90</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>5.974278</v>
+        <v>5.975611</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6557920269.43</v>
+        <v>6559383721.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1518.874410</v>
+        <v>1519.039131</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1373495345.86</v>
+        <v>1373644300.91</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.173281</v>
+        <v>6.173660</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613548452.90</v>
+        <v>2613709130.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.088429</v>
+        <v>4.091657</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2590265054.47</v>
+        <v>2592310249.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.754810</v>
+        <v>6.757945</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>318015201.65</v>
+        <v>318162782.52</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792171</v>
+        <v>1.792147</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444720383.14</v>
+        <v>444714304.18</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.455082</v>
+        <v>18.453088</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20260820.01</v>
+        <v>20258630.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.151584</v>
+        <v>3.152712</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>552399058.16</v>
+        <v>552596631.88</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.589675</v>
+        <v>14.590185</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>91</v>
       </c>
       <c r="G75" s="66">
-        <v>6452365247.94</v>
+        <v>6452591042.30</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.592812</v>
+        <v>6.593194</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2910609971.30</v>
+        <v>2910778536.06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1361.814050</v>
+        <v>1362.001050</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393037238.28</v>
+        <v>393091209.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232811</v>
+        <v>5.232753</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355947304.12</v>
+        <v>355943369.90</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>441.473300</v>
+        <v>441.142200</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>44147.33</v>
+        <v>44114.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7098.666000</v>
+        <v>7095.165000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70986.66</v>
+        <v>70951.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>184.183500</v>
+        <v>183.870900</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18418.35</v>
+        <v>18387.09</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.512428</v>
+        <v>46.547521</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1632074.59</v>
+        <v>1633305.95</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1213.237567</v>
+        <v>1214.727995</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>112831093.74</v>
+        <v>112969703.58</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.025097</v>
+        <v>21.024880</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671597145.54</v>
+        <v>1671579953.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.439534</v>
+        <v>31.437516</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978975506.18</v>
+        <v>978912673.89</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.491636</v>
+        <v>46.526748</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1631345.01</v>
+        <v>1632577.06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.081114</v>
+        <v>1.082219</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>610829388.95</v>
+        <v>611453792.65</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.624129</v>
+        <v>20.640556</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>207453639.93</v>
+        <v>207618876.43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.737714</v>
+        <v>19.738810</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3077306929.89</v>
+        <v>3077477824.47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.015292</v>
+        <v>0.014540</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8420.91</v>
+        <v>8007.21</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5675.718378</v>
+        <v>5676.461724</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5430527344.28</v>
+        <v>5431238577.06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.328652</v>
+        <v>1.330614</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>216457392.19</v>
+        <v>216777105.91</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.779013</v>
+        <v>0.778946</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135943277.19</v>
+        <v>135931626.92</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.596452</v>
+        <v>30.595867</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1549735290.84</v>
+        <v>1549705661.76</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094689</v>
+        <v>1.094483</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55490932.45</v>
+        <v>55480475.66</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208885</v>
+        <v>1.208871</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298594541.62</v>
+        <v>298591196.08</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599406</v>
+        <v>0.599346</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70333212.21</v>
+        <v>70326202.85</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.521250</v>
+        <v>52.516977</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39008478.07</v>
+        <v>39005304.05</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.947831</v>
+        <v>19.947407</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109606229.87</v>
+        <v>109603899.64</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1013.576313</v>
+        <v>1013.873124</v>
       </c>
       <c r="E100" s="66">
         <v>22861.00</v>
@@ -2899,12 +2899,12 @@
         <v>2</v>
       </c>
       <c r="G100" s="66">
-        <v>23171368.10</v>
+        <v>23178153.49</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.580638</v>
+        <v>0.580834</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1219340.83</v>
+        <v>1219750.44</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841316506.59</v>
+        <v>1841330764.81</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.935758</v>
+        <v>4.940807</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66157048.70</v>
+        <v>66224720.24</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.945283</v>
+        <v>13.945097</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174644300.15</v>
+        <v>174641965.83</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.367471</v>
+        <v>9.367109</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78542685.30</v>
+        <v>78539651.08</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.407463</v>
+        <v>14.407282</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933585971.42</v>
+        <v>933574264.02</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808957</v>
+        <v>8.808807</v>
       </c>
       <c r="E107" s="66">
         <v>78003587.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>687130230.99</v>
+        <v>687118565.95</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.930566</v>
+        <v>8.933853</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2907582879.83</v>
+        <v>2908652966.48</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.799564</v>
+        <v>29.804596</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661646301.24</v>
+        <v>661758030.63</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.771741</v>
+        <v>2.774195</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>293596351.57</v>
+        <v>293856263.08</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.329830</v>
+        <v>48.340897</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1837684558.80</v>
+        <v>1838105381.50</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.612307</v>
+        <v>11.611155</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147439899.94</v>
+        <v>147425276.26</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.903215</v>
+        <v>4.903442</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876848490.02</v>
+        <v>876889144.69</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.341978</v>
+        <v>39.361867</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40630585.23</v>
+        <v>40651125.89</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>145.374543</v>
+        <v>145.375280</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>558674.37</v>
+        <v>558677.20</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.139967</v>
+        <v>34.136465</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102419899.52</v>
+        <v>102409396.21</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002296</v>
+        <v>0.002299</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>259839274.83</v>
+        <v>260111721.86</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.955972</v>
+        <v>31.956014</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355110232.93</v>
+        <v>355110692.84</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>400.297232</v>
+        <v>400.377209</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300011567.01</v>
+        <v>300071507.25</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.374263</v>
+        <v>2.379244</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>489741869.10</v>
+        <v>490769239.08</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912534</v>
+        <v>0.912485</v>
       </c>
       <c r="E121" s="66">
         <v>229647810.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>209561325.29</v>
+        <v>209550182.77</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.500318</v>
+        <v>1.500248</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55069092.06</v>
+        <v>55066492.12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.022722</v>
+        <v>27.023477</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391382565.20</v>
+        <v>391393497.19</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027965</v>
+        <v>2.027946</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59054206.13</v>
+        <v>59053631.11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.686875</v>
+        <v>21.685175</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119497849.15</v>
+        <v>119488480.54</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.662968</v>
+        <v>7.662627</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178555687.24</v>
+        <v>178547742.83</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.024291</v>
+        <v>5.024101</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214484330.10</v>
+        <v>214476234.69</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723468</v>
+        <v>2.723412</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368707683.90</v>
+        <v>368700168.99</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.843299</v>
+        <v>23.843725</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451238836.33</v>
+        <v>451246915.11</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.411614</v>
+        <v>5.411133</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44226345.30</v>
+        <v>44222412.06</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348258</v>
+        <v>1.348184</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1021039931.30</v>
+        <v>1020984319.97</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949817</v>
+        <v>0.949756</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87030192.60</v>
+        <v>87024628.59</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.221770</v>
+        <v>12.221925</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172091691.33</v>
+        <v>172093865.71</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.215836</v>
+        <v>2.216325</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157773918.14</v>
+        <v>157808773.58</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.414370</v>
+        <v>13.418984</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101371438.89</v>
+        <v>101406308.30</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.172814</v>
+        <v>94.096593</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24314478.84</v>
+        <v>24294799.33</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.658652</v>
+        <v>4.659098</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425293064.02</v>
+        <v>425333784.25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.437581</v>
+        <v>18.439006</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>442870693.95</v>
+        <v>442904916.65</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27609.881928</v>
+        <v>27607.579230</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125183204.66</v>
+        <v>125172764.23</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4852.671834</v>
+        <v>4852.862985</v>
       </c>
       <c r="E141" s="66">
         <v>874610.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>4244195312.37</v>
+        <v>4244362495.14</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.208752</v>
+        <v>0.206652</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>208751.62</v>
+        <v>206651.50</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.385205</v>
+        <v>1.385771</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149825425.14</v>
+        <v>149886612.62</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.918223</v>
+        <v>15.918397</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156428005.57</v>
+        <v>1156440636.17</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.094435</v>
+        <v>16.094734</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5745897680.78</v>
+        <v>5746004525.63</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3292.726611</v>
+        <v>3292.831775</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193655130.18</v>
+        <v>193661315.18</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421457667.74</v>
+        <v>421457680.06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.312028</v>
+        <v>1.313409</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>525332313.61</v>
+        <v>525885393.48</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.036426</v>
+        <v>1.036209</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13511601958.70</v>
+        <v>13508766679.42</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.922338</v>
+        <v>0.922083</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13646790261.06</v>
+        <v>13643020437.81</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1930.489084</v>
+        <v>1930.443949</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41095765.14</v>
+        <v>41094804.32</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.585926</v>
+        <v>1.583883</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>61009786.50</v>
+        <v>60931191.72</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6765.028072</v>
+        <v>6765.147450</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964354751.70</v>
+        <v>964371768.95</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.283120</v>
+        <v>1926.284575</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337748703.35</v>
+        <v>337748958.58</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17334.522537</v>
+        <v>17335.316794</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504231798.30</v>
+        <v>2504346540.59</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20303.516431</v>
+        <v>20304.312953</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185046248.75</v>
+        <v>185053508.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15349.384965</v>
+        <v>15349.510184</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320341664.22</v>
+        <v>320344277.53</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1157.117509</v>
+        <v>1158.493324</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5890885.24</v>
+        <v>5897889.51</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3678.078622</v>
+        <v>3675.206727</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719619760.43</v>
+        <v>719057871.29</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200851.360126</v>
+        <v>200851.246707</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602107214.56</v>
+        <v>4602104615.80</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.423683</v>
+        <v>33.436658</v>
       </c>
       <c r="E162" s="66">
         <v>16759003.00</v>
@@ -4573,12 +4573,12 @@
         <v>25</v>
       </c>
       <c r="G162" s="66">
-        <v>560147596.55</v>
+        <v>560365052.02</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>81.007314</v>
+        <v>80.459663</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>398995611.12</v>
+        <v>396298196.48</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400356</v>
+        <v>1.400432</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154363679.81</v>
+        <v>154372093.55</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.344347</v>
+        <v>2579.389389</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438491118.28</v>
+        <v>438498775.57</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731286</v>
+        <v>1678.731288</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092782.64</v>
+        <v>927092783.83</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027192</v>
+        <v>1.027180</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970688236.35</v>
+        <v>970677507.49</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1047.538588</v>
+        <v>1047.496778</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114513775.85</v>
+        <v>114509205.23</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.827676</v>
+        <v>75.839843</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65868393.20</v>
+        <v>65878962.14</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188133</v>
+        <v>3.188115</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977105752.35</v>
+        <v>977100055.98</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2979.636201</v>
+        <v>2979.778477</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2194129607.24</v>
+        <v>2194234375.76</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4309.742248</v>
+        <v>4304.496351</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19135255.58</v>
+        <v>19111963.80</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63325.732908</v>
+        <v>63328.093002</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174882322.65</v>
+        <v>1174926109.46</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.689523</v>
+        <v>8193.615931</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148985856.59</v>
+        <v>148984518.47</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>45494.283681</v>
+        <v>45485.960698</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>2978192292.59</v>
+        <v>2977647445.20</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11591.553747</v>
+        <v>11591.415907</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675678351.41</v>
+        <v>2675646533.92</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2488.282390</v>
+        <v>2491.138569</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92949788.67</v>
+        <v>93056481.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.837286</v>
+        <v>2705.683364</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459689284.84</v>
+        <v>459663135.29</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3496.380473</v>
+        <v>3497.302617</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20758010.87</v>
+        <v>20763485.64</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3287.178274</v>
+        <v>3287.031831</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6835088954.22</v>
+        <v>6834784452.40</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994822</v>
+        <v>0.994795</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928561962.19</v>
+        <v>928536207.10</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4661.207199</v>
+        <v>4661.162503</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70263037.32</v>
+        <v>70262363.57</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,21 +5131,21 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.179001</v>
+        <v>1.179391</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
       </c>
       <c r="F183" s="65">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2385531.93</v>
+        <v>2386321.16</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.722614</v>
+        <v>3592.720059</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917247232.52</v>
+        <v>917246580.15</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211609</v>
+        <v>1.211579</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226652552.64</v>
+        <v>226647104.29</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.098772</v>
+        <v>1331.124883</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502501766.39</v>
+        <v>502511623.64</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.391634</v>
+        <v>1109.381653</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721229995.02</v>
+        <v>1721214508.92</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.939440</v>
+        <v>74.938987</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872894446.24</v>
+        <v>872889174.72</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.308253</v>
+        <v>10.252170</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>456765276.61</v>
+        <v>454280204.64</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>13.762573</v>
+        <v>14.207589</v>
       </c>
       <c r="E190" s="66">
         <v>159085884.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2189431072.86</v>
+        <v>2260226855.57</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7672.607081</v>
+        <v>7624.078138</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>287400516.05</v>
+        <v>285582718.88</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.921307</v>
+        <v>1.916657</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26297683.72</v>
+        <v>26234042.22</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441795</v>
+        <v>2.441904</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206114450.55</v>
+        <v>206123682.22</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.456295</v>
+        <v>44.436124</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>566103796.94</v>
+        <v>565846934.57</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14892.885054</v>
+        <v>14893.342464</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6207652348.27</v>
+        <v>6207843005.68</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6273.231309</v>
+        <v>6273.660710</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39772286.50</v>
+        <v>39775008.90</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.321327</v>
+        <v>2933.337373</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077535056.31</v>
+        <v>1077540950.65</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223987</v>
+        <v>1.223974</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523045189.11</v>
+        <v>523039492.33</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323392</v>
+        <v>1.323408</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121752106.65</v>
+        <v>121753536.28</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.345621</v>
+        <v>7.347874</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2803383713.97</v>
+        <v>2804243247.23</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>998.171481</v>
+        <v>998.199202</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>447999324.32</v>
+        <v>448011766.06</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2501.372884</v>
+        <v>2504.141704</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>513111622.49</v>
+        <v>513679596.05</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>0.004367</v>
+        <v>0.004372</v>
       </c>
       <c r="E205" s="66">
         <v>67618383967.00</v>
@@ -5734,12 +5734,12 @@
         <v>1</v>
       </c>
       <c r="G205" s="66">
-        <v>295315427.46</v>
+        <v>295633729.81</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>20.815058</v>
+        <v>20.816852</v>
       </c>
       <c r="E206" s="66">
         <v>81092133.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>1687937461.77</v>
+        <v>1688082938.69</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>3.358518</v>
+        <v>3.358587</v>
       </c>
       <c r="E207" s="66">
         <v>21323550.00</v>
@@ -5788,12 +5788,12 @@
         <v>2</v>
       </c>
       <c r="G207" s="66">
-        <v>71615530.62</v>
+        <v>71616994.37</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,21 +5806,21 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>7691.356354</v>
+        <v>7692.953742</v>
       </c>
       <c r="E208" s="66">
         <v>197052.47</v>
       </c>
       <c r="F208" s="65">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G208" s="66">
-        <v>1515600797.99</v>
+        <v>1515915567.26</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>1.844847</v>
+        <v>1.844818</v>
       </c>
       <c r="E209" s="66">
         <v>601179729.00</v>
@@ -5842,12 +5842,12 @@
         <v>16</v>
       </c>
       <c r="G209" s="66">
-        <v>1109084807.66</v>
+        <v>1109066944.18</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>25.855676</v>
+        <v>25.012812</v>
       </c>
       <c r="E210" s="66">
         <v>377.00</v>
@@ -5869,12 +5869,12 @@
         <v>1</v>
       </c>
       <c r="G210" s="66">
-        <v>9747.59</v>
+        <v>9429.83</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>1.741412</v>
+        <v>1.743416</v>
       </c>
       <c r="E211" s="66">
         <v>100000.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>174141.22</v>
+        <v>174341.56</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.741570</v>
+        <v>1.743574</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>174157.05</v>
+        <v>174357.39</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>61.330970</v>
+        <v>61.326071</v>
       </c>
       <c r="E213" s="66">
         <v>2554914.00</v>
@@ -5950,12 +5950,12 @@
         <v>9</v>
       </c>
       <c r="G213" s="66">
-        <v>156695354.34</v>
+        <v>156682837.00</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>15.232528</v>
+        <v>15.235480</v>
       </c>
       <c r="E214" s="66">
         <v>248000220.00</v>
@@ -5977,12 +5977,12 @@
         <v>2</v>
       </c>
       <c r="G214" s="66">
-        <v>3777670362.02</v>
+        <v>3778402291.08</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>1.801055</v>
+        <v>1.801144</v>
       </c>
       <c r="E215" s="66">
         <v>437816172.00</v>
@@ -6004,12 +6004,12 @@
         <v>7</v>
       </c>
       <c r="G215" s="66">
-        <v>788531058.38</v>
+        <v>788570166.45</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>0.390420</v>
+        <v>0.390020</v>
       </c>
       <c r="E216" s="66">
         <v>402507.00</v>
@@ -6031,12 +6031,12 @@
         <v>2</v>
       </c>
       <c r="G216" s="66">
-        <v>157146.80</v>
+        <v>156985.90</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>9.880374</v>
+        <v>9.879779</v>
       </c>
       <c r="E217" s="66">
         <v>27178800.00</v>
@@ -6058,12 +6058,12 @@
         <v>1</v>
       </c>
       <c r="G217" s="66">
-        <v>268536703.54</v>
+        <v>268520544.72</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>15.619395</v>
+        <v>15.618291</v>
       </c>
       <c r="E218" s="66">
         <v>10371838.00</v>
@@ -6085,12 +6085,12 @@
         <v>34</v>
       </c>
       <c r="G218" s="66">
-        <v>162001829.63</v>
+        <v>161990379.16</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.328343</v>
+        <v>15.327663</v>
       </c>
       <c r="E219" s="66">
         <v>19475841.00</v>
@@ -6112,12 +6112,12 @@
         <v>26</v>
       </c>
       <c r="G219" s="66">
-        <v>298532371.15</v>
+        <v>298519126.36</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>31.092413</v>
+        <v>31.090819</v>
       </c>
       <c r="E220" s="66">
         <v>9712281.00</v>
@@ -6139,12 +6139,12 @@
         <v>13</v>
       </c>
       <c r="G220" s="66">
-        <v>301978254.67</v>
+        <v>301962772.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>7.980646</v>
+        <v>7.980117</v>
       </c>
       <c r="E221" s="66">
         <v>12818249.00</v>
@@ -6166,12 +6166,12 @@
         <v>23</v>
       </c>
       <c r="G221" s="66">
-        <v>102297902.88</v>
+        <v>102291127.53</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>1659.786738</v>
+        <v>1659.780672</v>
       </c>
       <c r="E222" s="66">
         <v>330000.00</v>
@@ -6193,12 +6193,12 @@
         <v>2</v>
       </c>
       <c r="G222" s="66">
-        <v>547729623.51</v>
+        <v>547727621.72</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>5.169473</v>
+        <v>5.169780</v>
       </c>
       <c r="E223" s="66">
         <v>11867933.00</v>
@@ -6220,12 +6220,12 @@
         <v>3</v>
       </c>
       <c r="G223" s="66">
-        <v>61350962.94</v>
+        <v>61354606.75</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>0.946555</v>
+        <v>0.946583</v>
       </c>
       <c r="E224" s="66">
         <v>130000000.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>123052106.67</v>
+        <v>123055763.27</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>5.531297</v>
+        <v>5.519549</v>
       </c>
       <c r="E225" s="66">
         <v>103852814.00</v>
@@ -6274,12 +6274,12 @@
         <v>29</v>
       </c>
       <c r="G225" s="66">
-        <v>574440741.81</v>
+        <v>573220645.30</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6301,12 +6301,12 @@
         <v>2</v>
       </c>
       <c r="G226" s="66">
-        <v>6077.77</v>
+        <v>6077.76</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c t="n" r="D227">
-        <v>6.607009</v>
+        <v>6.606520</v>
       </c>
       <c r="E227" s="66">
         <v>11104667.00</v>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>73368631.54</v>
+        <v>73363208.35</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>26.526370</v>
+        <v>26.523143</v>
       </c>
       <c r="E228" s="66">
         <v>1038884.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>27557820.91</v>
+        <v>27554468.47</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>0.850656</v>
+        <v>0.850547</v>
       </c>
       <c r="E229" s="66">
         <v>73432275.00</v>
@@ -6382,12 +6382,12 @@
         <v>4</v>
       </c>
       <c r="G229" s="66">
-        <v>62465568.95</v>
+        <v>62457631.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.711714</v>
+        <v>0.711658</v>
       </c>
       <c r="E230" s="66">
         <v>801655137.00</v>
@@ -6409,12 +6409,12 @@
         <v>28</v>
       </c>
       <c r="G230" s="66">
-        <v>570549372.53</v>
+        <v>570504608.65</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>11.954510</v>
+        <v>11.956876</v>
       </c>
       <c r="E231" s="66">
         <v>26235742.00</v>
@@ -6436,12 +6436,12 @@
         <v>5</v>
       </c>
       <c r="G231" s="66">
-        <v>313635436.14</v>
+        <v>313697520.53</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6463,12 +6463,12 @@
         <v>1</v>
       </c>
       <c r="G232" s="66">
-        <v>471.03</v>
+        <v>471.02</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c t="n" r="D233">
-        <v>1.548570</v>
+        <v>1.550113</v>
       </c>
       <c r="E233" s="66">
         <v>24022001.00</v>
@@ -6490,12 +6490,12 @@
         <v>2</v>
       </c>
       <c r="G233" s="66">
-        <v>37199738.57</v>
+        <v>37236827.25</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>2.572183</v>
+        <v>2.572198</v>
       </c>
       <c r="E234" s="66">
         <v>68085562.00</v>
@@ -6517,12 +6517,12 @@
         <v>6</v>
       </c>
       <c r="G234" s="66">
-        <v>175128491.85</v>
+        <v>175129537.95</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>1055.699910</v>
+        <v>1056.755737</v>
       </c>
       <c r="E235" s="66">
         <v>20029.00</v>
@@ -6544,12 +6544,12 @@
         <v>1</v>
       </c>
       <c r="G235" s="66">
-        <v>21144613.49</v>
+        <v>21165760.66</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>3.244653</v>
+        <v>3.245111</v>
       </c>
       <c r="E236" s="66">
         <v>1427155857.00</v>
@@ -6571,12 +6571,12 @@
         <v>2</v>
       </c>
       <c r="G236" s="66">
-        <v>4630625042.39</v>
+        <v>4631279712.84</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>1687.747603</v>
+        <v>1689.526217</v>
       </c>
       <c r="E237" s="66">
         <v>97333.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>164273537.48</v>
+        <v>164446655.29</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1.161302</v>
+        <v>1.161269</v>
       </c>
       <c r="E238" s="66">
         <v>1103857956.00</v>
@@ -6625,12 +6625,12 @@
         <v>3</v>
       </c>
       <c r="G238" s="66">
-        <v>1281912225.28</v>
+        <v>1281876212.41</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>2.254758</v>
+        <v>2.247800</v>
       </c>
       <c r="E239" s="66">
         <v>296754544.00</v>
@@ -6652,12 +6652,12 @@
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>669109607.95</v>
+        <v>667045003.48</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>1002.962975</v>
+        <v>1003.943815</v>
       </c>
       <c r="E240" s="66">
         <v>1431712.00</v>
@@ -6679,12 +6679,12 @@
         <v>260</v>
       </c>
       <c r="G240" s="66">
-        <v>1435954126.95</v>
+        <v>1437358407.53</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>5.001709</v>
+        <v>5.001632</v>
       </c>
       <c r="E241" s="66">
         <v>395532870.00</v>
@@ -6706,12 +6706,12 @@
         <v>5</v>
       </c>
       <c r="G241" s="66">
-        <v>1978340366.64</v>
+        <v>1978309730.68</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>1303.866195</v>
+        <v>1303.855600</v>
       </c>
       <c r="E242" s="66">
         <v>1467447.00</v>
@@ -6733,12 +6733,12 @@
         <v>1</v>
       </c>
       <c r="G242" s="66">
-        <v>1913354536.00</v>
+        <v>1913338988.52</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>27000.729074</v>
+        <v>27002.146809</v>
       </c>
       <c r="E243" s="66">
         <v>40026.00</v>
@@ -6760,7 +6760,7 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1080731181.92</v>
+        <v>1080787928.18</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.860434</v>
+        <v>7724.862164</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915788562.22</v>
+        <v>1915788991.30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.248129</v>
+        <v>29.251127</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5083956452.09</v>
+        <v>5084477513.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.602396</v>
+        <v>0.598171</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>301197.90</v>
+        <v>299085.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11302.995364</v>
+        <v>11304.158648</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3334541874.24</v>
+        <v>3334885059.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5355.354298</v>
+        <v>5355.359544</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52214704.41</v>
+        <v>52214755.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24466.328517</v>
+        <v>24459.640309</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2023365368.38</v>
+        <v>2022812253.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.515813</v>
+        <v>9968.612413</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72929661.69</v>
+        <v>72930368.41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198792</v>
+        <v>2.198733</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1265096022.83</v>
+        <v>1265062127.87</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.410523</v>
+        <v>1141.404451</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893953863.11</v>
+        <v>893949107.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>365.014778</v>
+        <v>365.629159</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>377425.28</v>
+        <v>378060.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.356023</v>
+        <v>23.357653</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333368985.87</v>
+        <v>2333531877.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.490216</v>
+        <v>24.496366</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2700348949.38</v>
+        <v>2701027009.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340041</v>
+        <v>8.340043</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506762.56</v>
+        <v>94506784.30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.462377</v>
+        <v>7.467063</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>548666604.75</v>
+        <v>549011075.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.815095</v>
+        <v>10.815025</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164665332.74</v>
+        <v>164664269.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>967.894140</v>
+        <v>967.598793</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41665906.93</v>
+        <v>41653192.84</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1224.937338</v>
+        <v>1226.381556</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11638129.65</v>
+        <v>11651851.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.647834</v>
+        <v>13.648431</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569401806.80</v>
+        <v>1569470476.72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999394</v>
+        <v>0.999339</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99939.39</v>
+        <v>99933.91</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1013.305815</v>
+        <v>1013.765836</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20266116.29</v>
+        <v>20275316.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.562202</v>
+        <v>724.554395</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004952186.09</v>
+        <v>3004919806.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.449178</v>
+        <v>1124.441263</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723557589.43</v>
+        <v>2723538419.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999394</v>
+        <v>0.999339</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99939.39</v>
+        <v>99933.91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.650551</v>
+        <v>1.651439</v>
       </c>
       <c r="E27" s="66">
         <v>292286905.00</v>
@@ -928,12 +928,12 @@
         <v>18</v>
       </c>
       <c r="G27" s="66">
-        <v>482434396.45</v>
+        <v>482693997.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>899.610862</v>
+        <v>894.857672</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4497154.70</v>
+        <v>4473393.50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1165.843841</v>
+        <v>1166.476591</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>58292192.05</v>
+        <v>58323829.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809471</v>
+        <v>1.809541</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361894118.29</v>
+        <v>361908206.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1366.286835</v>
+        <v>1367.495535</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5465147.34</v>
+        <v>5469982.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7322.123477</v>
+        <v>7322.005050</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533672969.62</v>
+        <v>533664338.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.922642</v>
+        <v>6974.816376</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173208253.98</v>
+        <v>173205615.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20487.031559</v>
+        <v>20487.360236</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>333283029.40</v>
+        <v>333288376.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1157.477318</v>
+        <v>1160.019220</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5787386.59</v>
+        <v>5800096.10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1156.477318</v>
+        <v>1159.019220</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5782386.59</v>
+        <v>5795096.10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1036.567009</v>
+        <v>1038.799946</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26017831.92</v>
+        <v>26073878.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694887</v>
+        <v>1.694856</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231641639.38</v>
+        <v>231637439.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1223.786812</v>
+        <v>1225.192748</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>326218731.43</v>
+        <v>326593504.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3687.278062</v>
+        <v>3687.412079</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>752204724.69</v>
+        <v>752232064.12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3610.053203</v>
+        <v>3587.039996</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>253295772.94</v>
+        <v>251681074.25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6858.177737</v>
+        <v>6805.130963</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>192135559.57</v>
+        <v>190649425.51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110081</v>
+        <v>0.110066</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34767535.54</v>
+        <v>34763002.35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947066</v>
+        <v>1.947180</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242645627.08</v>
+        <v>242659730.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.605009</v>
+        <v>5.605032</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59440445.36</v>
+        <v>59440694.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465212</v>
+        <v>0.465225</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652035072.01</v>
+        <v>1652080675.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008870</v>
+        <v>0.008895</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>603409912.19</v>
+        <v>605152377.40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.127817</v>
+        <v>0.127567</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>183901.47</v>
+        <v>183542.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.443370</v>
+        <v>0.443600</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>606522.19</v>
+        <v>606836.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1773.014709</v>
+        <v>1773.476532</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>508768343.75</v>
+        <v>508900864.35</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16912.112169</v>
+        <v>16913.786183</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370324520.16</v>
+        <v>370361176.04</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.281821</v>
+        <v>1.282853</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12834870.90</v>
+        <v>12845210.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7526.567511</v>
+        <v>7525.852438</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44549753.10</v>
+        <v>44545520.58</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.326962</v>
+        <v>7.328834</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>241966932.68</v>
+        <v>242028766.72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.091796</v>
+        <v>0.080729</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>103750.76</v>
+        <v>91242.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.359054</v>
+        <v>6.364767</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109580910.46</v>
+        <v>109679349.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990292</v>
+        <v>0.990312</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59417524.26</v>
+        <v>59418701.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591116</v>
+        <v>1.591085</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137645062.26</v>
+        <v>137642379.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.623220</v>
+        <v>8.623033</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344928812.70</v>
+        <v>344921334.82</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.696508</v>
+        <v>0.695100</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>696507.64</v>
+        <v>695099.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.873006</v>
+        <v>0.871740</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>754221.32</v>
+        <v>753127.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.245204</v>
+        <v>2.245043</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170677838.91</v>
+        <v>170665599.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.711643</v>
+        <v>5.712056</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1622993759.87</v>
+        <v>1623111191.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.364112</v>
+        <v>1.365456</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2690884325.62</v>
+        <v>2693535828.33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296334</v>
+        <v>1.296314</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744742035.11</v>
+        <v>1744714491.54</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975078</v>
+        <v>0.975176</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153574706.90</v>
+        <v>153590179.18</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>5.975611</v>
+        <v>5.976957</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6559383721.83</v>
+        <v>6560861102.54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1519.039131</v>
+        <v>1514.913175</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1373644300.91</v>
+        <v>1369913260.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.173660</v>
+        <v>6.173537</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613709130.18</v>
+        <v>2613656848.04</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.091657</v>
+        <v>4.092889</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2592310249.71</v>
+        <v>2593090677.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.757945</v>
+        <v>6.763634</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>318162782.52</v>
+        <v>318430634.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792147</v>
+        <v>1.792692</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444714304.18</v>
+        <v>444849713.31</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.453088</v>
+        <v>18.450373</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20258630.12</v>
+        <v>20255649.57</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.152712</v>
+        <v>3.154563</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>552596631.88</v>
+        <v>552921233.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,21 +2215,21 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.590185</v>
+        <v>14.591866</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
       </c>
       <c r="F75" s="65">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6452591042.30</v>
+        <v>6453334315.53</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.593194</v>
+        <v>6.594171</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2910778536.06</v>
+        <v>2911209796.60</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1362.001050</v>
+        <v>1361.993378</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393091209.17</v>
+        <v>393088994.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232753</v>
+        <v>5.232708</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355943369.90</v>
+        <v>355940308.65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>441.142200</v>
+        <v>440.811100</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>44114.22</v>
+        <v>44081.11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7095.165000</v>
+        <v>7091.665000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70951.65</v>
+        <v>70916.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>183.870900</v>
+        <v>183.558300</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18387.09</v>
+        <v>18355.83</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.547521</v>
+        <v>46.582835</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1633305.95</v>
+        <v>1634545.10</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1214.727995</v>
+        <v>1216.577084</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>112969703.58</v>
+        <v>113141668.84</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.024880</v>
+        <v>21.024507</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671579953.45</v>
+        <v>1671550272.96</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.437516</v>
+        <v>31.435516</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978912673.89</v>
+        <v>978850391.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.526748</v>
+        <v>46.562083</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1632577.06</v>
+        <v>1633816.93</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.082219</v>
+        <v>1.083623</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>611453792.65</v>
+        <v>612246905.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.640556</v>
+        <v>20.664036</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>207618876.43</v>
+        <v>207855049.62</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.738810</v>
+        <v>19.740835</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3077477824.47</v>
+        <v>3077793659.95</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014540</v>
+        <v>0.014435</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8007.21</v>
+        <v>7949.08</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5676.461724</v>
+        <v>5677.173895</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5431238577.06</v>
+        <v>5431919982.56</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.330614</v>
+        <v>1.331649</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>216777105.91</v>
+        <v>216945726.64</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778946</v>
+        <v>0.778951</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135931626.92</v>
+        <v>135932475.59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.595867</v>
+        <v>30.595286</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1549705661.76</v>
+        <v>1549676208.96</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094483</v>
+        <v>1.094275</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55480475.66</v>
+        <v>55469921.03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208871</v>
+        <v>1.208857</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298591196.08</v>
+        <v>298587718.87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599346</v>
+        <v>0.599280</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70326202.85</v>
+        <v>70318419.85</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.516977</v>
+        <v>52.513791</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39005304.05</v>
+        <v>39002937.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.947407</v>
+        <v>19.946983</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109603899.64</v>
+        <v>109601569.41</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1013.873124</v>
+        <v>1014.362437</v>
       </c>
       <c r="E100" s="66">
         <v>22861.00</v>
@@ -2899,12 +2899,12 @@
         <v>2</v>
       </c>
       <c r="G100" s="66">
-        <v>23178153.49</v>
+        <v>23189339.68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.580834</v>
+        <v>0.611135</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1219750.44</v>
+        <v>1283383.06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841330764.81</v>
+        <v>1841344643.34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.940807</v>
+        <v>4.945798</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66224720.24</v>
+        <v>66291616.56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.945097</v>
+        <v>13.944909</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174641965.83</v>
+        <v>174639606.47</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.367109</v>
+        <v>9.366747</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78539651.08</v>
+        <v>78536616.90</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.407282</v>
+        <v>14.407101</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933574264.02</v>
+        <v>933562501.87</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808807</v>
+        <v>8.808794</v>
       </c>
       <c r="E107" s="66">
-        <v>78003587.00</v>
+        <v>79280717.00</v>
       </c>
       <c r="F107" s="65">
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>687118565.95</v>
+        <v>698367529.47</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.933853</v>
+        <v>8.936099</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2908652966.48</v>
+        <v>2909384377.68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.804596</v>
+        <v>29.809333</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661758030.63</v>
+        <v>661863215.17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.774195</v>
+        <v>2.777099</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>293856263.08</v>
+        <v>294163896.53</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.340897</v>
+        <v>48.352081</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1838105381.50</v>
+        <v>1838530643.12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.611155</v>
+        <v>11.610939</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147425276.26</v>
+        <v>147422530.52</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.903442</v>
+        <v>4.903342</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876889144.69</v>
+        <v>876871348.54</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.361867</v>
+        <v>39.381506</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40651125.89</v>
+        <v>40671407.89</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>145.375280</v>
+        <v>145.384582</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>558677.20</v>
+        <v>558712.95</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.136465</v>
+        <v>34.132964</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102409396.21</v>
+        <v>102398892.86</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002299</v>
+        <v>0.002301</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>260111721.86</v>
+        <v>260381121.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956014</v>
+        <v>31.956055</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355110692.84</v>
+        <v>355111151.57</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>400.377209</v>
+        <v>400.518308</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300071507.25</v>
+        <v>300177257.49</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.379244</v>
+        <v>2.382241</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>490769239.08</v>
+        <v>491387612.89</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912485</v>
+        <v>0.912439</v>
       </c>
       <c r="E121" s="66">
-        <v>229647810.00</v>
+        <v>246086436.00</v>
       </c>
       <c r="F121" s="65">
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>209550182.77</v>
+        <v>224538881.29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.500248</v>
+        <v>1.500177</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55066492.12</v>
+        <v>55063920.62</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.023477</v>
+        <v>27.024242</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391393497.19</v>
+        <v>391404578.48</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027946</v>
+        <v>2.027941</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59053631.11</v>
+        <v>59053481.77</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.685175</v>
+        <v>21.707975</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119488480.54</v>
+        <v>119614113.15</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.662627</v>
+        <v>7.662286</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178547742.83</v>
+        <v>178539798.65</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.024101</v>
+        <v>5.023920</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214476234.69</v>
+        <v>214468495.41</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723412</v>
+        <v>2.723356</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368700168.99</v>
+        <v>368692633.76</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.843725</v>
+        <v>23.844153</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451246915.11</v>
+        <v>451255004.61</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.411133</v>
+        <v>5.410651</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44222412.06</v>
+        <v>44218478.96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348184</v>
+        <v>1.348197</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020984319.97</v>
+        <v>1020993751.28</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949756</v>
+        <v>0.949696</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87024628.59</v>
+        <v>87019064.81</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.221925</v>
+        <v>12.224312</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172093865.71</v>
+        <v>172127483.89</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.216325</v>
+        <v>2.216815</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157808773.58</v>
+        <v>157843641.55</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.418984</v>
+        <v>13.425272</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101406308.30</v>
+        <v>101453831.07</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.096593</v>
+        <v>94.091903</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24294799.33</v>
+        <v>24293588.50</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.659098</v>
+        <v>4.659544</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425333784.25</v>
+        <v>425374505.90</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.439006</v>
+        <v>18.440445</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>442904916.65</v>
+        <v>442939496.66</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27607.579230</v>
+        <v>27607.222812</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125172764.23</v>
+        <v>125171148.23</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4852.862985</v>
+        <v>4854.433810</v>
       </c>
       <c r="E141" s="66">
         <v>874610.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>4244362495.14</v>
+        <v>4245736354.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.206652</v>
+        <v>0.204551</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>206651.50</v>
+        <v>204551.39</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.385771</v>
+        <v>1.386189</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149886612.62</v>
+        <v>149931810.70</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.918397</v>
+        <v>15.918575</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156440636.17</v>
+        <v>1156453583.67</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.094734</v>
+        <v>16.095101</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5746004525.63</v>
+        <v>5746135601.68</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3292.831775</v>
+        <v>3292.935788</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193661315.18</v>
+        <v>193667432.51</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c t="n" r="D147">
-        <v>0.977860</v>
+        <v>0.977861</v>
       </c>
       <c r="E147" s="66">
         <v>431000000.00</v>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421457680.06</v>
+        <v>421458031.64</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.313409</v>
+        <v>1.314981</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>525885393.48</v>
+        <v>526514862.33</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.036209</v>
+        <v>1.036175</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13508766679.42</v>
+        <v>13508329107.96</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.922083</v>
+        <v>0.922028</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13643020437.81</v>
+        <v>13642193774.96</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1930.443949</v>
+        <v>1930.447440</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41094804.32</v>
+        <v>41094878.64</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.583883</v>
+        <v>1.584834</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60931191.72</v>
+        <v>60967796.57</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6765.147450</v>
+        <v>6765.037829</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964371768.95</v>
+        <v>964356142.58</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.284575</v>
+        <v>1926.189718</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337748958.58</v>
+        <v>337732326.61</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17335.316794</v>
+        <v>17335.300068</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504346540.59</v>
+        <v>2504344124.37</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20304.312953</v>
+        <v>20305.096071</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185053508.25</v>
+        <v>185060645.59</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15349.510184</v>
+        <v>15349.640443</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320344277.53</v>
+        <v>320346996.04</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1158.493324</v>
+        <v>1159.823589</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5897889.51</v>
+        <v>5904661.89</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.206727</v>
+        <v>3675.284904</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719057871.29</v>
+        <v>719073166.73</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200851.246707</v>
+        <v>200851.133698</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602104615.80</v>
+        <v>4602102026.42</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.436658</v>
+        <v>33.449572</v>
       </c>
       <c r="E162" s="66">
         <v>16759003.00</v>
@@ -4573,12 +4573,12 @@
         <v>25</v>
       </c>
       <c r="G162" s="66">
-        <v>560365052.02</v>
+        <v>560581472.47</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.459663</v>
+        <v>80.441135</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396298196.48</v>
+        <v>396206938.35</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400432</v>
+        <v>1.400495</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154372093.55</v>
+        <v>154379036.73</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.389389</v>
+        <v>2579.436612</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438498775.57</v>
+        <v>438506803.40</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731288</v>
+        <v>1678.731291</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092783.83</v>
+        <v>927092785.08</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027180</v>
+        <v>1.027169</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970677507.49</v>
+        <v>970667307.00</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1047.496778</v>
+        <v>1047.455115</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114509205.23</v>
+        <v>114504650.79</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.839843</v>
+        <v>75.851873</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65878962.14</v>
+        <v>65889412.47</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188115</v>
+        <v>3.188106</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977100055.98</v>
+        <v>977097219.72</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2979.778477</v>
+        <v>2979.952427</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2194234375.76</v>
+        <v>2194362468.50</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4304.496351</v>
+        <v>4331.788700</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19111963.80</v>
+        <v>19233141.83</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63328.093002</v>
+        <v>63327.042854</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174926109.46</v>
+        <v>1174906626.07</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.615931</v>
+        <v>8193.542339</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148984518.47</v>
+        <v>148983180.35</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>45485.960698</v>
+        <v>46184.443425</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>2977647445.20</v>
+        <v>3023372219.91</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11591.415907</v>
+        <v>11591.278068</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675646533.92</v>
+        <v>2675614716.43</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2491.138569</v>
+        <v>2488.908362</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>93056481.25</v>
+        <v>92973171.87</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.683364</v>
+        <v>2705.529476</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459663135.29</v>
+        <v>459636991.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3497.302617</v>
+        <v>3496.724005</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20763485.64</v>
+        <v>20760050.42</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3287.031831</v>
+        <v>3286.993115</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6834784452.40</v>
+        <v>6834703949.46</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994795</v>
+        <v>0.994769</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928536207.10</v>
+        <v>928512203.29</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4661.162503</v>
+        <v>4661.117807</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70262363.57</v>
+        <v>70261689.83</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.179391</v>
+        <v>1.179839</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2386321.16</v>
+        <v>2387228.64</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.720059</v>
+        <v>3592.717504</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917246580.15</v>
+        <v>917245927.78</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211579</v>
+        <v>1.211550</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226647104.29</v>
+        <v>226641655.92</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.124883</v>
+        <v>1331.170781</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502511623.64</v>
+        <v>502528950.47</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.381653</v>
+        <v>1109.330544</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721214508.92</v>
+        <v>1721135213.13</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.938987</v>
+        <v>74.938539</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872889174.72</v>
+        <v>872883947.35</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.252170</v>
+        <v>10.223493</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>454280204.64</v>
+        <v>453009467.32</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,21 +5320,21 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.207589</v>
+        <v>14.207046</v>
       </c>
       <c r="E190" s="66">
-        <v>159085884.00</v>
+        <v>145515811.00</v>
       </c>
       <c r="F190" s="65">
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2260226855.57</v>
+        <v>2067349864.89</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7624.078138</v>
+        <v>7570.376000</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>285582718.88</v>
+        <v>283571144.19</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.916657</v>
+        <v>1.916558</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26234042.22</v>
+        <v>26232686.87</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441904</v>
+        <v>2.441838</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206123682.22</v>
+        <v>206118129.37</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.436124</v>
+        <v>44.330301</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>565846934.57</v>
+        <v>564499387.12</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14893.342464</v>
+        <v>14893.906311</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6207843005.68</v>
+        <v>6208078028.40</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6273.660710</v>
+        <v>6274.111915</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39775008.90</v>
+        <v>39777869.54</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.337373</v>
+        <v>2933.354733</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077540950.65</v>
+        <v>1077547327.63</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223974</v>
+        <v>1.223961</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523039492.33</v>
+        <v>523033834.38</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323408</v>
+        <v>1.323456</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121753536.28</v>
+        <v>121757965.65</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.347874</v>
+        <v>7.354572</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2804243247.23</v>
+        <v>2806799535.09</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>998.199202</v>
+        <v>998.179832</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>448011766.06</v>
+        <v>448003072.08</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2504.141704</v>
+        <v>2507.317130</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,214 +5707,214 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>513679596.05</v>
+        <v>514330977.41</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
-          <t xml:space="preserve">TUG</t>
+          <t xml:space="preserve">TN1</t>
         </is>
       </c>
       <c t="inlineStr" r="C205">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D205">
-        <v>0.004372</v>
+        <v>1.000000</v>
       </c>
       <c r="E205" s="66">
-        <v>67618383967.00</v>
+        <v>300000.00</v>
       </c>
       <c r="F205" s="65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G205" s="66">
-        <v>295633729.81</v>
+        <v>300000.00</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
-          <t xml:space="preserve">UCG</t>
+          <t xml:space="preserve">TUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C206">
         <is>
-          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D206">
-        <v>20.816852</v>
+        <v>0.004374</v>
       </c>
       <c r="E206" s="66">
-        <v>81092133.00</v>
+        <v>67618383967.00</v>
       </c>
       <c r="F206" s="65">
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>1688082938.69</v>
+        <v>295778185.03</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
-          <t xml:space="preserve">UG2</t>
+          <t xml:space="preserve">UCG</t>
         </is>
       </c>
       <c t="inlineStr" r="C207">
         <is>
-          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">RE-PIE PORTFÖY YÖNETİMİ A.Ş. SAMPAŞ HOLDİNG ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D207">
-        <v>3.358587</v>
+        <v>20.819557</v>
       </c>
       <c r="E207" s="66">
-        <v>21323550.00</v>
+        <v>81092133.00</v>
       </c>
       <c r="F207" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>71616994.37</v>
+        <v>1688302309.61</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
-          <t xml:space="preserve">UKA</t>
+          <t xml:space="preserve">UG2</t>
         </is>
       </c>
       <c t="inlineStr" r="C208">
         <is>
-          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ÜNLÜ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D208">
-        <v>7692.953742</v>
+        <v>3.358655</v>
       </c>
       <c r="E208" s="66">
-        <v>197052.47</v>
+        <v>21323550.00</v>
       </c>
       <c r="F208" s="65">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>1515915567.26</v>
+        <v>71618456.76</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
-          <t xml:space="preserve">UNC</t>
+          <t xml:space="preserve">UKA</t>
         </is>
       </c>
       <c t="inlineStr" r="C209">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">TERA PORTFÖY YÖNETİMİ A.Ş. KONUT ALFA KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D209">
-        <v>1.844818</v>
+        <v>7699.654675</v>
       </c>
       <c r="E209" s="66">
-        <v>601179729.00</v>
+        <v>197052.47</v>
       </c>
       <c r="F209" s="65">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G209" s="66">
-        <v>1109066944.18</v>
+        <v>1517236002.63</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
-          <t xml:space="preserve">UUG</t>
+          <t xml:space="preserve">UNC</t>
         </is>
       </c>
       <c t="inlineStr" r="C210">
         <is>
-          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D210">
-        <v>25.012812</v>
+        <v>1.844790</v>
       </c>
       <c r="E210" s="66">
-        <v>377.00</v>
+        <v>601179729.00</v>
       </c>
       <c r="F210" s="65">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>9429.83</v>
+        <v>1109050235.28</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
-          <t xml:space="preserve">VBI</t>
+          <t xml:space="preserve">UUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C211">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">PARDUS PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D211">
-        <v>1.743416</v>
+        <v>24.168382</v>
       </c>
       <c r="E211" s="66">
-        <v>100000.00</v>
+        <v>377.00</v>
       </c>
       <c r="F211" s="65">
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>174341.56</v>
+        <v>9111.48</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
-          <t xml:space="preserve">VIK</t>
+          <t xml:space="preserve">VBI</t>
         </is>
       </c>
       <c t="inlineStr" r="C212">
         <is>
-          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.743574</v>
+        <v>1.746060</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,844 +5923,871 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>174357.39</v>
+        <v>174605.98</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
-          <t xml:space="preserve">VMG</t>
+          <t xml:space="preserve">VIK</t>
         </is>
       </c>
       <c t="inlineStr" r="C213">
         <is>
-          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">WAM GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. İKİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D213">
-        <v>61.326071</v>
+        <v>1.746218</v>
       </c>
       <c r="E213" s="66">
-        <v>2554914.00</v>
+        <v>100000.00</v>
       </c>
       <c r="F213" s="65">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>156682837.00</v>
+        <v>174621.81</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
-          <t xml:space="preserve">VVF</t>
+          <t xml:space="preserve">VMG</t>
         </is>
       </c>
       <c t="inlineStr" r="C214">
         <is>
-          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İSTANBUL PORTFÖY YÖNETİMİ A.Ş. VERA MEKAN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D214">
-        <v>15.235480</v>
+        <v>61.321202</v>
       </c>
       <c r="E214" s="66">
-        <v>248000220.00</v>
+        <v>2554914.00</v>
       </c>
       <c r="F214" s="65">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>3778402291.08</v>
+        <v>156670398.10</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
-          <t xml:space="preserve">YAL</t>
+          <t xml:space="preserve">VVF</t>
         </is>
       </c>
       <c t="inlineStr" r="C215">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">NEO PORTFÖY YÖNETİMİ A.Ş. BİRİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D215">
-        <v>1.801144</v>
+        <v>15.238457</v>
       </c>
       <c r="E215" s="66">
-        <v>437816172.00</v>
+        <v>248000220.00</v>
       </c>
       <c r="F215" s="65">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>788570166.45</v>
+        <v>3779140587.65</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
-          <t xml:space="preserve">YD1</t>
+          <t xml:space="preserve">YAL</t>
         </is>
       </c>
       <c t="inlineStr" r="C216">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YALÇINLAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D216">
-        <v>0.390020</v>
+        <v>1.801150</v>
       </c>
       <c r="E216" s="66">
-        <v>402507.00</v>
+        <v>437816172.00</v>
       </c>
       <c r="F216" s="65">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G216" s="66">
-        <v>156985.90</v>
+        <v>788572593.23</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
-          <t xml:space="preserve">YD2</t>
+          <t xml:space="preserve">YD1</t>
         </is>
       </c>
       <c t="inlineStr" r="C217">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALTIN BAŞAK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D217">
-        <v>9.879779</v>
+        <v>0.391971</v>
       </c>
       <c r="E217" s="66">
-        <v>27178800.00</v>
+        <v>402507.00</v>
       </c>
       <c r="F217" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>268520544.72</v>
+        <v>157771.14</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
-          <t xml:space="preserve">YD3</t>
+          <t xml:space="preserve">YD2</t>
         </is>
       </c>
       <c t="inlineStr" r="C218">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ALZAMİL KİRA GETİRİLİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D218">
-        <v>15.618291</v>
+        <v>9.879188</v>
       </c>
       <c r="E218" s="66">
-        <v>10371838.00</v>
+        <v>27178800.00</v>
       </c>
       <c r="F218" s="65">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>161990379.16</v>
+        <v>268504486.48</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
-          <t xml:space="preserve">YD4</t>
+          <t xml:space="preserve">YD3</t>
         </is>
       </c>
       <c t="inlineStr" r="C219">
         <is>
-          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. PRİMO GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.327663</v>
+        <v>15.617378</v>
       </c>
       <c r="E219" s="66">
-        <v>19475841.00</v>
+        <v>10371838.00</v>
       </c>
       <c r="F219" s="65">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>298519126.36</v>
+        <v>161980914.56</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
-          <t xml:space="preserve">YD5</t>
+          <t xml:space="preserve">YD4</t>
         </is>
       </c>
       <c t="inlineStr" r="C220">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRIMENKUL VE GIRISIM SERMAYESI PORTFÖY YÖNETIMI A.S. PORTAKAL ÇIÇEGI GAYRIMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D220">
-        <v>31.090819</v>
+        <v>15.326912</v>
       </c>
       <c r="E220" s="66">
-        <v>9712281.00</v>
+        <v>19475841.00</v>
       </c>
       <c r="F220" s="65">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>301962772.99</v>
+        <v>298504505.14</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
-          <t xml:space="preserve">YD7</t>
+          <t xml:space="preserve">YD5</t>
         </is>
       </c>
       <c t="inlineStr" r="C221">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.  A1 GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D221">
-        <v>7.980117</v>
+        <v>31.088482</v>
       </c>
       <c r="E221" s="66">
-        <v>12818249.00</v>
+        <v>9712281.00</v>
       </c>
       <c r="F221" s="65">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>102291127.53</v>
+        <v>301940077.77</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
-          <t xml:space="preserve">YE3</t>
+          <t xml:space="preserve">YD7</t>
         </is>
       </c>
       <c t="inlineStr" r="C222">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş.KARDELEN GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D222">
-        <v>1659.780672</v>
+        <v>7.979517</v>
       </c>
       <c r="E222" s="66">
-        <v>330000.00</v>
+        <v>12818249.00</v>
       </c>
       <c r="F222" s="65">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>547727621.72</v>
+        <v>102283437.69</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
-          <t xml:space="preserve">YE6</t>
+          <t xml:space="preserve">YE3</t>
         </is>
       </c>
       <c t="inlineStr" r="C223">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AKASYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D223">
-        <v>5.169780</v>
+        <v>1659.774619</v>
       </c>
       <c r="E223" s="66">
-        <v>11867933.00</v>
+        <v>330000.00</v>
       </c>
       <c r="F223" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>61354606.75</v>
+        <v>547725624.32</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
-          <t xml:space="preserve">YGG</t>
+          <t xml:space="preserve">YE6</t>
         </is>
       </c>
       <c t="inlineStr" r="C224">
         <is>
-          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş NİLÜFER GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D224">
-        <v>0.946583</v>
+        <v>5.169625</v>
       </c>
       <c r="E224" s="66">
-        <v>130000000.00</v>
+        <v>11867933.00</v>
       </c>
       <c r="F224" s="65">
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>123055763.27</v>
+        <v>61352759.37</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
-          <t xml:space="preserve">YG1</t>
+          <t xml:space="preserve">YGG</t>
         </is>
       </c>
       <c t="inlineStr" r="C225">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ARGEUS GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D225">
-        <v>5.519549</v>
+        <v>0.946612</v>
       </c>
       <c r="E225" s="66">
-        <v>103852814.00</v>
+        <v>130000000.00</v>
       </c>
       <c r="F225" s="65">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>573220645.30</v>
+        <v>123059601.68</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
-          <t xml:space="preserve">YG2</t>
+          <t xml:space="preserve">YG1</t>
         </is>
       </c>
       <c t="inlineStr" r="C226">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LOTUS GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D226">
-        <v>0.000007</v>
+        <v>5.519542</v>
       </c>
       <c r="E226" s="66">
-        <v>869111122.00</v>
+        <v>103852814.00</v>
       </c>
       <c r="F226" s="65">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>6077.76</v>
+        <v>573219928.77</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
-          <t xml:space="preserve">YG3</t>
+          <t xml:space="preserve">YG2</t>
         </is>
       </c>
       <c t="inlineStr" r="C227">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. AYÇİÇEĞİ PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D227">
-        <v>6.606520</v>
+        <v>0.000007</v>
       </c>
       <c r="E227" s="66">
-        <v>11104667.00</v>
+        <v>869111122.00</v>
       </c>
       <c r="F227" s="65">
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>73363208.35</v>
+        <v>6078.75</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
-          <t xml:space="preserve">YG5</t>
+          <t xml:space="preserve">YG3</t>
         </is>
       </c>
       <c t="inlineStr" r="C228">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ERGUVAN PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D228">
-        <v>26.523143</v>
+        <v>6.606033</v>
       </c>
       <c r="E228" s="66">
-        <v>1038884.00</v>
+        <v>11104667.00</v>
       </c>
       <c r="F228" s="65">
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>27554468.47</v>
+        <v>73357795.34</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
-          <t xml:space="preserve">YG6</t>
+          <t xml:space="preserve">YG5</t>
         </is>
       </c>
       <c t="inlineStr" r="C229">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. FULYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D229">
-        <v>0.850547</v>
+        <v>26.519621</v>
       </c>
       <c r="E229" s="66">
-        <v>73432275.00</v>
+        <v>1038884.00</v>
       </c>
       <c r="F229" s="65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>62457631.03</v>
+        <v>27550809.60</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
-          <t xml:space="preserve">YG7</t>
+          <t xml:space="preserve">YG6</t>
         </is>
       </c>
       <c t="inlineStr" r="C230">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MANOLYA GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.711658</v>
+        <v>0.850445</v>
       </c>
       <c r="E230" s="66">
-        <v>801655137.00</v>
+        <v>73432275.00</v>
       </c>
       <c r="F230" s="65">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>570504608.65</v>
+        <v>62450114.65</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
-          <t xml:space="preserve">YG8</t>
+          <t xml:space="preserve">YG7</t>
         </is>
       </c>
       <c t="inlineStr" r="C231">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. MENEKŞE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D231">
-        <v>11.956876</v>
+        <v>0.711564</v>
       </c>
       <c r="E231" s="66">
-        <v>26235742.00</v>
+        <v>801655137.00</v>
       </c>
       <c r="F231" s="65">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>313697520.53</v>
+        <v>570428671.30</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
-          <t xml:space="preserve">YOR</t>
+          <t xml:space="preserve">YG8</t>
         </is>
       </c>
       <c t="inlineStr" r="C232">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LALE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D232">
-        <v>0.004710</v>
+        <v>11.956817</v>
       </c>
       <c r="E232" s="66">
-        <v>100000.00</v>
+        <v>26235742.00</v>
       </c>
       <c r="F232" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>471.02</v>
+        <v>313695963.45</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
-          <t xml:space="preserve">YYF</t>
+          <t xml:space="preserve">YOR</t>
         </is>
       </c>
       <c t="inlineStr" r="C233">
         <is>
-          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ORKİDE PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D233">
-        <v>1.550113</v>
+        <v>0.004716</v>
       </c>
       <c r="E233" s="66">
-        <v>24022001.00</v>
+        <v>100000.00</v>
       </c>
       <c r="F233" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>37236827.25</v>
+        <v>471.55</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
-          <t xml:space="preserve">YZA</t>
+          <t xml:space="preserve">YYF</t>
         </is>
       </c>
       <c t="inlineStr" r="C234">
         <is>
-          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">İŞ PORTFÖY YÖNETİMİ A.Ş. YEDİNCİ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D234">
-        <v>2.572198</v>
+        <v>1.552115</v>
       </c>
       <c r="E234" s="66">
-        <v>68085562.00</v>
+        <v>24022001.00</v>
       </c>
       <c r="F234" s="65">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>175129537.95</v>
+        <v>37284917.59</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
-          <t xml:space="preserve">ZEP</t>
+          <t xml:space="preserve">YZA</t>
         </is>
       </c>
       <c t="inlineStr" r="C235">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">24 GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. ZAMBAK PROJE GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D235">
-        <v>1056.755737</v>
+        <v>2.572212</v>
       </c>
       <c r="E235" s="66">
-        <v>20029.00</v>
+        <v>68085562.00</v>
       </c>
       <c r="F235" s="65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>21165760.66</v>
+        <v>175130521.92</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
-          <t xml:space="preserve">ZGG</t>
+          <t xml:space="preserve">ZEP</t>
         </is>
       </c>
       <c t="inlineStr" r="C236">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. EMLAK KONUT GELİR PAYLAŞIMI BİRİNCİ KATILIM GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D236">
-        <v>3.245111</v>
+        <v>1057.815397</v>
       </c>
       <c r="E236" s="66">
-        <v>1427155857.00</v>
+        <v>20029.00</v>
       </c>
       <c r="F236" s="65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>4631279712.84</v>
+        <v>21186984.59</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
-          <t xml:space="preserve">ZGU</t>
+          <t xml:space="preserve">ZGG</t>
         </is>
       </c>
       <c t="inlineStr" r="C237">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BGF KATILIM ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D237">
-        <v>1689.526217</v>
+        <v>3.245629</v>
       </c>
       <c r="E237" s="66">
-        <v>97333.00</v>
+        <v>1427155857.00</v>
       </c>
       <c r="F237" s="65">
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>164446655.29</v>
+        <v>4632018708.40</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
-          <t xml:space="preserve">ZG6</t>
+          <t xml:space="preserve">ZGU</t>
         </is>
       </c>
       <c t="inlineStr" r="C238">
         <is>
-          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÖZGÜN ÖZEL GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1.161269</v>
+        <v>1690.015253</v>
       </c>
       <c r="E238" s="66">
-        <v>1103857956.00</v>
+        <v>97333.00</v>
       </c>
       <c r="F238" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>1281876212.41</v>
+        <v>164494254.58</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
-          <t xml:space="preserve">ZPV</t>
+          <t xml:space="preserve">ZG6</t>
         </is>
       </c>
       <c t="inlineStr" r="C239">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
+          <t xml:space="preserve">ARZ GAYRİMENKUL VE GİRİŞİM SERMAYESİ PORTFÖY YÖNETİMİ A.Ş. LEVENT GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D239">
-        <v>2.247800</v>
+        <v>1.161237</v>
       </c>
       <c r="E239" s="66">
-        <v>296754544.00</v>
+        <v>1103857956.00</v>
       </c>
       <c r="F239" s="65">
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>667045003.48</v>
+        <v>1281840319.55</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
-          <t xml:space="preserve">ZUC</t>
+          <t xml:space="preserve">ZPV</t>
         </is>
       </c>
       <c t="inlineStr" r="C240">
         <is>
-          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. BAŞAK KATILIM GAYRİMENKUL YATIRIM (TL) FONU</t>
         </is>
       </c>
       <c t="n" r="D240">
-        <v>1003.943815</v>
+        <v>2.251292</v>
       </c>
       <c r="E240" s="66">
-        <v>1431712.00</v>
+        <v>296754544.00</v>
       </c>
       <c r="F240" s="65">
-        <v>260</v>
+        <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>1437358407.53</v>
+        <v>668081105.15</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
-          <t xml:space="preserve">ZUG</t>
+          <t xml:space="preserve">ZUC</t>
         </is>
       </c>
       <c t="inlineStr" r="C241">
         <is>
-          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">AZİMUT PORTFÖY YÖNETİMİ A.Ş. ÜÇÜNCÜ GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D241">
-        <v>5.001632</v>
+        <v>1005.025858</v>
       </c>
       <c r="E241" s="66">
-        <v>395532870.00</v>
+        <v>1431712.00</v>
       </c>
       <c r="F241" s="65">
-        <v>5</v>
+        <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1978309730.68</v>
+        <v>1438907581.18</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
-          <t xml:space="preserve">ZVD</t>
+          <t xml:space="preserve">ZUG</t>
         </is>
       </c>
       <c t="inlineStr" r="C242">
         <is>
-          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+          <t xml:space="preserve">ZİRAAT PORTFÖY YÖNETİMİ A.Ş. ÜSKÜDAR GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
       <c t="n" r="D242">
-        <v>1303.855600</v>
+        <v>5.001555</v>
       </c>
       <c r="E242" s="66">
-        <v>1467447.00</v>
+        <v>395532870.00</v>
       </c>
       <c r="F242" s="65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1913338988.52</v>
+        <v>1978279457.70</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
+          <t xml:space="preserve">ZVD</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="C243">
+        <is>
+          <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş.ESTA GAYRİMENKUL YATIRIM FONU</t>
+        </is>
+      </c>
+      <c t="n" r="D243">
+        <v>1303.844324</v>
+      </c>
+      <c r="E243" s="66">
+        <v>1467447.00</v>
+      </c>
+      <c r="F243" s="65">
+        <v>1</v>
+      </c>
+      <c r="G243" s="66">
+        <v>1913322441.31</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="67">
+        <v>46128</v>
+      </c>
+      <c t="inlineStr" r="B244">
+        <is>
           <t xml:space="preserve">ZVE</t>
         </is>
       </c>
-      <c t="inlineStr" r="C243">
+      <c t="inlineStr" r="C244">
         <is>
           <t xml:space="preserve">ATLAS PORTFÖY YÖNETİMİ A.Ş. A&amp;AK GAYRİMENKUL YATIRIM FONU</t>
         </is>
       </c>
-      <c t="n" r="D243">
-        <v>27002.146809</v>
-      </c>
-      <c r="E243" s="66">
+      <c t="n" r="D244">
+        <v>26978.437568</v>
+      </c>
+      <c r="E244" s="66">
         <v>40026.00</v>
       </c>
-      <c r="F243" s="65">
-        <v>1</v>
-      </c>
-      <c r="G243" s="66">
-        <v>1080787928.18</v>
+      <c r="F244" s="65">
+        <v>1</v>
+      </c>
+      <c r="G244" s="66">
+        <v>1079838942.09</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.862164</v>
+        <v>7724.863489</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915788991.30</v>
+        <v>1915789319.88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.251127</v>
+        <v>29.253873</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5084477513.66</v>
+        <v>5084954909.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.598171</v>
+        <v>0.593946</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>299085.38</v>
+        <v>296973.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11304.158648</v>
+        <v>11305.624099</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3334885059.42</v>
+        <v>3335317387.94</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5355.359544</v>
+        <v>5355.632772</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52214755.55</v>
+        <v>52217419.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24459.640309</v>
+        <v>24464.021486</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2022812253.59</v>
+        <v>2023174576.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.612413</v>
+        <v>9968.709146</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72930368.41</v>
+        <v>72931076.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198733</v>
+        <v>2.198674</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1265062127.87</v>
+        <v>1265028101.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.404451</v>
+        <v>1141.414072</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893949107.14</v>
+        <v>893956642.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>365.629159</v>
+        <v>366.264981</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>378060.55</v>
+        <v>378717.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.357653</v>
+        <v>23.358792</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333531877.76</v>
+        <v>2333645624.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.496366</v>
+        <v>24.499382</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701027009.34</v>
+        <v>2701359560.13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340043</v>
+        <v>8.340044</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506784.30</v>
+        <v>94506804.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.467063</v>
+        <v>7.469556</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>549011075.89</v>
+        <v>549194390.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.815025</v>
+        <v>10.814941</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164664269.29</v>
+        <v>164662998.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>967.598793</v>
+        <v>967.326532</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41653192.84</v>
+        <v>41641472.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1226.381556</v>
+        <v>1227.821544</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11651851.16</v>
+        <v>11665532.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.648431</v>
+        <v>13.649078</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569470476.72</v>
+        <v>1569544880.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999339</v>
+        <v>0.999284</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99933.91</v>
+        <v>99928.43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1013.765836</v>
+        <v>1014.278084</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20275316.72</v>
+        <v>20285561.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.554395</v>
+        <v>724.546815</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004919806.64</v>
+        <v>3004888371.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.441263</v>
+        <v>1124.433784</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723538419.63</v>
+        <v>2723520303.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999339</v>
+        <v>0.999284</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99933.91</v>
+        <v>99928.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.651439</v>
+        <v>1.652340</v>
       </c>
       <c r="E27" s="66">
         <v>292286905.00</v>
@@ -928,12 +928,12 @@
         <v>18</v>
       </c>
       <c r="G27" s="66">
-        <v>482693997.84</v>
+        <v>482957246.55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>894.857672</v>
+        <v>890.101200</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4473393.50</v>
+        <v>4449615.90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1166.476591</v>
+        <v>1159.999026</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>58323829.55</v>
+        <v>57999951.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809541</v>
+        <v>1.809643</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361908206.27</v>
+        <v>361928660.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1367.495535</v>
+        <v>1368.710958</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5469982.14</v>
+        <v>5474843.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7322.005050</v>
+        <v>7321.886768</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533664338.08</v>
+        <v>533655717.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.816376</v>
+        <v>6974.799384</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173205615.06</v>
+        <v>173205193.11</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20487.360236</v>
+        <v>20566.766352</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>333288376.32</v>
+        <v>334580155.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1160.019220</v>
+        <v>1161.399232</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5800096.10</v>
+        <v>5806996.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1159.019220</v>
+        <v>1160.399232</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5795096.10</v>
+        <v>5801996.16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1038.799946</v>
+        <v>1038.633817</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26073878.64</v>
+        <v>26069708.81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694856</v>
+        <v>1.694826</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231637439.36</v>
+        <v>231633229.68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1225.192748</v>
+        <v>1226.471991</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>326593504.91</v>
+        <v>326934506.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3687.412079</v>
+        <v>3618.833262</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>752232064.12</v>
+        <v>738241985.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3587.039996</v>
+        <v>3545.043974</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>251681074.25</v>
+        <v>248734465.36</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6805.130963</v>
+        <v>6819.449674</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>190649425.51</v>
+        <v>191050571.93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110066</v>
+        <v>0.110052</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34763002.35</v>
+        <v>34758522.58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947180</v>
+        <v>1.947309</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242659730.81</v>
+        <v>242675910.73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.605032</v>
+        <v>5.605036</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59440694.09</v>
+        <v>59440732.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465225</v>
+        <v>0.465235</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652080675.87</v>
+        <v>1652118284.39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008895</v>
+        <v>0.008910</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>605152377.40</v>
+        <v>606184111.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.127567</v>
+        <v>0.109890</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>183542.61</v>
+        <v>158109.24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.443600</v>
+        <v>0.442771</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>606836.75</v>
+        <v>605703.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1773.476532</v>
+        <v>1773.742495</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>508900864.35</v>
+        <v>508977182.65</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16913.786183</v>
+        <v>16915.524744</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370361176.04</v>
+        <v>370399245.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.282853</v>
+        <v>1.283919</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12845210.77</v>
+        <v>12855880.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7525.852438</v>
+        <v>7525.137390</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44545520.58</v>
+        <v>44541288.21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.328834</v>
+        <v>7.330714</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>242028766.72</v>
+        <v>242090860.74</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.080729</v>
+        <v>0.070544</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>91242.24</v>
+        <v>79731.05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.364767</v>
+        <v>6.370416</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109679349.39</v>
+        <v>109776700.15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990312</v>
+        <v>0.990333</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59418701.08</v>
+        <v>59419991.32</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591085</v>
+        <v>1.591054</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137642379.66</v>
+        <v>137639710.72</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.623033</v>
+        <v>8.622857</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344921334.82</v>
+        <v>344914267.85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.695100</v>
+        <v>0.693691</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>695099.74</v>
+        <v>693690.83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.871740</v>
+        <v>0.870543</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>753127.49</v>
+        <v>752093.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.245043</v>
+        <v>2.244882</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170665599.69</v>
+        <v>170653363.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.712056</v>
+        <v>5.712493</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1623111191.47</v>
+        <v>1623235295.98</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.365456</v>
+        <v>1.350198</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2693535828.33</v>
+        <v>2663438553.48</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296314</v>
+        <v>1.296293</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744714491.54</v>
+        <v>1744686960.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975176</v>
+        <v>0.975274</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153590179.18</v>
+        <v>153605614.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>5.976957</v>
+        <v>6.020957</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6560861102.54</v>
+        <v>6609159714.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1514.913175</v>
+        <v>1515.098951</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1369913260.81</v>
+        <v>1370081254.75</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.173537</v>
+        <v>6.174126</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613656848.04</v>
+        <v>2613906206.76</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.092889</v>
+        <v>4.094403</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2593090677.17</v>
+        <v>2594050103.35</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.763634</v>
+        <v>6.766213</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>318430634.49</v>
+        <v>318552045.97</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792692</v>
+        <v>1.792625</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444849713.31</v>
+        <v>444833070.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.450373</v>
+        <v>18.448378</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20255649.57</v>
+        <v>20253459.11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.154563</v>
+        <v>3.156350</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>552921233.09</v>
+        <v>553234424.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.591866</v>
+        <v>14.593741</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6453334315.53</v>
+        <v>6454163749.40</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.594171</v>
+        <v>6.594536</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2911209796.60</v>
+        <v>2911371075.29</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1361.993378</v>
+        <v>1361.648342</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393088994.87</v>
+        <v>392989412.86</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232708</v>
+        <v>5.232676</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355940308.65</v>
+        <v>355938163.34</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>440.811100</v>
+        <v>440.480100</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>44081.11</v>
+        <v>44048.01</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7091.665000</v>
+        <v>7088.165000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70916.65</v>
+        <v>70881.65</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>183.558300</v>
+        <v>183.245700</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18355.83</v>
+        <v>18324.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.582835</v>
+        <v>46.041141</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1634545.10</v>
+        <v>1615537.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1216.577084</v>
+        <v>1218.543768</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>113141668.84</v>
+        <v>113324570.44</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.024507</v>
+        <v>21.023906</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671550272.96</v>
+        <v>1671502460.82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.435516</v>
+        <v>31.433561</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978850391.62</v>
+        <v>978789493.45</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.562083</v>
+        <v>45.998646</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1633816.93</v>
+        <v>1614046.49</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.083623</v>
+        <v>1.085250</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>612246905.96</v>
+        <v>613166185.91</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.664036</v>
+        <v>20.688432</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>207855049.62</v>
+        <v>208100444.52</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.740835</v>
+        <v>19.743470</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3077793659.95</v>
+        <v>3078204453.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014435</v>
+        <v>0.014556</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>7949.08</v>
+        <v>8015.87</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5677.173895</v>
+        <v>5677.901203</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5431919982.56</v>
+        <v>5432615870.69</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.331649</v>
+        <v>1.332735</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>216945726.64</v>
+        <v>217122707.60</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778951</v>
+        <v>0.778958</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135932475.59</v>
+        <v>135933663.59</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.595286</v>
+        <v>30.634227</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1549676208.96</v>
+        <v>1551648649.10</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094275</v>
+        <v>1.094071</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55469921.03</v>
+        <v>55459585.96</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208857</v>
+        <v>1.208843</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298587718.87</v>
+        <v>298584269.45</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599280</v>
+        <v>0.599220</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70318419.85</v>
+        <v>70311424.14</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.513791</v>
+        <v>52.510604</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39002937.52</v>
+        <v>39000571.06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.946983</v>
+        <v>19.946559</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109601569.41</v>
+        <v>109599239.18</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1014.362437</v>
+        <v>1014.632942</v>
       </c>
       <c r="E100" s="66">
         <v>22861.00</v>
@@ -2899,12 +2899,12 @@
         <v>2</v>
       </c>
       <c r="G100" s="66">
-        <v>23189339.68</v>
+        <v>23195523.68</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.611135</v>
+        <v>0.611702</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1283383.06</v>
+        <v>1284573.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841344643.34</v>
+        <v>1841358601.26</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.945798</v>
+        <v>4.950801</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66291616.56</v>
+        <v>66358674.05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.944909</v>
+        <v>13.944721</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174639606.47</v>
+        <v>174637255.98</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.366747</v>
+        <v>9.366385</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78536616.90</v>
+        <v>78533582.76</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.407101</v>
+        <v>14.406920</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933562501.87</v>
+        <v>933550788.20</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808794</v>
+        <v>8.808758</v>
       </c>
       <c r="E107" s="66">
         <v>79280717.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>698367529.47</v>
+        <v>698364616.51</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.936099</v>
+        <v>8.936566</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2909384377.68</v>
+        <v>2909536488.68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.809333</v>
+        <v>29.811020</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661863215.17</v>
+        <v>661900673.00</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.777099</v>
+        <v>2.779368</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>294163896.53</v>
+        <v>294404214.67</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.352081</v>
+        <v>48.365817</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1838530643.12</v>
+        <v>1839052916.52</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.610939</v>
+        <v>11.610718</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147422530.52</v>
+        <v>147419735.43</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.903342</v>
+        <v>4.903299</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876871348.54</v>
+        <v>876863544.00</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.381506</v>
+        <v>39.401197</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40671407.89</v>
+        <v>40691743.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>145.384582</v>
+        <v>145.384819</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>558712.95</v>
+        <v>558713.86</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.132964</v>
+        <v>34.122104</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102398892.86</v>
+        <v>102366311.06</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002301</v>
+        <v>0.002303</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>260381121.34</v>
+        <v>260651156.60</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956055</v>
+        <v>31.956095</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355111151.57</v>
+        <v>355111598.16</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>400.518308</v>
+        <v>400.639979</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300177257.49</v>
+        <v>300268446.61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.382241</v>
+        <v>2.377196</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>491387612.89</v>
+        <v>490346829.78</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912439</v>
+        <v>0.912461</v>
       </c>
       <c r="E121" s="66">
         <v>246086436.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>224538881.29</v>
+        <v>224544248.58</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.500177</v>
+        <v>1.500114</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55063920.62</v>
+        <v>55061600.47</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.024242</v>
+        <v>27.021359</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391404578.48</v>
+        <v>391362825.25</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027941</v>
+        <v>2.027918</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59053481.77</v>
+        <v>59052838.92</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.707975</v>
+        <v>21.724674</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119614113.15</v>
+        <v>119706124.77</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.662286</v>
+        <v>7.661945</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178539798.65</v>
+        <v>178531854.38</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.023920</v>
+        <v>5.023741</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214468495.41</v>
+        <v>214460872.82</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723356</v>
+        <v>2.723301</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368692633.76</v>
+        <v>368685096.57</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.844153</v>
+        <v>23.844390</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451255004.61</v>
+        <v>451259501.07</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.410651</v>
+        <v>5.410170</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44218478.96</v>
+        <v>44214545.98</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348197</v>
+        <v>1.348192</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020993751.28</v>
+        <v>1020990174.72</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949696</v>
+        <v>0.949635</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87019064.81</v>
+        <v>87013501.29</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.224312</v>
+        <v>12.226273</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172127483.89</v>
+        <v>172155098.20</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.216815</v>
+        <v>2.217304</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157843641.55</v>
+        <v>157878442.66</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.425272</v>
+        <v>13.439369</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101453831.07</v>
+        <v>101560354.59</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.091903</v>
+        <v>94.087275</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24293588.50</v>
+        <v>24292393.44</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.659544</v>
+        <v>4.659989</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425374505.90</v>
+        <v>425415148.24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.440445</v>
+        <v>18.233749</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>442939496.66</v>
+        <v>437974642.95</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27607.222812</v>
+        <v>27606.867545</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125171148.23</v>
+        <v>125169537.45</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4854.433810</v>
+        <v>4855.989302</v>
       </c>
       <c r="E141" s="66">
         <v>874610.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>4245736354.36</v>
+        <v>4247096803.08</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.204551</v>
+        <v>0.202451</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>204551.39</v>
+        <v>202451.28</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.386189</v>
+        <v>1.386700</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149931810.70</v>
+        <v>149987097.24</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.918575</v>
+        <v>15.919828</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156453583.67</v>
+        <v>1156544563.22</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.095101</v>
+        <v>16.092116</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5746135601.68</v>
+        <v>5745069694.98</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3292.935788</v>
+        <v>3293.040852</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193667432.51</v>
+        <v>193673611.61</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c t="n" r="D147">
-        <v>0.977861</v>
+        <v>0.977862</v>
       </c>
       <c r="E147" s="66">
         <v>431000000.00</v>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421458031.64</v>
+        <v>421458364.45</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.314981</v>
+        <v>1.316469</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>526514862.33</v>
+        <v>527110725.95</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.036175</v>
+        <v>1.036001</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13508329107.96</v>
+        <v>13506058876.49</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.922028</v>
+        <v>0.921774</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13642193774.96</v>
+        <v>13638440371.68</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1930.447440</v>
+        <v>1926.474677</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41094878.64</v>
+        <v>41010307.46</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.584834</v>
+        <v>1.582272</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60967796.57</v>
+        <v>60869232.31</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6765.037829</v>
+        <v>6765.225743</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964356142.58</v>
+        <v>964382929.63</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.189718</v>
+        <v>1926.191178</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337732326.61</v>
+        <v>337732582.55</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17335.300068</v>
+        <v>17336.095724</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504344124.37</v>
+        <v>2504459068.82</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20305.096071</v>
+        <v>20305.896867</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185060645.59</v>
+        <v>185067944.05</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15349.640443</v>
+        <v>15349.770383</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320346996.04</v>
+        <v>320349707.89</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1159.823589</v>
+        <v>1161.198631</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5904661.89</v>
+        <v>5911662.23</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.284904</v>
+        <v>3675.363189</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719073166.73</v>
+        <v>719088483.38</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200851.133698</v>
+        <v>200851.020690</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602102026.42</v>
+        <v>4602099437.07</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,21 +4564,21 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.449572</v>
+        <v>33.461207</v>
       </c>
       <c r="E162" s="66">
-        <v>16759003.00</v>
+        <v>18098207.00</v>
       </c>
       <c r="F162" s="65">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G162" s="66">
-        <v>560581472.47</v>
+        <v>605587858.50</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.441135</v>
+        <v>80.477175</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396206938.35</v>
+        <v>396384450.19</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400495</v>
+        <v>1.400597</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154379036.73</v>
+        <v>154390253.68</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.436612</v>
+        <v>2579.503492</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438506803.40</v>
+        <v>438518173.12</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731291</v>
+        <v>1678.731293</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092785.08</v>
+        <v>927092786.33</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027169</v>
+        <v>1.027159</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970667307.00</v>
+        <v>970657138.01</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1047.455115</v>
+        <v>1046.866292</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114504650.79</v>
+        <v>114440282.48</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.851873</v>
+        <v>75.863672</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65889412.47</v>
+        <v>65899661.84</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188106</v>
+        <v>3.188098</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977097219.72</v>
+        <v>977095004.15</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2979.952427</v>
+        <v>2980.145274</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2194362468.50</v>
+        <v>2194504476.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4331.788700</v>
+        <v>4344.286412</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19233141.83</v>
+        <v>19288631.67</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63327.042854</v>
+        <v>63326.219217</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174906626.07</v>
+        <v>1174891345.14</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.542339</v>
+        <v>8193.468747</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148983180.35</v>
+        <v>148981842.23</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>46184.443425</v>
+        <v>46184.048098</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>3023372219.91</v>
+        <v>3023346340.65</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11591.278068</v>
+        <v>11591.140228</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675614716.43</v>
+        <v>2675582898.94</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2488.908362</v>
+        <v>2487.565928</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92973171.87</v>
+        <v>92923025.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.529476</v>
+        <v>2705.375589</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459636991.59</v>
+        <v>459610848.01</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3496.724005</v>
+        <v>3496.040563</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20760050.42</v>
+        <v>20755992.82</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3286.993115</v>
+        <v>3286.952371</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6834703949.46</v>
+        <v>6834619230.90</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994769</v>
+        <v>0.994744</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928512203.29</v>
+        <v>928488920.91</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4661.117807</v>
+        <v>4661.073113</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70261689.83</v>
+        <v>70261016.10</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.179839</v>
+        <v>1.180270</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2387228.64</v>
+        <v>2388099.86</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.717504</v>
+        <v>3592.714949</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917245927.78</v>
+        <v>917245275.41</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211550</v>
+        <v>1.211521</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226641655.92</v>
+        <v>226636207.48</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.170781</v>
+        <v>1331.219243</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502528950.47</v>
+        <v>502547245.26</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.330544</v>
+        <v>1109.320588</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721135213.13</v>
+        <v>1721119766.80</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.938539</v>
+        <v>74.938090</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872883947.35</v>
+        <v>872878720.93</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.223493</v>
+        <v>10.233889</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>453009467.32</v>
+        <v>453470153.16</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.207046</v>
+        <v>14.206734</v>
       </c>
       <c r="E190" s="66">
         <v>145515811.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2067349864.89</v>
+        <v>2067304390.79</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7570.376000</v>
+        <v>7574.630819</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>283571144.19</v>
+        <v>283730521.21</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.916558</v>
+        <v>1.916223</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26232686.87</v>
+        <v>26228103.97</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441838</v>
+        <v>2.441761</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206118129.37</v>
+        <v>206111626.78</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.330301</v>
+        <v>44.333375</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>564499387.12</v>
+        <v>564538539.42</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14893.906311</v>
+        <v>14894.521921</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6208078028.40</v>
+        <v>6208334627.19</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6274.111915</v>
+        <v>6274.563565</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39777869.54</v>
+        <v>39780733.00</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.354733</v>
+        <v>2933.383754</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077547327.63</v>
+        <v>1077557988.30</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223961</v>
+        <v>1.223948</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523033834.38</v>
+        <v>523028520.16</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323456</v>
+        <v>1.323510</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121757965.65</v>
+        <v>121762933.22</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.354572</v>
+        <v>7.356446</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2806799535.09</v>
+        <v>2807514923.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>998.179832</v>
+        <v>1002.659059</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>448003072.08</v>
+        <v>450013438.68</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2507.317130</v>
+        <v>2510.699061</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>514330977.41</v>
+        <v>515024719.77</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5728,18 +5728,18 @@
         <v>1.000000</v>
       </c>
       <c r="E205" s="66">
-        <v>300000.00</v>
+        <v>7060340.00</v>
       </c>
       <c r="F205" s="65">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="G205" s="66">
-        <v>300000.00</v>
+        <v>7060340.00</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>0.004374</v>
+        <v>0.004373</v>
       </c>
       <c r="E206" s="66">
         <v>67618383967.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>295778185.03</v>
+        <v>295675320.41</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>20.819557</v>
+        <v>20.820119</v>
       </c>
       <c r="E207" s="66">
         <v>81092133.00</v>
@@ -5788,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>1688302309.61</v>
+        <v>1688347840.28</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>3.358655</v>
+        <v>3.358724</v>
       </c>
       <c r="E208" s="66">
         <v>21323550.00</v>
@@ -5815,12 +5815,12 @@
         <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>71618456.76</v>
+        <v>71619911.37</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>7699.654675</v>
+        <v>7701.546171</v>
       </c>
       <c r="E209" s="66">
         <v>197052.47</v>
@@ -5842,12 +5842,12 @@
         <v>38</v>
       </c>
       <c r="G209" s="66">
-        <v>1517236002.63</v>
+        <v>1517608726.71</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.844790</v>
+        <v>1.844778</v>
       </c>
       <c r="E210" s="66">
         <v>601179729.00</v>
@@ -5869,12 +5869,12 @@
         <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>1109050235.28</v>
+        <v>1109043372.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>24.168382</v>
+        <v>23.325544</v>
       </c>
       <c r="E211" s="66">
         <v>377.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>9111.48</v>
+        <v>8793.73</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.746060</v>
+        <v>1.748907</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>174605.98</v>
+        <v>174890.67</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>1.746218</v>
+        <v>1.749065</v>
       </c>
       <c r="E213" s="66">
         <v>100000.00</v>
@@ -5950,12 +5950,12 @@
         <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>174621.81</v>
+        <v>174906.50</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>61.321202</v>
+        <v>61.316302</v>
       </c>
       <c r="E214" s="66">
         <v>2554914.00</v>
@@ -5977,12 +5977,12 @@
         <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>156670398.10</v>
+        <v>156657878.42</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>15.238457</v>
+        <v>15.241474</v>
       </c>
       <c r="E215" s="66">
         <v>248000220.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>3779140587.65</v>
+        <v>3779888806.88</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,21 +6022,21 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>1.801150</v>
+        <v>1.801156</v>
       </c>
       <c r="E216" s="66">
-        <v>437816172.00</v>
+        <v>504995473.00</v>
       </c>
       <c r="F216" s="65">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G216" s="66">
-        <v>788572593.23</v>
+        <v>909575617.50</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>0.391971</v>
+        <v>0.391900</v>
       </c>
       <c r="E217" s="66">
         <v>402507.00</v>
@@ -6058,12 +6058,12 @@
         <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>157771.14</v>
+        <v>157742.52</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>9.879188</v>
+        <v>9.878594</v>
       </c>
       <c r="E218" s="66">
         <v>27178800.00</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>268504486.48</v>
+        <v>268488320.08</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.617378</v>
+        <v>15.616313</v>
       </c>
       <c r="E219" s="66">
         <v>10371838.00</v>
@@ -6112,12 +6112,12 @@
         <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>161980914.56</v>
+        <v>161969864.96</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>15.326912</v>
+        <v>15.326159</v>
       </c>
       <c r="E220" s="66">
         <v>19475841.00</v>
@@ -6139,12 +6139,12 @@
         <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>298504505.14</v>
+        <v>298489845.04</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>31.088482</v>
+        <v>31.086078</v>
       </c>
       <c r="E221" s="66">
         <v>9712281.00</v>
@@ -6166,12 +6166,12 @@
         <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>301940077.77</v>
+        <v>301916723.47</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>7.979517</v>
+        <v>7.978896</v>
       </c>
       <c r="E222" s="66">
         <v>12818249.00</v>
@@ -6193,12 +6193,12 @@
         <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>102283437.69</v>
+        <v>102275472.96</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>1659.774619</v>
+        <v>1659.768553</v>
       </c>
       <c r="E223" s="66">
         <v>330000.00</v>
@@ -6220,12 +6220,12 @@
         <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>547725624.32</v>
+        <v>547723622.53</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.169625</v>
+        <v>5.169565</v>
       </c>
       <c r="E224" s="66">
         <v>11867933.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>61352759.37</v>
+        <v>61352054.27</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.946612</v>
+        <v>0.946654</v>
       </c>
       <c r="E225" s="66">
         <v>130000000.00</v>
@@ -6274,12 +6274,12 @@
         <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>123059601.68</v>
+        <v>123065019.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>5.519542</v>
+        <v>5.519535</v>
       </c>
       <c r="E226" s="66">
         <v>103852814.00</v>
@@ -6301,12 +6301,12 @@
         <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>573219928.77</v>
+        <v>573219202.18</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>6078.75</v>
+        <v>6078.74</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>6.606033</v>
+        <v>6.605545</v>
       </c>
       <c r="E228" s="66">
         <v>11104667.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>73357795.34</v>
+        <v>73352372.16</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>26.519621</v>
+        <v>26.516398</v>
       </c>
       <c r="E229" s="66">
         <v>1038884.00</v>
@@ -6382,12 +6382,12 @@
         <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>27550809.60</v>
+        <v>27547461.84</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.850445</v>
+        <v>0.850339</v>
       </c>
       <c r="E230" s="66">
         <v>73432275.00</v>
@@ -6409,12 +6409,12 @@
         <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>62450114.65</v>
+        <v>62442314.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.711564</v>
+        <v>0.711508</v>
       </c>
       <c r="E231" s="66">
         <v>801655137.00</v>
@@ -6436,12 +6436,12 @@
         <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>570428671.30</v>
+        <v>570384439.07</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>11.956817</v>
+        <v>11.956763</v>
       </c>
       <c r="E232" s="66">
         <v>26235742.00</v>
@@ -6463,12 +6463,12 @@
         <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>313695963.45</v>
+        <v>313694547.85</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c t="n" r="D233">
-        <v>0.004716</v>
+        <v>0.004715</v>
       </c>
       <c r="E233" s="66">
         <v>100000.00</v>
@@ -6490,12 +6490,12 @@
         <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>471.55</v>
+        <v>471.54</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1.552115</v>
+        <v>1.554437</v>
       </c>
       <c r="E234" s="66">
         <v>24022001.00</v>
@@ -6517,12 +6517,12 @@
         <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>37284917.59</v>
+        <v>37340676.94</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>2.572212</v>
+        <v>2.572228</v>
       </c>
       <c r="E235" s="66">
         <v>68085562.00</v>
@@ -6544,12 +6544,12 @@
         <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>175130521.92</v>
+        <v>175131610.31</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1057.815397</v>
+        <v>1058.875240</v>
       </c>
       <c r="E236" s="66">
         <v>20029.00</v>
@@ -6571,12 +6571,12 @@
         <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>21186984.59</v>
+        <v>21208212.18</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>3.245629</v>
+        <v>3.246126</v>
       </c>
       <c r="E237" s="66">
         <v>1427155857.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>4632018708.40</v>
+        <v>4632727036.71</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1690.015253</v>
+        <v>1684.503178</v>
       </c>
       <c r="E238" s="66">
         <v>97333.00</v>
@@ -6625,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>164494254.58</v>
+        <v>163957747.86</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,21 +6643,21 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>1.161237</v>
+        <v>1.161206</v>
       </c>
       <c r="E239" s="66">
-        <v>1103857956.00</v>
+        <v>1107173943.00</v>
       </c>
       <c r="F239" s="65">
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1281840319.55</v>
+        <v>1285656931.02</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>2.251292</v>
+        <v>2.240860</v>
       </c>
       <c r="E240" s="66">
         <v>296754544.00</v>
@@ -6679,12 +6679,12 @@
         <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>668081105.15</v>
+        <v>664985459.89</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1005.025858</v>
+        <v>1006.101136</v>
       </c>
       <c r="E241" s="66">
         <v>1431712.00</v>
@@ -6706,12 +6706,12 @@
         <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1438907581.18</v>
+        <v>1440447069.14</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>5.001555</v>
+        <v>5.001478</v>
       </c>
       <c r="E242" s="66">
         <v>395532870.00</v>
@@ -6733,12 +6733,12 @@
         <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1978279457.70</v>
+        <v>1978249072.28</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>1303.844324</v>
+        <v>1303.833724</v>
       </c>
       <c r="E243" s="66">
         <v>1467447.00</v>
@@ -6760,12 +6760,12 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1913322441.31</v>
+        <v>1913306886.31</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c t="inlineStr" r="B244">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="D244">
-        <v>26978.437568</v>
+        <v>26962.806741</v>
       </c>
       <c r="E244" s="66">
         <v>40026.00</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="G244" s="66">
-        <v>1079838942.09</v>
+        <v>1079213302.61</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.863489</v>
+        <v>7724.864814</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915789319.88</v>
+        <v>1915789648.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.253873</v>
+        <v>29.248592</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5084954909.43</v>
+        <v>5084036947.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.593946</v>
+        <v>0.579675</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>296973.04</v>
+        <v>289837.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11305.624099</v>
+        <v>11302.672572</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3335317387.94</v>
+        <v>3334446646.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5355.632772</v>
+        <v>5355.905948</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52217419.53</v>
+        <v>52220082.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24464.021486</v>
+        <v>24463.948353</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2023174576.93</v>
+        <v>2023168528.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.709146</v>
+        <v>9968.805860</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72931076.11</v>
+        <v>72931783.67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198674</v>
+        <v>2.198489</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1265028101.41</v>
+        <v>1264921548.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.414072</v>
+        <v>1141.394182</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893956642.83</v>
+        <v>893941064.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>366.264981</v>
+        <v>366.819004</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>378717.99</v>
+        <v>379290.85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.358792</v>
+        <v>23.357535</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333645624.65</v>
+        <v>2333520057.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.499382</v>
+        <v>24.497654</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701359560.13</v>
+        <v>2701169020.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340044</v>
+        <v>8.340046</v>
       </c>
       <c r="E15" s="66">
         <v>11331690.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506804.89</v>
+        <v>94506827.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.469556</v>
+        <v>7.469522</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>549194390.48</v>
+        <v>549191913.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.814941</v>
+        <v>10.814239</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164662998.68</v>
+        <v>164652302.60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>967.326532</v>
+        <v>966.406016</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41641472.54</v>
+        <v>41601846.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1227.821544</v>
+        <v>1229.084795</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11665532.49</v>
+        <v>11677534.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.649078</v>
+        <v>13.648316</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569544880.27</v>
+        <v>1569457259.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999284</v>
+        <v>0.999120</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99928.43</v>
+        <v>99912.00</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1014.278084</v>
+        <v>1015.616926</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20285561.68</v>
+        <v>20312338.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.546815</v>
+        <v>724.523100</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004888371.18</v>
+        <v>3004790018.16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.433784</v>
+        <v>1124.418316</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723520303.22</v>
+        <v>2723482838.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999284</v>
+        <v>0.999120</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99928.43</v>
+        <v>99912.00</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.652340</v>
+        <v>1.677183</v>
       </c>
       <c r="E27" s="66">
-        <v>292286905.00</v>
+        <v>314786294.00</v>
       </c>
       <c r="F27" s="65">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G27" s="66">
-        <v>482957246.55</v>
+        <v>527954217.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>890.101200</v>
+        <v>873.296999</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4449615.90</v>
+        <v>4365611.70</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1159.999026</v>
+        <v>1215.042394</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>57999951.29</v>
+        <v>60752119.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809643</v>
+        <v>1.809650</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361928660.88</v>
+        <v>361929933.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1368.710958</v>
+        <v>1369.312505</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5474843.83</v>
+        <v>5477250.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7321.886768</v>
+        <v>7321.192451</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533655717.08</v>
+        <v>533605111.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.799384</v>
+        <v>6974.242566</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173205193.11</v>
+        <v>173191365.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20566.766352</v>
+        <v>20566.788289</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>334580155.02</v>
+        <v>334580511.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1161.399232</v>
+        <v>1162.642302</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5806996.16</v>
+        <v>5813211.51</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1160.399232</v>
+        <v>1161.642304</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5801996.16</v>
+        <v>5808211.52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1038.633817</v>
+        <v>1038.741558</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26069708.81</v>
+        <v>26072413.10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694826</v>
+        <v>1.694530</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231633229.68</v>
+        <v>231592836.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1226.471991</v>
+        <v>1229.997948</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>326934506.34</v>
+        <v>327874403.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3618.833262</v>
+        <v>3618.725572</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>738241985.54</v>
+        <v>738220016.65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3545.043974</v>
+        <v>3636.595517</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>248734465.36</v>
+        <v>255158087.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6819.449674</v>
+        <v>6807.962410</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>191050571.93</v>
+        <v>190728750.02</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110052</v>
+        <v>0.110009</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34758522.58</v>
+        <v>34745092.20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947309</v>
+        <v>1.947179</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242675910.73</v>
+        <v>242659704.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.605036</v>
+        <v>5.604238</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59440732.25</v>
+        <v>59432272.44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465235</v>
+        <v>0.465189</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652118284.39</v>
+        <v>1651954057.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008910</v>
+        <v>0.008912</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>606184111.77</v>
+        <v>606277098.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.109890</v>
+        <v>0.108866</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>158109.24</v>
+        <v>156635.61</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.442771</v>
+        <v>0.442067</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>605703.44</v>
+        <v>604739.88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1773.742495</v>
+        <v>1776.352858</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>508977182.65</v>
+        <v>509726229.00</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16915.524744</v>
+        <v>16916.609680</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370399245.33</v>
+        <v>370423002.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.283919</v>
+        <v>1.284360</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12855880.61</v>
+        <v>12860296.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7525.137390</v>
+        <v>7522.992367</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44541288.21</v>
+        <v>44528591.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.330714</v>
+        <v>7.335788</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>242090860.74</v>
+        <v>242258425.43</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.070544</v>
+        <v>0.036423</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>79731.05</v>
+        <v>41166.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.370416</v>
+        <v>6.375069</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109776700.15</v>
+        <v>109856879.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990333</v>
+        <v>0.990240</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59419991.32</v>
+        <v>59414380.64</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.591054</v>
+        <v>1.590954</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137639710.72</v>
+        <v>137631099.87</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.622857</v>
+        <v>8.621262</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344914267.85</v>
+        <v>344850487.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.693691</v>
+        <v>0.687876</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>693690.83</v>
+        <v>687876.09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.870543</v>
+        <v>0.863910</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>752093.02</v>
+        <v>746363.03</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.244882</v>
+        <v>2.244390</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170653363.96</v>
+        <v>170615967.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.712493</v>
+        <v>5.712839</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1623235295.98</v>
+        <v>1623333654.20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.350198</v>
+        <v>1.351219</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2663438553.48</v>
+        <v>2665451712.93</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296293</v>
+        <v>1.296231</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744686960.45</v>
+        <v>1744603113.27</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975274</v>
+        <v>0.975285</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153605614.07</v>
+        <v>153607413.71</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>6.020957</v>
+        <v>6.022915</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6609159714.34</v>
+        <v>6611308201.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1515.098951</v>
+        <v>1514.861860</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1370081254.75</v>
+        <v>1369866857.43</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.174126</v>
+        <v>6.179249</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613906206.76</v>
+        <v>2616075385.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.094403</v>
+        <v>4.095988</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2594050103.35</v>
+        <v>2595053988.57</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.766213</v>
+        <v>6.775799</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>318552045.97</v>
+        <v>319003338.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792625</v>
+        <v>1.792410</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444833070.69</v>
+        <v>444779751.50</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.448378</v>
+        <v>18.442251</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20253459.11</v>
+        <v>20246732.89</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.156350</v>
+        <v>3.157175</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>553234424.99</v>
+        <v>553378964.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.593741</v>
+        <v>14.594298</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6454163749.40</v>
+        <v>6454410170.92</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.594536</v>
+        <v>6.594669</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2911371075.29</v>
+        <v>2911429829.83</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1361.648342</v>
+        <v>1362.240211</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>392989412.86</v>
+        <v>393160233.90</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232676</v>
+        <v>5.232330</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355938163.34</v>
+        <v>355914584.60</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>440.480100</v>
+        <v>439.487000</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>44048.01</v>
+        <v>43948.70</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7088.165000</v>
+        <v>7077.666000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70881.65</v>
+        <v>70776.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>183.245700</v>
+        <v>182.308200</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18324.57</v>
+        <v>18230.82</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.041141</v>
+        <v>46.024619</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1615537.61</v>
+        <v>1614957.87</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1218.543768</v>
+        <v>1220.073842</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>113324570.44</v>
+        <v>113466867.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.023906</v>
+        <v>21.020291</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671502460.82</v>
+        <v>1671215094.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.433561</v>
+        <v>31.427302</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978789493.45</v>
+        <v>978594616.41</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>45.998646</v>
+        <v>45.978148</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1614046.49</v>
+        <v>1613327.23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.085250</v>
+        <v>1.086464</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>613166185.91</v>
+        <v>613851888.83</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.688432</v>
+        <v>20.708867</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>208100444.52</v>
+        <v>208306004.06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.743470</v>
+        <v>19.744814</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3078204453.45</v>
+        <v>3078413951.77</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014556</v>
+        <v>0.014677</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8015.87</v>
+        <v>8082.51</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5677.901203</v>
+        <v>5678.128595</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5432615870.69</v>
+        <v>5432833439.89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.332735</v>
+        <v>1.335791</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>217122707.60</v>
+        <v>217620534.09</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778958</v>
+        <v>0.778822</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135933663.59</v>
+        <v>135909921.66</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.634227</v>
+        <v>30.632220</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1551648649.10</v>
+        <v>1551546967.67</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.094071</v>
+        <v>1.092132</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55459585.96</v>
+        <v>55361283.75</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208843</v>
+        <v>1.208705</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298584269.45</v>
+        <v>298550187.20</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599220</v>
+        <v>0.599039</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70311424.14</v>
+        <v>70290215.52</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.510604</v>
+        <v>52.500489</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>39000571.06</v>
+        <v>38993058.46</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.946559</v>
+        <v>19.945286</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109599239.18</v>
+        <v>109592248.48</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,21 +2890,21 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1014.632942</v>
+        <v>1005.377530</v>
       </c>
       <c r="E100" s="66">
-        <v>22861.00</v>
+        <v>67591.00</v>
       </c>
       <c r="F100" s="65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G100" s="66">
-        <v>23195523.68</v>
+        <v>67954472.61</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.611702</v>
+        <v>0.611611</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1284573.73</v>
+        <v>1284384.10</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841358601.26</v>
+        <v>1841332034.94</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.950801</v>
+        <v>4.955402</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66358674.05</v>
+        <v>66420356.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.944721</v>
+        <v>13.943789</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174637255.98</v>
+        <v>174625588.57</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.366385</v>
+        <v>9.365300</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78533582.76</v>
+        <v>78524480.75</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.406920</v>
+        <v>14.406349</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933550788.20</v>
+        <v>933513797.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808758</v>
+        <v>8.808220</v>
       </c>
       <c r="E107" s="66">
         <v>79280717.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>698364616.51</v>
+        <v>698321989.38</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.936566</v>
+        <v>8.943244</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2909536488.68</v>
+        <v>2911710499.53</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.811020</v>
+        <v>29.801953</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661900673.00</v>
+        <v>661699345.39</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.779368</v>
+        <v>2.780607</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>294404214.67</v>
+        <v>294535452.18</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.365817</v>
+        <v>48.366862</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1839052916.52</v>
+        <v>1839092649.36</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.610718</v>
+        <v>11.609862</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147419735.43</v>
+        <v>147408858.74</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.903299</v>
+        <v>4.903040</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876863544.00</v>
+        <v>876817346.81</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.401197</v>
+        <v>39.415246</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40691743.33</v>
+        <v>40706253.15</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>145.384819</v>
+        <v>126.380315</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>558713.86</v>
+        <v>485679.55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>34.122104</v>
+        <v>32.092647</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>102366311.06</v>
+        <v>96277942.35</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002303</v>
+        <v>0.002306</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>260651156.60</v>
+        <v>260912539.23</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956095</v>
+        <v>31.954411</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355111598.16</v>
+        <v>355092883.38</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>400.639979</v>
+        <v>400.789255</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300268446.61</v>
+        <v>300380324.45</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.377196</v>
+        <v>2.409390</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>490346829.78</v>
+        <v>496987607.44</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912461</v>
+        <v>0.912381</v>
       </c>
       <c r="E121" s="66">
         <v>246086436.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>224544248.58</v>
+        <v>224524666.82</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.500114</v>
+        <v>1.499861</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55061600.47</v>
+        <v>55052292.92</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.021359</v>
+        <v>27.019835</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391362825.25</v>
+        <v>391340752.53</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027918</v>
+        <v>2.027762</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59052838.92</v>
+        <v>59048285.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.724674</v>
+        <v>21.732054</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119706124.77</v>
+        <v>119746792.48</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.661945</v>
+        <v>7.660934</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178531854.38</v>
+        <v>178508287.88</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.023741</v>
+        <v>5.022435</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214460872.82</v>
+        <v>214405110.84</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723301</v>
+        <v>2.723116</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368685096.57</v>
+        <v>368660103.88</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.844390</v>
+        <v>23.843979</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451259501.07</v>
+        <v>451251714.22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.410170</v>
+        <v>5.408727</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44214545.98</v>
+        <v>44202747.81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348192</v>
+        <v>1.348146</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020990174.72</v>
+        <v>1020955320.70</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949635</v>
+        <v>0.949453</v>
       </c>
       <c r="E132" s="66">
         <v>91628362.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87013501.29</v>
+        <v>86996812.19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.226273</v>
+        <v>12.226700</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172155098.20</v>
+        <v>172161108.99</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.217304</v>
+        <v>2.217641</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157878442.66</v>
+        <v>157902459.69</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.439369</v>
+        <v>13.443298</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101560354.59</v>
+        <v>101590044.88</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.087275</v>
+        <v>94.052150</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24292393.44</v>
+        <v>24283324.72</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.659989</v>
+        <v>4.660281</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425415148.24</v>
+        <v>425441743.80</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c t="n" r="D138">
-        <v>999.950000</v>
+        <v>1000.000000</v>
       </c>
       <c r="E138" s="66">
         <v>100.00</v>
@@ -3925,12 +3925,12 @@
         <v>1</v>
       </c>
       <c r="G138" s="66">
-        <v>99995.00</v>
+        <v>100000.00</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.233749</v>
+        <v>18.233957</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>437974642.95</v>
+        <v>437979635.52</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27606.867545</v>
+        <v>27604.177439</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125169537.45</v>
+        <v>125157340.51</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,21 +3997,21 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4855.989302</v>
+        <v>4857.204596</v>
       </c>
       <c r="E141" s="66">
-        <v>874610.00</v>
+        <v>709751.00</v>
       </c>
       <c r="F141" s="65">
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>4247096803.08</v>
+        <v>3447405819.42</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.202451</v>
+        <v>0.196151</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>202451.28</v>
+        <v>196150.94</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.386700</v>
+        <v>1.387168</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>149987097.24</v>
+        <v>150037761.96</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.919828</v>
+        <v>15.920627</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156544563.22</v>
+        <v>1156602599.72</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.092116</v>
+        <v>16.093374</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5745069694.98</v>
+        <v>5745518879.04</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3293.040852</v>
+        <v>3292.781348</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193673611.61</v>
+        <v>193658349.43</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421458364.45</v>
+        <v>421458732.07</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.316469</v>
+        <v>1.318113</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>527110725.95</v>
+        <v>527768914.68</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.036001</v>
+        <v>1.035354</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13506058876.49</v>
+        <v>13497617175.11</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.921774</v>
+        <v>0.921014</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13638440371.68</v>
+        <v>13627195247.10</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c t="n" r="D151">
-        <v>999.950000</v>
+        <v>1000.000000</v>
       </c>
       <c r="E151" s="66">
         <v>100.00</v>
@@ -4276,12 +4276,12 @@
         <v>1</v>
       </c>
       <c r="G151" s="66">
-        <v>99995.00</v>
+        <v>100000.00</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1926.474677</v>
+        <v>1926.488365</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41010307.46</v>
+        <v>41010598.84</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.582272</v>
+        <v>1.582002</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60869232.31</v>
+        <v>60858861.57</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6765.225743</v>
+        <v>6765.410351</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964382929.63</v>
+        <v>964409245.59</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.191178</v>
+        <v>1926.192637</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337732582.55</v>
+        <v>337732838.43</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17336.095724</v>
+        <v>17336.891304</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504459068.82</v>
+        <v>2504574002.23</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20305.896867</v>
+        <v>20306.681971</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185067944.05</v>
+        <v>185075099.48</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15349.770383</v>
+        <v>15349.926951</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320349707.89</v>
+        <v>320352975.46</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1161.198631</v>
+        <v>1162.437335</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5911662.23</v>
+        <v>5917968.47</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.363189</v>
+        <v>3675.441460</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719088483.38</v>
+        <v>719103797.00</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200851.020690</v>
+        <v>200850.681717</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602099437.07</v>
+        <v>4602091670.19</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.461207</v>
+        <v>33.481522</v>
       </c>
       <c r="E162" s="66">
         <v>18098207.00</v>
@@ -4573,12 +4573,12 @@
         <v>27</v>
       </c>
       <c r="G162" s="66">
-        <v>605587858.50</v>
+        <v>605955514.65</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.477175</v>
+        <v>80.481628</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396384450.19</v>
+        <v>396406385.11</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400597</v>
+        <v>1.400645</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154390253.68</v>
+        <v>154395580.26</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.503492</v>
+        <v>2579.512038</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438518173.12</v>
+        <v>438519625.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731293</v>
+        <v>1678.731295</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092786.33</v>
+        <v>927092787.55</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027159</v>
+        <v>1.027101</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970657138.01</v>
+        <v>970602423.01</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1046.866292</v>
+        <v>1046.733867</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114440282.48</v>
+        <v>114425806.19</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.863672</v>
+        <v>75.861847</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65899661.84</v>
+        <v>65898075.90</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188098</v>
+        <v>3.188007</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977095004.15</v>
+        <v>977067104.45</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2980.145274</v>
+        <v>2980.345211</v>
       </c>
       <c r="E171" s="66">
         <v>736375.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2194504476.08</v>
+        <v>2194651704.63</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4344.286412</v>
+        <v>4355.335944</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19288631.67</v>
+        <v>19337691.59</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63326.219217</v>
+        <v>63324.883775</v>
       </c>
       <c r="E173" s="66">
         <v>18553.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174891345.14</v>
+        <v>1174866568.68</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.468747</v>
+        <v>8193.247972</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148981842.23</v>
+        <v>148977827.87</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>46184.048098</v>
+        <v>46180.708708</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>3023346340.65</v>
+        <v>3023127734.15</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11591.140228</v>
+        <v>11590.726710</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675582898.94</v>
+        <v>2675487446.47</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2487.565928</v>
+        <v>2487.707837</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92923025.25</v>
+        <v>92928326.26</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.375589</v>
+        <v>2705.760178</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459610848.01</v>
+        <v>459676185.08</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3496.040563</v>
+        <v>3495.954891</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20755992.82</v>
+        <v>20755484.19</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3286.952371</v>
+        <v>3296.470609</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6834619230.90</v>
+        <v>6854410673.24</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994744</v>
+        <v>0.994678</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928488920.91</v>
+        <v>928427242.98</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4661.073113</v>
+        <v>4660.939031</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70261016.10</v>
+        <v>70258994.96</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.180270</v>
+        <v>1.179493</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2388099.86</v>
+        <v>2386527.91</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.714949</v>
+        <v>3592.707283</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917245275.41</v>
+        <v>917243318.30</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211521</v>
+        <v>1.211434</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226636207.48</v>
+        <v>226619830.91</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.219243</v>
+        <v>1331.225348</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502547245.26</v>
+        <v>502549549.76</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.320588</v>
+        <v>1109.290548</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721119766.80</v>
+        <v>1721073159.39</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.938090</v>
+        <v>74.936564</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872878720.93</v>
+        <v>872860942.06</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.233889</v>
+        <v>10.224903</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>453470153.16</v>
+        <v>453071962.02</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.206734</v>
+        <v>14.204591</v>
       </c>
       <c r="E190" s="66">
         <v>145515811.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2067304390.79</v>
+        <v>2066992519.05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7574.630819</v>
+        <v>7568.545803</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>283730521.21</v>
+        <v>283502588.69</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.916223</v>
+        <v>1.915786</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26228103.97</v>
+        <v>26222124.16</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441761</v>
+        <v>2.441708</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206111626.78</v>
+        <v>206107102.35</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.333375</v>
+        <v>44.331431</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>564538539.42</v>
+        <v>564513777.44</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14894.521921</v>
+        <v>14894.428659</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6208334627.19</v>
+        <v>6208295753.77</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6274.563565</v>
+        <v>6274.880453</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39780733.00</v>
+        <v>39782742.07</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.383754</v>
+        <v>2933.360473</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077557988.30</v>
+        <v>1077549436.23</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223948</v>
+        <v>1.223903</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523028520.16</v>
+        <v>523009333.83</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323510</v>
+        <v>1.323386</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121762933.22</v>
+        <v>121751529.82</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.356446</v>
+        <v>7.368405</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2807514923.53</v>
+        <v>2812078782.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>1002.659059</v>
+        <v>1002.584739</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>450013438.68</v>
+        <v>449980082.70</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2510.699061</v>
+        <v>2515.634317</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>515024719.77</v>
+        <v>516037098.72</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>1.000000</v>
+        <v>1.003234</v>
       </c>
       <c r="E205" s="66">
-        <v>7060340.00</v>
+        <v>23381511.00</v>
       </c>
       <c r="F205" s="65">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="G205" s="66">
-        <v>7060340.00</v>
+        <v>23457127.44</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>0.004373</v>
+        <v>0.004400</v>
       </c>
       <c r="E206" s="66">
         <v>67618383967.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>295675320.41</v>
+        <v>297491412.22</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>20.820119</v>
+        <v>20.820531</v>
       </c>
       <c r="E207" s="66">
         <v>81092133.00</v>
@@ -5788,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>1688347840.28</v>
+        <v>1688381228.55</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>3.358724</v>
+        <v>3.358977</v>
       </c>
       <c r="E208" s="66">
         <v>21323550.00</v>
@@ -5815,12 +5815,12 @@
         <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>71619911.37</v>
+        <v>71625310.12</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,21 +5833,21 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>7701.546171</v>
+        <v>7703.622338</v>
       </c>
       <c r="E209" s="66">
         <v>197052.47</v>
       </c>
       <c r="F209" s="65">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G209" s="66">
-        <v>1517608726.71</v>
+        <v>1518017840.38</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.844778</v>
+        <v>1.844542</v>
       </c>
       <c r="E210" s="66">
         <v>601179729.00</v>
@@ -5869,12 +5869,12 @@
         <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>1109043372.59</v>
+        <v>1108901167.33</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>23.325544</v>
+        <v>20.587188</v>
       </c>
       <c r="E211" s="66">
         <v>377.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>8793.73</v>
+        <v>7761.37</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.748907</v>
+        <v>1.751125</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>174890.67</v>
+        <v>175112.53</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>1.749065</v>
+        <v>1.751284</v>
       </c>
       <c r="E213" s="66">
         <v>100000.00</v>
@@ -5950,12 +5950,12 @@
         <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>174906.50</v>
+        <v>175128.36</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>61.316302</v>
+        <v>61.301240</v>
       </c>
       <c r="E214" s="66">
         <v>2554914.00</v>
@@ -5977,12 +5977,12 @@
         <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>156657878.42</v>
+        <v>156619395.08</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>15.241474</v>
+        <v>15.244222</v>
       </c>
       <c r="E215" s="66">
         <v>248000220.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>3779888806.88</v>
+        <v>3780570307.56</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>1.801156</v>
+        <v>1.800888</v>
       </c>
       <c r="E216" s="66">
         <v>504995473.00</v>
@@ -6031,12 +6031,12 @@
         <v>8</v>
       </c>
       <c r="G216" s="66">
-        <v>909575617.50</v>
+        <v>909440480.48</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>0.391900</v>
+        <v>0.391864</v>
       </c>
       <c r="E217" s="66">
         <v>402507.00</v>
@@ -6058,12 +6058,12 @@
         <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>157742.52</v>
+        <v>157727.84</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>9.878594</v>
+        <v>9.876787</v>
       </c>
       <c r="E218" s="66">
         <v>27178800.00</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>268488320.08</v>
+        <v>268439214.96</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.616313</v>
+        <v>15.613250</v>
       </c>
       <c r="E219" s="66">
         <v>10371838.00</v>
@@ -6112,12 +6112,12 @@
         <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>161969864.96</v>
+        <v>161938102.45</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>15.326159</v>
+        <v>15.323896</v>
       </c>
       <c r="E220" s="66">
         <v>19475841.00</v>
@@ -6139,12 +6139,12 @@
         <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>298489845.04</v>
+        <v>298445757.13</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>31.086078</v>
+        <v>31.079821</v>
       </c>
       <c r="E221" s="66">
         <v>9712281.00</v>
@@ -6166,12 +6166,12 @@
         <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>301916723.47</v>
+        <v>301855958.54</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>7.978896</v>
+        <v>7.977145</v>
       </c>
       <c r="E222" s="66">
         <v>12818249.00</v>
@@ -6193,12 +6193,12 @@
         <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>102275472.96</v>
+        <v>102253026.63</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>1659.768553</v>
+        <v>1659.752199</v>
       </c>
       <c r="E223" s="66">
         <v>330000.00</v>
@@ -6220,12 +6220,12 @@
         <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>547723622.53</v>
+        <v>547718225.74</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.169565</v>
+        <v>5.169419</v>
       </c>
       <c r="E224" s="66">
         <v>11867933.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>61352054.27</v>
+        <v>61350313.29</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.946654</v>
+        <v>0.946662</v>
       </c>
       <c r="E225" s="66">
         <v>130000000.00</v>
@@ -6274,12 +6274,12 @@
         <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>123065019.81</v>
+        <v>123066061.21</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>5.519535</v>
+        <v>5.519489</v>
       </c>
       <c r="E226" s="66">
         <v>103852814.00</v>
@@ -6301,12 +6301,12 @@
         <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>573219202.18</v>
+        <v>573214423.34</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>6078.74</v>
+        <v>6078.71</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>6.605545</v>
+        <v>6.604079</v>
       </c>
       <c r="E228" s="66">
         <v>11104667.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>73352372.16</v>
+        <v>73336102.65</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>26.516398</v>
+        <v>26.509950</v>
       </c>
       <c r="E229" s="66">
         <v>1038884.00</v>
@@ -6382,12 +6382,12 @@
         <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>27547461.84</v>
+        <v>27540762.98</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.850339</v>
+        <v>0.850126</v>
       </c>
       <c r="E230" s="66">
         <v>73432275.00</v>
@@ -6409,12 +6409,12 @@
         <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>62442314.06</v>
+        <v>62426690.85</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.711508</v>
+        <v>0.711635</v>
       </c>
       <c r="E231" s="66">
         <v>801655137.00</v>
@@ -6436,12 +6436,12 @@
         <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>570384439.07</v>
+        <v>570485891.43</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>11.956763</v>
+        <v>12.020110</v>
       </c>
       <c r="E232" s="66">
         <v>26235742.00</v>
@@ -6463,12 +6463,12 @@
         <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>313694547.85</v>
+        <v>315356511.74</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6490,12 +6490,12 @@
         <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>471.54</v>
+        <v>471.51</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1.554437</v>
+        <v>1.556157</v>
       </c>
       <c r="E234" s="66">
         <v>24022001.00</v>
@@ -6517,12 +6517,12 @@
         <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>37340676.94</v>
+        <v>37381997.71</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>2.572228</v>
+        <v>2.571931</v>
       </c>
       <c r="E235" s="66">
         <v>68085562.00</v>
@@ -6544,12 +6544,12 @@
         <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>175131610.31</v>
+        <v>175111384.32</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1058.875240</v>
+        <v>1062.013859</v>
       </c>
       <c r="E236" s="66">
         <v>20029.00</v>
@@ -6571,12 +6571,12 @@
         <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>21208212.18</v>
+        <v>21271075.58</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>3.246126</v>
+        <v>3.246550</v>
       </c>
       <c r="E237" s="66">
         <v>1427155857.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>4632727036.71</v>
+        <v>4633332794.00</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1684.503178</v>
+        <v>1703.217891</v>
       </c>
       <c r="E238" s="66">
         <v>97333.00</v>
@@ -6625,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>163957747.86</v>
+        <v>165779307.01</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>1.161206</v>
+        <v>1.161107</v>
       </c>
       <c r="E239" s="66">
         <v>1107173943.00</v>
@@ -6652,12 +6652,12 @@
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1285656931.02</v>
+        <v>1285547013.38</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>2.240860</v>
+        <v>2.209430</v>
       </c>
       <c r="E240" s="66">
         <v>296754544.00</v>
@@ -6679,12 +6679,12 @@
         <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>664985459.89</v>
+        <v>655658324.93</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1006.101136</v>
+        <v>1007.135101</v>
       </c>
       <c r="E241" s="66">
         <v>1431712.00</v>
@@ -6706,12 +6706,12 @@
         <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1440447069.14</v>
+        <v>1441927410.08</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>5.001478</v>
+        <v>5.004464</v>
       </c>
       <c r="E242" s="66">
         <v>395532870.00</v>
@@ -6733,12 +6733,12 @@
         <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1978249072.28</v>
+        <v>1979430019.89</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>1303.833724</v>
+        <v>1303.799168</v>
       </c>
       <c r="E243" s="66">
         <v>1467447.00</v>
@@ -6760,12 +6760,12 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1913306886.31</v>
+        <v>1913256177.54</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c t="inlineStr" r="B244">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="D244">
-        <v>26962.806741</v>
+        <v>26963.461119</v>
       </c>
       <c r="E244" s="66">
         <v>40026.00</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="G244" s="66">
-        <v>1079213302.61</v>
+        <v>1079239494.74</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.864814</v>
+        <v>7724.868791</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915789648.39</v>
+        <v>1915790634.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.248592</v>
+        <v>29.263796</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5084036947.62</v>
+        <v>5086679738.00</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.579675</v>
+        <v>0.577053</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>289837.49</v>
+        <v>288526.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11302.672572</v>
+        <v>11305.758134</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3334446646.11</v>
+        <v>3335356930.14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5355.905948</v>
+        <v>5356.726176</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52220082.99</v>
+        <v>52228080.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24463.948353</v>
+        <v>24466.512729</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2023168528.78</v>
+        <v>2023380602.70</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9968.805860</v>
+        <v>9969.096251</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72931783.67</v>
+        <v>72933908.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198489</v>
+        <v>2.198425</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1264921548.17</v>
+        <v>1264884566.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.394182</v>
+        <v>1141.401261</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893941064.72</v>
+        <v>893946609.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>366.819004</v>
+        <v>368.433143</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>379290.85</v>
+        <v>380959.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.357535</v>
+        <v>23.359416</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333520057.97</v>
+        <v>2333707998.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.497654</v>
+        <v>24.500442</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701169020.21</v>
+        <v>2701476441.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,21 +595,21 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340046</v>
+        <v>8.339952</v>
       </c>
       <c r="E15" s="66">
-        <v>11331690.89</v>
+        <v>11751343.89</v>
       </c>
       <c r="F15" s="65">
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>94506827.63</v>
+        <v>98005638.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.469522</v>
+        <v>7.472391</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>549191913.81</v>
+        <v>549402813.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.814239</v>
+        <v>10.814204</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164652302.60</v>
+        <v>164651775.79</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>966.406016</v>
+        <v>966.141623</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41601846.16</v>
+        <v>41590464.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1229.084795</v>
+        <v>1233.547299</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11677534.64</v>
+        <v>11719932.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.648316</v>
+        <v>13.651236</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569457259.36</v>
+        <v>1569792989.70</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999120</v>
+        <v>0.999065</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99912.00</v>
+        <v>99906.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1015.616926</v>
+        <v>1016.131926</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20312338.52</v>
+        <v>20322638.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.523100</v>
+        <v>724.515496</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004790018.16</v>
+        <v>3004758483.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.418316</v>
+        <v>1124.415980</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723482838.91</v>
+        <v>2723477179.03</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999120</v>
+        <v>0.999065</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99912.00</v>
+        <v>99906.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.677183</v>
+        <v>1.701789</v>
       </c>
       <c r="E27" s="66">
-        <v>314786294.00</v>
+        <v>336949912.00</v>
       </c>
       <c r="F27" s="65">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27" s="66">
-        <v>527954217.89</v>
+        <v>573417553.36</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>873.296999</v>
+        <v>882.398190</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4365611.70</v>
+        <v>4411108.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1215.042394</v>
+        <v>1202.915250</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>60752119.69</v>
+        <v>60145762.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.809650</v>
+        <v>1.808758</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361929933.71</v>
+        <v>361751638.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1369.312505</v>
+        <v>1373.563645</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5477250.02</v>
+        <v>5494254.58</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7321.192451</v>
+        <v>7321.415019</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533605111.76</v>
+        <v>533621333.66</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.242566</v>
+        <v>6974.483009</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173191365.64</v>
+        <v>173197336.57</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20566.788289</v>
+        <v>20567.789995</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>334580511.89</v>
+        <v>334596807.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1162.642302</v>
+        <v>1166.135364</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5813211.51</v>
+        <v>5830676.82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1161.642304</v>
+        <v>1165.135366</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5808211.52</v>
+        <v>5825676.83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1038.741558</v>
+        <v>1041.613441</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26072413.10</v>
+        <v>26144497.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694530</v>
+        <v>1.694699</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231592836.85</v>
+        <v>231615878.60</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1229.997948</v>
+        <v>1231.514086</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>327874403.13</v>
+        <v>328278552.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3618.725572</v>
+        <v>3618.715503</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>738220016.65</v>
+        <v>738217962.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3636.595517</v>
+        <v>3594.527700</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>255158087.88</v>
+        <v>252206441.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6807.962410</v>
+        <v>6794.329076</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>190728750.02</v>
+        <v>190346804.80</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.110009</v>
+        <v>0.109995</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34745092.20</v>
+        <v>34740626.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947179</v>
+        <v>1.947543</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242659704.72</v>
+        <v>242705061.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.604238</v>
+        <v>5.605179</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59432272.44</v>
+        <v>59442247.98</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465189</v>
+        <v>0.465234</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1651954057.27</v>
+        <v>1652112895.72</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008912</v>
+        <v>0.008938</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>606277098.28</v>
+        <v>608039014.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.108866</v>
+        <v>0.108736</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>156635.61</v>
+        <v>156448.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.442067</v>
+        <v>0.443134</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>604739.88</v>
+        <v>606200.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1776.352858</v>
+        <v>1777.242617</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>509726229.00</v>
+        <v>509981546.30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16916.609680</v>
+        <v>16922.561397</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370423002.16</v>
+        <v>370553326.92</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.284360</v>
+        <v>1.288167</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12860296.41</v>
+        <v>12898416.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7522.992367</v>
+        <v>7522.277402</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44528591.82</v>
+        <v>44524359.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.335788</v>
+        <v>7.338231</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>242258425.43</v>
+        <v>242339096.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.036423</v>
+        <v>0.027154</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>41166.37</v>
+        <v>30689.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.375069</v>
+        <v>6.387761</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>109856879.44</v>
+        <v>110075592.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990240</v>
+        <v>0.990418</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59414380.64</v>
+        <v>59425103.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.590954</v>
+        <v>1.590927</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137631099.87</v>
+        <v>137628702.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.621262</v>
+        <v>8.622138</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344850487.91</v>
+        <v>344885513.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.687876</v>
+        <v>0.688025</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>687876.09</v>
+        <v>688024.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.863910</v>
+        <v>0.864079</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>746363.03</v>
+        <v>746508.59</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.244390</v>
+        <v>2.244238</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170615967.11</v>
+        <v>170604386.09</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.712839</v>
+        <v>5.716571</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1623333654.20</v>
+        <v>1624394121.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.351219</v>
+        <v>1.354181</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2665451712.93</v>
+        <v>2671295325.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296231</v>
+        <v>1.296211</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744603113.27</v>
+        <v>1744576825.29</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975285</v>
+        <v>0.975666</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153607413.71</v>
+        <v>153667449.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>6.022915</v>
+        <v>6.026468</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6611308201.01</v>
+        <v>6615208226.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1514.861860</v>
+        <v>1514.895999</v>
       </c>
       <c r="E68" s="66">
         <v>904285.00</v>
@@ -2035,12 +2035,12 @@
         <v>245</v>
       </c>
       <c r="G68" s="66">
-        <v>1369866857.43</v>
+        <v>1369897728.32</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.179249</v>
+        <v>6.176634</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2616075385.53</v>
+        <v>2614968166.22</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.095988</v>
+        <v>4.096131</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2595053988.57</v>
+        <v>2595144669.15</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.775799</v>
+        <v>6.779529</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>319003338.62</v>
+        <v>319178948.83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792410</v>
+        <v>1.792419</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444779751.50</v>
+        <v>444781896.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.442251</v>
+        <v>18.440400</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20246732.89</v>
+        <v>20244700.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.157175</v>
+        <v>3.160064</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>553378964.61</v>
+        <v>553885274.90</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.594298</v>
+        <v>14.598742</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6454410170.92</v>
+        <v>6456375412.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.594669</v>
+        <v>6.595176</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2911429829.83</v>
+        <v>2911653906.57</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1362.240211</v>
+        <v>1362.150521</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393160233.90</v>
+        <v>393134348.21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232330</v>
+        <v>5.232458</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355914584.60</v>
+        <v>355923314.11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>439.487000</v>
+        <v>439.156100</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>43948.70</v>
+        <v>43915.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7077.666000</v>
+        <v>7074.167000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70776.66</v>
+        <v>70741.67</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>182.308200</v>
+        <v>181.995700</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18230.82</v>
+        <v>18199.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.024619</v>
+        <v>46.135792</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1614957.87</v>
+        <v>1618858.80</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1220.073842</v>
+        <v>1224.279769</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>113466867.33</v>
+        <v>113858018.53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.020291</v>
+        <v>21.021235</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671215094.98</v>
+        <v>1671290109.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.427302</v>
+        <v>31.425881</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978594616.41</v>
+        <v>978550351.96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>45.978148</v>
+        <v>46.087960</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1613327.23</v>
+        <v>1617180.42</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.086464</v>
+        <v>1.089792</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>613851888.83</v>
+        <v>615732464.36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.708867</v>
+        <v>20.764752</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>208306004.06</v>
+        <v>208868134.76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.744814</v>
+        <v>19.749609</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3078413951.77</v>
+        <v>3079161614.48</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.014677</v>
+        <v>0.015041</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8082.51</v>
+        <v>8283.05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5678.128595</v>
+        <v>5679.714226</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5432833439.89</v>
+        <v>5434350571.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.335791</v>
+        <v>1.337019</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>217620534.09</v>
+        <v>217820546.29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778822</v>
+        <v>0.778917</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135909921.66</v>
+        <v>135926559.09</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.632220</v>
+        <v>30.631824</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1551546967.67</v>
+        <v>1551526903.28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.092132</v>
+        <v>1.092040</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55361283.75</v>
+        <v>55356660.94</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208705</v>
+        <v>1.208779</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298550187.20</v>
+        <v>298568488.86</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.599039</v>
+        <v>0.598981</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70290215.52</v>
+        <v>70283376.46</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.500489</v>
+        <v>52.497878</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>38993058.46</v>
+        <v>38991119.16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.945286</v>
+        <v>19.944862</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109592248.48</v>
+        <v>109589918.26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1005.377530</v>
+        <v>1007.553659</v>
       </c>
       <c r="E100" s="66">
         <v>67591.00</v>
@@ -2899,12 +2899,12 @@
         <v>4</v>
       </c>
       <c r="G100" s="66">
-        <v>67954472.61</v>
+        <v>68101559.36</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.611611</v>
+        <v>0.613618</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1284384.10</v>
+        <v>1288598.02</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841332034.94</v>
+        <v>1841408604.67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.955402</v>
+        <v>4.969941</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66420356.79</v>
+        <v>66615222.93</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.943789</v>
+        <v>13.943938</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174625588.57</v>
+        <v>174627449.56</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.365300</v>
+        <v>9.364938</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78524480.75</v>
+        <v>78521446.80</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.406349</v>
+        <v>14.406201</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933513797.42</v>
+        <v>933504209.96</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808220</v>
+        <v>8.808502</v>
       </c>
       <c r="E107" s="66">
         <v>79280717.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>698321989.38</v>
+        <v>698344341.42</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.943244</v>
+        <v>8.942011</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2911710499.53</v>
+        <v>2911309001.02</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.801953</v>
+        <v>29.808506</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661699345.39</v>
+        <v>661844853.04</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.780607</v>
+        <v>2.788463</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>294535452.18</v>
+        <v>295367638.45</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.366862</v>
+        <v>48.410883</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1839092649.36</v>
+        <v>1840766518.31</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.609862</v>
+        <v>11.609868</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147408858.74</v>
+        <v>147408935.90</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.903040</v>
+        <v>4.902909</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876817346.81</v>
+        <v>876793855.97</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.415246</v>
+        <v>39.476187</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40706253.15</v>
+        <v>40769190.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>126.380315</v>
+        <v>125.216864</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>485679.55</v>
+        <v>481208.41</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>32.092647</v>
+        <v>32.088326</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>96277942.35</v>
+        <v>96264977.46</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002306</v>
+        <v>0.002312</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>260912539.23</v>
+        <v>261685360.58</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.954411</v>
+        <v>31.956253</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355092883.38</v>
+        <v>355113353.60</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>400.789255</v>
+        <v>401.033220</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300380324.45</v>
+        <v>300563169.69</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.409390</v>
+        <v>2.400738</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>496987607.44</v>
+        <v>495202991.83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912381</v>
+        <v>0.912548</v>
       </c>
       <c r="E121" s="66">
         <v>246086436.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>224524666.82</v>
+        <v>224565796.52</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.499861</v>
+        <v>1.499821</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55052292.92</v>
+        <v>55050830.66</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.019835</v>
+        <v>27.007136</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391340752.53</v>
+        <v>391156828.53</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027762</v>
+        <v>2.027923</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59048285.01</v>
+        <v>59052964.59</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.732054</v>
+        <v>21.735462</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119746792.48</v>
+        <v>119765567.93</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.660934</v>
+        <v>7.660620</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178508287.88</v>
+        <v>178500980.59</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.022435</v>
+        <v>5.022603</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214405110.84</v>
+        <v>214412264.23</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723116</v>
+        <v>2.723078</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368660103.88</v>
+        <v>368654953.11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.843979</v>
+        <v>23.846103</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451251714.22</v>
+        <v>451291913.28</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.408727</v>
+        <v>5.408245</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44202747.81</v>
+        <v>44198815.35</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348146</v>
+        <v>1.348190</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020955320.70</v>
+        <v>1020988448.33</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,21 +3754,21 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.949453</v>
+        <v>0.947606</v>
       </c>
       <c r="E132" s="66">
-        <v>91628362.00</v>
+        <v>91944333.00</v>
       </c>
       <c r="F132" s="65">
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>86996812.19</v>
+        <v>87126980.61</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.226700</v>
+        <v>12.228015</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172161108.99</v>
+        <v>172179628.10</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.217641</v>
+        <v>2.219261</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>157902459.69</v>
+        <v>158017822.79</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.443298</v>
+        <v>13.474083</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101590044.88</v>
+        <v>101822691.83</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.052150</v>
+        <v>94.066903</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24283324.72</v>
+        <v>24287133.66</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.660281</v>
+        <v>4.661772</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425441743.80</v>
+        <v>425577927.91</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.233957</v>
+        <v>18.238250</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>437979635.52</v>
+        <v>438082759.76</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27604.177439</v>
+        <v>27605.481676</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125157340.51</v>
+        <v>125163253.92</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4857.204596</v>
+        <v>4857.549390</v>
       </c>
       <c r="E141" s="66">
         <v>709751.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>3447405819.42</v>
+        <v>3447650537.23</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.196151</v>
+        <v>0.194051</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>196150.94</v>
+        <v>194050.83</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.387168</v>
+        <v>1.388450</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>150037761.96</v>
+        <v>150176445.29</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.920627</v>
+        <v>15.920509</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156602599.72</v>
+        <v>1156594063.10</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.093374</v>
+        <v>16.089376</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5745518879.04</v>
+        <v>5744091676.81</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3292.781348</v>
+        <v>3293.487913</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193658349.43</v>
+        <v>193699904.64</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c t="n" r="D147">
-        <v>0.977862</v>
+        <v>0.977865</v>
       </c>
       <c r="E147" s="66">
         <v>431000000.00</v>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421458732.07</v>
+        <v>421459703.80</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.318113</v>
+        <v>1.322458</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>527768914.68</v>
+        <v>529508688.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.035354</v>
+        <v>1.035137</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13497617175.11</v>
+        <v>13494793207.19</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.921014</v>
+        <v>0.920762</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13627195247.10</v>
+        <v>13623466634.49</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1926.488365</v>
+        <v>1926.337126</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41010598.84</v>
+        <v>41007379.30</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.582002</v>
+        <v>1.584096</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60858861.57</v>
+        <v>60939407.31</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6765.410351</v>
+        <v>6766.241784</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964409245.59</v>
+        <v>964527766.35</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.192637</v>
+        <v>1926.197019</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337732838.43</v>
+        <v>337733606.76</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17336.891304</v>
+        <v>17339.280250</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504574002.23</v>
+        <v>2504919121.27</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20306.681971</v>
+        <v>20308.980206</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185075099.48</v>
+        <v>185096045.60</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15349.926951</v>
+        <v>15350.304722</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320352975.46</v>
+        <v>320360859.55</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1162.437335</v>
+        <v>1161.857099</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5917968.47</v>
+        <v>5915014.49</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.441460</v>
+        <v>3675.676471</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719103797.00</v>
+        <v>719149777.25</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200850.681717</v>
+        <v>200850.568660</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602091670.19</v>
+        <v>4602089079.70</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.481522</v>
+        <v>33.517873</v>
       </c>
       <c r="E162" s="66">
         <v>18098207.00</v>
@@ -4573,12 +4573,12 @@
         <v>27</v>
       </c>
       <c r="G162" s="66">
-        <v>605955514.65</v>
+        <v>606613412.45</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.481628</v>
+        <v>80.482525</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396406385.11</v>
+        <v>396410802.12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400645</v>
+        <v>1.400842</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154395580.26</v>
+        <v>154417314.97</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.512038</v>
+        <v>2579.653865</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438519625.99</v>
+        <v>438543736.64</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731295</v>
+        <v>1678.731302</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092787.55</v>
+        <v>927092791.34</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027101</v>
+        <v>1.027116</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970602423.01</v>
+        <v>970616362.91</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1046.733867</v>
+        <v>1046.697364</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114425806.19</v>
+        <v>114421815.71</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.861847</v>
+        <v>75.910944</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65898075.90</v>
+        <v>65940724.96</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188007</v>
+        <v>3.188032</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977067104.45</v>
+        <v>977074677.21</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,21 +4807,21 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2980.345211</v>
+        <v>2980.604993</v>
       </c>
       <c r="E171" s="66">
-        <v>736375.00</v>
+        <v>698493.00</v>
       </c>
       <c r="F171" s="65">
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2194651704.63</v>
+        <v>2081931723.58</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4355.335944</v>
+        <v>4385.130338</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19337691.59</v>
+        <v>19469978.70</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,21 +4861,21 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63324.883775</v>
+        <v>63233.891486</v>
       </c>
       <c r="E173" s="66">
-        <v>18553.00</v>
+        <v>18709.00</v>
       </c>
       <c r="F173" s="65">
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1174866568.68</v>
+        <v>1183042875.82</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.247972</v>
+        <v>8193.174380</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148977827.87</v>
+        <v>148976489.75</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>46180.708708</v>
+        <v>46173.857932</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>3023127734.15</v>
+        <v>3022679261.79</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11590.726710</v>
+        <v>11590.588871</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675487446.47</v>
+        <v>2675455628.98</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2487.707837</v>
+        <v>2487.399775</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92928326.26</v>
+        <v>92916818.61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.760178</v>
+        <v>2705.752044</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459676185.08</v>
+        <v>459674803.23</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3495.954891</v>
+        <v>3495.714105</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20755484.19</v>
+        <v>20754054.64</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3296.470609</v>
+        <v>3296.435827</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6854410673.24</v>
+        <v>6854338351.66</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994678</v>
+        <v>0.994659</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928427242.98</v>
+        <v>928409454.12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4660.939031</v>
+        <v>4660.894338</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70258994.96</v>
+        <v>70258321.25</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.179493</v>
+        <v>1.182131</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2386527.91</v>
+        <v>2391865.30</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.707283</v>
+        <v>3592.704728</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917243318.30</v>
+        <v>917242665.93</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211434</v>
+        <v>1.211405</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226619830.91</v>
+        <v>226614414.95</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.225348</v>
+        <v>1331.349588</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502549549.76</v>
+        <v>502596451.52</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.290548</v>
+        <v>1109.280752</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721073159.39</v>
+        <v>1721057961.37</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.936564</v>
+        <v>74.936296</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872860942.06</v>
+        <v>872857824.42</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.224903</v>
+        <v>10.215968</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>453071962.02</v>
+        <v>452676057.96</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.204591</v>
+        <v>14.205801</v>
       </c>
       <c r="E190" s="66">
         <v>145515811.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2066992519.05</v>
+        <v>2067168608.41</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7568.545803</v>
+        <v>7555.070374</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>283502588.69</v>
+        <v>282997826.07</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.915786</v>
+        <v>1.915740</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26222124.16</v>
+        <v>26221496.54</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441708</v>
+        <v>2.441727</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206107102.35</v>
+        <v>206108727.74</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.331431</v>
+        <v>44.331708</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>564513777.44</v>
+        <v>564517309.87</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14894.428659</v>
+        <v>14895.877404</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6208295753.77</v>
+        <v>6208899619.61</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6274.880453</v>
+        <v>6276.374396</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39782742.07</v>
+        <v>39792213.67</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.360473</v>
+        <v>2933.430626</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077549436.23</v>
+        <v>1077575206.30</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223903</v>
+        <v>1.223894</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523009333.83</v>
+        <v>523005224.41</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323386</v>
+        <v>1.323574</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121751529.82</v>
+        <v>121768843.09</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.368405</v>
+        <v>7.365578</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2812078782.12</v>
+        <v>2810999771.74</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>1002.584739</v>
+        <v>1002.593851</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>449980082.70</v>
+        <v>449984172.16</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2515.634317</v>
+        <v>2521.841495</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>516037098.72</v>
+        <v>517310389.52</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>1.003234</v>
+        <v>1.004209</v>
       </c>
       <c r="E205" s="66">
-        <v>23381511.00</v>
+        <v>336560675.00</v>
       </c>
       <c r="F205" s="65">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="G205" s="66">
-        <v>23457127.44</v>
+        <v>337977130.08</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>0.004400</v>
+        <v>0.004393</v>
       </c>
       <c r="E206" s="66">
         <v>67618383967.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>297491412.22</v>
+        <v>297074459.03</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>20.820531</v>
+        <v>20.819633</v>
       </c>
       <c r="E207" s="66">
         <v>81092133.00</v>
@@ -5788,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>1688381228.55</v>
+        <v>1688308428.81</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>3.358977</v>
+        <v>3.358999</v>
       </c>
       <c r="E208" s="66">
         <v>21323550.00</v>
@@ -5815,12 +5815,12 @@
         <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>71625310.12</v>
+        <v>71625773.58</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>7703.622338</v>
+        <v>7708.340010</v>
       </c>
       <c r="E209" s="66">
         <v>197052.47</v>
@@ -5842,12 +5842,12 @@
         <v>36</v>
       </c>
       <c r="G209" s="66">
-        <v>1518017840.38</v>
+        <v>1518947469.40</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.844542</v>
+        <v>1.844688</v>
       </c>
       <c r="E210" s="66">
         <v>601179729.00</v>
@@ -5869,12 +5869,12 @@
         <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>1108901167.33</v>
+        <v>1108988813.36</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>20.587188</v>
+        <v>20.895862</v>
       </c>
       <c r="E211" s="66">
         <v>377.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>7761.37</v>
+        <v>7877.74</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.751125</v>
+        <v>1.756821</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>175112.53</v>
+        <v>175682.14</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>1.751284</v>
+        <v>1.756980</v>
       </c>
       <c r="E213" s="66">
         <v>100000.00</v>
@@ -5950,12 +5950,12 @@
         <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>175128.36</v>
+        <v>175697.97</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>61.301240</v>
+        <v>61.295160</v>
       </c>
       <c r="E214" s="66">
         <v>2554914.00</v>
@@ -5977,12 +5977,12 @@
         <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>156619395.08</v>
+        <v>156603862.67</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>15.244222</v>
+        <v>15.253237</v>
       </c>
       <c r="E215" s="66">
         <v>248000220.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>3780570307.56</v>
+        <v>3782806240.76</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>1.800888</v>
+        <v>1.801131</v>
       </c>
       <c r="E216" s="66">
         <v>504995473.00</v>
@@ -6031,12 +6031,12 @@
         <v>8</v>
       </c>
       <c r="G216" s="66">
-        <v>909440480.48</v>
+        <v>909563081.97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>0.391864</v>
+        <v>0.391838</v>
       </c>
       <c r="E217" s="66">
         <v>402507.00</v>
@@ -6058,12 +6058,12 @@
         <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>157727.84</v>
+        <v>157717.51</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>9.876787</v>
+        <v>9.876214</v>
       </c>
       <c r="E218" s="66">
         <v>27178800.00</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>268439214.96</v>
+        <v>268423654.58</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.613250</v>
+        <v>15.612045</v>
       </c>
       <c r="E219" s="66">
         <v>10371838.00</v>
@@ -6112,12 +6112,12 @@
         <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>161938102.45</v>
+        <v>161925598.90</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>15.323896</v>
+        <v>15.323077</v>
       </c>
       <c r="E220" s="66">
         <v>19475841.00</v>
@@ -6139,12 +6139,12 @@
         <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>298445757.13</v>
+        <v>298429809.49</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>31.079821</v>
+        <v>31.075472</v>
       </c>
       <c r="E221" s="66">
         <v>9712281.00</v>
@@ -6166,12 +6166,12 @@
         <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>301855958.54</v>
+        <v>301813714.36</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>7.977145</v>
+        <v>8.070443</v>
       </c>
       <c r="E222" s="66">
         <v>12818249.00</v>
@@ -6193,12 +6193,12 @@
         <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>102253026.63</v>
+        <v>103448953.39</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>1659.752199</v>
+        <v>1659.746133</v>
       </c>
       <c r="E223" s="66">
         <v>330000.00</v>
@@ -6220,12 +6220,12 @@
         <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>547718225.74</v>
+        <v>547716223.95</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.169419</v>
+        <v>5.168690</v>
       </c>
       <c r="E224" s="66">
         <v>11867933.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>61350313.29</v>
+        <v>61341661.27</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.946662</v>
+        <v>0.946747</v>
       </c>
       <c r="E225" s="66">
         <v>130000000.00</v>
@@ -6274,12 +6274,12 @@
         <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>123066061.21</v>
+        <v>123077128.42</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>5.519489</v>
+        <v>5.515319</v>
       </c>
       <c r="E226" s="66">
         <v>103852814.00</v>
@@ -6301,12 +6301,12 @@
         <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>573214423.34</v>
+        <v>572781439.93</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>6078.71</v>
+        <v>6078.70</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>6.604079</v>
+        <v>6.603591</v>
       </c>
       <c r="E228" s="66">
         <v>11104667.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>73336102.65</v>
+        <v>73330679.48</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>26.509950</v>
+        <v>26.503488</v>
       </c>
       <c r="E229" s="66">
         <v>1038884.00</v>
@@ -6382,12 +6382,12 @@
         <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>27540762.98</v>
+        <v>27534049.13</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.850126</v>
+        <v>0.849913</v>
       </c>
       <c r="E230" s="66">
         <v>73432275.00</v>
@@ -6409,12 +6409,12 @@
         <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>62426690.85</v>
+        <v>62411020.71</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.711635</v>
+        <v>0.711690</v>
       </c>
       <c r="E231" s="66">
         <v>801655137.00</v>
@@ -6436,12 +6436,12 @@
         <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>570485891.43</v>
+        <v>570530274.44</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>12.020110</v>
+        <v>12.020056</v>
       </c>
       <c r="E232" s="66">
         <v>26235742.00</v>
@@ -6463,12 +6463,12 @@
         <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>315356511.74</v>
+        <v>315355090.32</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6490,12 +6490,12 @@
         <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>471.51</v>
+        <v>471.50</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1.556157</v>
+        <v>1.560910</v>
       </c>
       <c r="E234" s="66">
         <v>24022001.00</v>
@@ -6517,12 +6517,12 @@
         <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>37381997.71</v>
+        <v>37496189.92</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>2.571931</v>
+        <v>2.572292</v>
       </c>
       <c r="E235" s="66">
         <v>68085562.00</v>
@@ -6544,12 +6544,12 @@
         <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>175111384.32</v>
+        <v>175135963.98</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1062.013859</v>
+        <v>1063.123580</v>
       </c>
       <c r="E236" s="66">
         <v>20029.00</v>
@@ -6571,12 +6571,12 @@
         <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>21271075.58</v>
+        <v>21293302.18</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>3.246550</v>
+        <v>3.248149</v>
       </c>
       <c r="E237" s="66">
         <v>1427155857.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>4633332794.00</v>
+        <v>4635614382.19</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1703.217891</v>
+        <v>1697.512384</v>
       </c>
       <c r="E238" s="66">
         <v>97333.00</v>
@@ -6625,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>165779307.01</v>
+        <v>165223972.92</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>1.161107</v>
+        <v>1.161080</v>
       </c>
       <c r="E239" s="66">
         <v>1107173943.00</v>
@@ -6652,12 +6652,12 @@
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1285547013.38</v>
+        <v>1285517939.83</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>2.209430</v>
+        <v>2.188699</v>
       </c>
       <c r="E240" s="66">
         <v>296754544.00</v>
@@ -6679,12 +6679,12 @@
         <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>655658324.93</v>
+        <v>649506242.32</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1007.135101</v>
+        <v>1010.442767</v>
       </c>
       <c r="E241" s="66">
         <v>1431712.00</v>
@@ -6706,12 +6706,12 @@
         <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1441927410.08</v>
+        <v>1446663035.44</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>5.004464</v>
+        <v>5.004415</v>
       </c>
       <c r="E242" s="66">
         <v>395532870.00</v>
@@ -6733,12 +6733,12 @@
         <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1979430019.89</v>
+        <v>1979410506.09</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>1303.799168</v>
+        <v>1303.788516</v>
       </c>
       <c r="E243" s="66">
         <v>1467447.00</v>
@@ -6760,12 +6760,12 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1913256177.54</v>
+        <v>1913240545.87</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c t="inlineStr" r="B244">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="D244">
-        <v>26963.461119</v>
+        <v>26968.610097</v>
       </c>
       <c r="E244" s="66">
         <v>40026.00</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="G244" s="66">
-        <v>1079239494.74</v>
+        <v>1079445587.75</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.868791</v>
+        <v>7724.870121</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
@@ -280,12 +280,12 @@
         <v>564</v>
       </c>
       <c r="G3" s="66">
-        <v>1915790634.76</v>
+        <v>1915790964.70</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.263796</v>
+        <v>29.266003</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5086679738.00</v>
+        <v>5087063323.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.577053</v>
+        <v>0.572833</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>288526.41</v>
+        <v>286416.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11305.758134</v>
+        <v>11308.406849</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3335356930.14</v>
+        <v>3336138338.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5356.726176</v>
+        <v>5357.000541</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52228080.22</v>
+        <v>52230755.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24466.512729</v>
+        <v>24466.492493</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2023380602.70</v>
+        <v>2023378929.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9969.096251</v>
+        <v>9969.193386</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72933908.17</v>
+        <v>72934618.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198425</v>
+        <v>2.198366</v>
       </c>
       <c r="E10" s="66">
         <v>575359508.00</v>
@@ -469,12 +469,12 @@
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1264884566.36</v>
+        <v>1264850907.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.401261</v>
+        <v>1141.405393</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893946609.24</v>
+        <v>893949845.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>368.433143</v>
+        <v>368.965058</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>380959.87</v>
+        <v>381509.87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.359416</v>
+        <v>23.359149</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333707998.91</v>
+        <v>2333681325.88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.500442</v>
+        <v>24.498343</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701476441.82</v>
+        <v>2701245017.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.339952</v>
+        <v>8.340340</v>
       </c>
       <c r="E15" s="66">
         <v>11751343.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>98005638.61</v>
+        <v>98010208.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.472391</v>
+        <v>7.471649</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>549402813.35</v>
+        <v>549348322.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.814204</v>
+        <v>10.814158</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164651775.79</v>
+        <v>164651064.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>966.141623</v>
+        <v>965.869355</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41590464.58</v>
+        <v>41578743.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1233.547299</v>
+        <v>1235.029949</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11719932.89</v>
+        <v>11734019.55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.651236</v>
+        <v>13.651666</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569792989.70</v>
+        <v>1569842396.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999065</v>
+        <v>0.999011</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99906.53</v>
+        <v>99901.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1016.131926</v>
+        <v>1016.650114</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20322638.52</v>
+        <v>20333002.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.515496</v>
+        <v>724.507915</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004758483.15</v>
+        <v>3004727043.14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.415980</v>
+        <v>1124.413840</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723477179.03</v>
+        <v>2723471997.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999065</v>
+        <v>0.999011</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99906.53</v>
+        <v>99901.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.701789</v>
+        <v>1.702707</v>
       </c>
       <c r="E27" s="66">
         <v>336949912.00</v>
@@ -928,12 +928,12 @@
         <v>22</v>
       </c>
       <c r="G27" s="66">
-        <v>573417553.36</v>
+        <v>573726855.24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>882.398190</v>
+        <v>883.623361</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4411108.55</v>
+        <v>4417233.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1202.915250</v>
+        <v>1197.514081</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>60145762.49</v>
+        <v>59875704.03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.808758</v>
+        <v>1.808810</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361751638.17</v>
+        <v>361761977.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1373.563645</v>
+        <v>1374.777188</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5494254.58</v>
+        <v>5499108.75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7321.415019</v>
+        <v>7321.276432</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533621333.66</v>
+        <v>533611232.76</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.483009</v>
+        <v>6974.744292</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173197336.57</v>
+        <v>173203825.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20567.789995</v>
+        <v>20568.035451</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>334596807.64</v>
+        <v>334600800.71</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1166.135364</v>
+        <v>1167.301662</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5830676.82</v>
+        <v>5836508.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1165.135366</v>
+        <v>1166.301664</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5825676.83</v>
+        <v>5831508.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1041.613441</v>
+        <v>1041.537725</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26144497.38</v>
+        <v>26142596.91</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694699</v>
+        <v>1.694668</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231615878.60</v>
+        <v>231611630.65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1231.514086</v>
+        <v>1232.775291</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>328278552.34</v>
+        <v>328614745.51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3618.715503</v>
+        <v>3618.685915</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>738217962.61</v>
+        <v>738211926.57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3594.527700</v>
+        <v>3647.345521</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>252206441.57</v>
+        <v>255912351.13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6794.329076</v>
+        <v>6782.000950</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>190346804.80</v>
+        <v>190001425.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.109995</v>
+        <v>0.109981</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34740626.76</v>
+        <v>34736146.91</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947543</v>
+        <v>1.947593</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242705061.76</v>
+        <v>242711252.27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.605179</v>
+        <v>5.605262</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59442247.98</v>
+        <v>59443130.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465234</v>
+        <v>0.465227</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652112895.72</v>
+        <v>1652089700.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008938</v>
+        <v>0.008929</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>608039014.51</v>
+        <v>607424561.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.108736</v>
+        <v>0.081614</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>156448.91</v>
+        <v>117425.00</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.443134</v>
+        <v>0.443236</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>606200.14</v>
+        <v>606339.79</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1777.242617</v>
+        <v>1777.790804</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>509981546.30</v>
+        <v>510138849.13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16922.561397</v>
+        <v>16924.315256</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370553326.92</v>
+        <v>370591731.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.288167</v>
+        <v>1.289226</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12898416.46</v>
+        <v>12909019.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7522.277402</v>
+        <v>7521.562458</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44524359.94</v>
+        <v>44520128.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.338231</v>
+        <v>7.340113</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>242339096.66</v>
+        <v>242401238.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.027154</v>
+        <v>0.016968</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>30689.87</v>
+        <v>19177.25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.387761</v>
+        <v>6.392053</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>110075592.76</v>
+        <v>110149550.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990418</v>
+        <v>0.990440</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59425103.19</v>
+        <v>59426370.70</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.590927</v>
+        <v>1.590895</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137628702.25</v>
+        <v>137625945.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.622138</v>
+        <v>8.621948</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344885513.58</v>
+        <v>344877936.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.688025</v>
+        <v>0.686611</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>688024.77</v>
+        <v>686611.14</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.864079</v>
+        <v>0.862440</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>746508.59</v>
+        <v>745093.30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.244238</v>
+        <v>2.244077</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170604386.09</v>
+        <v>170592147.47</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.716571</v>
+        <v>5.716899</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1624394121.08</v>
+        <v>1624487430.93</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.354181</v>
+        <v>1.355156</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2671295325.21</v>
+        <v>2673217725.35</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296211</v>
+        <v>1.296191</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744576825.29</v>
+        <v>1744549280.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975666</v>
+        <v>0.975686</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153667449.79</v>
+        <v>153670506.32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>6.026468</v>
+        <v>6.027830</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6615208226.99</v>
+        <v>6616703945.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,21 +2026,21 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1514.895999</v>
+        <v>1514.936963</v>
       </c>
       <c r="E68" s="66">
-        <v>904285.00</v>
+        <v>957363.00</v>
       </c>
       <c r="F68" s="65">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G68" s="66">
-        <v>1369897728.32</v>
+        <v>1450344595.89</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.176634</v>
+        <v>6.172716</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2614968166.22</v>
+        <v>2613309442.15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.096131</v>
+        <v>4.098974</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2595144669.15</v>
+        <v>2596946225.94</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.779529</v>
+        <v>6.782601</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>319178948.83</v>
+        <v>319323559.01</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792419</v>
+        <v>1.792402</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444781896.29</v>
+        <v>444777622.78</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.440400</v>
+        <v>18.435615</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20244700.54</v>
+        <v>20239447.22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.160064</v>
+        <v>3.161291</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>553885274.90</v>
+        <v>554100410.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.598742</v>
+        <v>14.600050</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6456375412.27</v>
+        <v>6456953809.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.595176</v>
+        <v>6.601109</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2911653906.57</v>
+        <v>2914273122.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1362.150521</v>
+        <v>1362.087131</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393134348.21</v>
+        <v>393116053.17</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232458</v>
+        <v>5.232403</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355923314.11</v>
+        <v>355919566.97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>439.156100</v>
+        <v>438.825200</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>43915.61</v>
+        <v>43882.52</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7074.167000</v>
+        <v>7070.668000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70741.67</v>
+        <v>70706.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>181.995700</v>
+        <v>181.683200</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18199.57</v>
+        <v>18168.32</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.135792</v>
+        <v>46.158611</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1618858.80</v>
+        <v>1619659.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1224.279769</v>
+        <v>1225.783250</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>113858018.53</v>
+        <v>113997842.28</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.021235</v>
+        <v>21.021187</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671290109.77</v>
+        <v>1671286341.60</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.425881</v>
+        <v>31.423994</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978550351.96</v>
+        <v>978491621.69</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.087960</v>
+        <v>46.109441</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1617180.42</v>
+        <v>1617934.19</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.089792</v>
+        <v>1.090925</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>615732464.36</v>
+        <v>616372645.20</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.764752</v>
+        <v>20.781445</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>208868134.76</v>
+        <v>209036047.76</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.749609</v>
+        <v>19.751412</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3079161614.48</v>
+        <v>3079442665.30</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.015041</v>
+        <v>0.015163</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8283.05</v>
+        <v>8349.94</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5679.714226</v>
+        <v>5680.440978</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5434350571.49</v>
+        <v>5435045927.49</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.337019</v>
+        <v>1.338095</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>217820546.29</v>
+        <v>217995823.47</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778917</v>
+        <v>0.778908</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135926559.09</v>
+        <v>135924997.06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.631824</v>
+        <v>30.631222</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1551526903.28</v>
+        <v>1551496423.34</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.092040</v>
+        <v>1.091827</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55356660.94</v>
+        <v>55345824.42</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208779</v>
+        <v>1.208766</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298568488.86</v>
+        <v>298565165.79</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.598981</v>
+        <v>0.598921</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70283376.46</v>
+        <v>70276365.24</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.497878</v>
+        <v>52.494749</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>38991119.16</v>
+        <v>38988794.73</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.944862</v>
+        <v>19.944438</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109589918.26</v>
+        <v>109587588.04</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1007.553659</v>
+        <v>1007.890899</v>
       </c>
       <c r="E100" s="66">
         <v>67591.00</v>
@@ -2899,12 +2899,12 @@
         <v>4</v>
       </c>
       <c r="G100" s="66">
-        <v>68101559.36</v>
+        <v>68124353.78</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.613618</v>
+        <v>0.614106</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1288598.02</v>
+        <v>1289621.87</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841408604.67</v>
+        <v>1841422922.85</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.969941</v>
+        <v>4.974998</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66615222.93</v>
+        <v>66683011.50</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.943938</v>
+        <v>13.943752</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174627449.56</v>
+        <v>174625118.14</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.364938</v>
+        <v>9.364576</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78521446.80</v>
+        <v>78518412.89</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.406201</v>
+        <v>14.405683</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933504209.96</v>
+        <v>933470614.67</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808502</v>
+        <v>8.808504</v>
       </c>
       <c r="E107" s="66">
         <v>79280717.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>698344341.42</v>
+        <v>698344521.72</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.942011</v>
+        <v>8.940539</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2911309001.02</v>
+        <v>2910829933.95</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.808506</v>
+        <v>29.813525</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661844853.04</v>
+        <v>661956275.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.788463</v>
+        <v>2.791243</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>295367638.45</v>
+        <v>295662063.07</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.410883</v>
+        <v>48.423588</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1840766518.31</v>
+        <v>1841249592.61</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.609868</v>
+        <v>11.609661</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147408935.90</v>
+        <v>147406315.15</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.902909</v>
+        <v>4.902878</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876793855.97</v>
+        <v>876788286.40</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.476187</v>
+        <v>39.496113</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40769190.33</v>
+        <v>40789768.17</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>125.216864</v>
+        <v>123.787385</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>481208.41</v>
+        <v>475714.92</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>32.088326</v>
+        <v>32.082178</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>96264977.46</v>
+        <v>96246534.66</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002312</v>
+        <v>0.002315</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>261685360.58</v>
+        <v>261958280.58</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956253</v>
+        <v>31.956297</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355113353.60</v>
+        <v>355113834.07</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>401.033220</v>
+        <v>401.161021</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300563169.69</v>
+        <v>300658952.83</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.400738</v>
+        <v>2.390834</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>495202991.83</v>
+        <v>493159988.44</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912548</v>
+        <v>0.912571</v>
       </c>
       <c r="E121" s="66">
         <v>246086436.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>224565796.52</v>
+        <v>224571262.46</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.499821</v>
+        <v>1.499747</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55050830.66</v>
+        <v>55048120.90</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.007136</v>
+        <v>27.007881</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391156828.53</v>
+        <v>391167615.32</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027923</v>
+        <v>2.027908</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59052964.59</v>
+        <v>59052527.23</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.735462</v>
+        <v>21.743910</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119765567.93</v>
+        <v>119812116.99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.660620</v>
+        <v>7.660289</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178500980.59</v>
+        <v>178493250.43</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.022603</v>
+        <v>5.022513</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214412264.23</v>
+        <v>214408450.00</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723078</v>
+        <v>2.723022</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368654953.11</v>
+        <v>368647422.53</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.846103</v>
+        <v>23.846002</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451291913.28</v>
+        <v>451289993.65</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.408245</v>
+        <v>5.407764</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44198815.35</v>
+        <v>44194883.01</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348190</v>
+        <v>1.348151</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020988448.33</v>
+        <v>1020958863.71</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.947606</v>
+        <v>0.947341</v>
       </c>
       <c r="E132" s="66">
         <v>91944333.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87126980.61</v>
+        <v>87102613.41</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.228015</v>
+        <v>12.229126</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172179628.10</v>
+        <v>172195268.44</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.219261</v>
+        <v>2.219771</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>158017822.79</v>
+        <v>158054099.63</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.474083</v>
+        <v>13.478351</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101822691.83</v>
+        <v>101854940.18</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.066903</v>
+        <v>94.062424</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24287133.66</v>
+        <v>24285977.20</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.661772</v>
+        <v>4.662221</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425577927.91</v>
+        <v>425618833.70</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.238250</v>
+        <v>18.239531</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>438082759.76</v>
+        <v>438113534.56</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27605.481676</v>
+        <v>27605.149960</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125163253.92</v>
+        <v>125161749.92</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4857.549390</v>
+        <v>4857.704413</v>
       </c>
       <c r="E141" s="66">
         <v>709751.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>3447650537.23</v>
+        <v>3447760564.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.194051</v>
+        <v>0.191951</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>194050.83</v>
+        <v>191950.72</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.388450</v>
+        <v>1.388473</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>150176445.29</v>
+        <v>150178889.69</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.920509</v>
+        <v>15.920663</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156594063.10</v>
+        <v>1156605238.87</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.089376</v>
+        <v>16.089645</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5744091676.81</v>
+        <v>5744187469.74</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3293.487913</v>
+        <v>3293.653612</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193699904.64</v>
+        <v>193709649.87</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c t="n" r="D147">
-        <v>0.977865</v>
+        <v>0.977866</v>
       </c>
       <c r="E147" s="66">
         <v>431000000.00</v>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421459703.80</v>
+        <v>421460087.95</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.322458</v>
+        <v>1.324176</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>529508688.42</v>
+        <v>530196485.28</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.035137</v>
+        <v>1.034921</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13494793207.19</v>
+        <v>13491981710.71</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.920762</v>
+        <v>0.920512</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13623466634.49</v>
+        <v>13619766257.08</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1926.337126</v>
+        <v>1926.304169</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41007379.30</v>
+        <v>41006677.73</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.584096</v>
+        <v>1.584047</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60939407.31</v>
+        <v>60937500.99</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6766.241784</v>
+        <v>6766.391577</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964527766.35</v>
+        <v>964549119.27</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.197019</v>
+        <v>1926.198485</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337733606.76</v>
+        <v>337733863.76</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17339.280250</v>
+        <v>17340.079395</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2504919121.27</v>
+        <v>2505034569.81</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20308.980206</v>
+        <v>20309.778187</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185096045.60</v>
+        <v>185103318.40</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15350.304722</v>
+        <v>15350.434916</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320360859.55</v>
+        <v>320363576.70</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1161.857099</v>
+        <v>1163.238104</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5915014.49</v>
+        <v>5922045.19</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.676471</v>
+        <v>3675.755082</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719149777.25</v>
+        <v>719165157.53</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200850.568660</v>
+        <v>200850.455652</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602089079.70</v>
+        <v>4602086490.36</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.517873</v>
+        <v>33.532089</v>
       </c>
       <c r="E162" s="66">
         <v>18098207.00</v>
@@ -4573,12 +4573,12 @@
         <v>27</v>
       </c>
       <c r="G162" s="66">
-        <v>606613412.45</v>
+        <v>606870683.24</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.482525</v>
+        <v>80.485020</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396410802.12</v>
+        <v>396423092.51</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400842</v>
+        <v>1.400902</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154417314.97</v>
+        <v>154423870.38</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.653865</v>
+        <v>2579.690257</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438543736.64</v>
+        <v>438549923.43</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731302</v>
+        <v>1678.731304</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092791.34</v>
+        <v>927092792.44</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027116</v>
+        <v>1.027103</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970616362.91</v>
+        <v>970604714.32</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1046.697364</v>
+        <v>1046.654739</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114421815.71</v>
+        <v>114417156.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.910944</v>
+        <v>75.922819</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65940724.96</v>
+        <v>65951040.40</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188032</v>
+        <v>3.188014</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977074677.21</v>
+        <v>977069119.47</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2980.604993</v>
+        <v>2980.355790</v>
       </c>
       <c r="E171" s="66">
         <v>698493.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2081931723.58</v>
+        <v>2081757657.08</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4385.130338</v>
+        <v>4369.622158</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19469978.70</v>
+        <v>19401122.38</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63233.891486</v>
+        <v>63235.105294</v>
       </c>
       <c r="E173" s="66">
         <v>18709.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1183042875.82</v>
+        <v>1183065584.94</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.174380</v>
+        <v>8193.100788</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148976489.75</v>
+        <v>148975151.63</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>46173.857932</v>
+        <v>46173.667364</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>3022679261.79</v>
+        <v>3022666786.62</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11590.588871</v>
+        <v>11590.451031</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675455628.98</v>
+        <v>2675423811.49</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2487.399775</v>
+        <v>2487.009457</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92916818.61</v>
+        <v>92902238.27</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.752044</v>
+        <v>2705.598475</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459674803.23</v>
+        <v>459648713.77</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3495.714105</v>
+        <v>3495.720332</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20754054.64</v>
+        <v>20754091.61</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3296.435827</v>
+        <v>3296.258670</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6854338351.66</v>
+        <v>6853969984.50</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994659</v>
+        <v>0.994632</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928409454.12</v>
+        <v>928384580.83</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4660.894338</v>
+        <v>4660.849645</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70258321.25</v>
+        <v>70257647.55</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.182131</v>
+        <v>1.182444</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2391865.30</v>
+        <v>2392498.92</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.704728</v>
+        <v>3592.702173</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917242665.93</v>
+        <v>917242013.56</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211405</v>
+        <v>1.211376</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226614414.95</v>
+        <v>226608967.14</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.349588</v>
+        <v>1331.377030</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502596451.52</v>
+        <v>502606811.29</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.280752</v>
+        <v>1109.270776</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721057961.37</v>
+        <v>1721042482.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.936296</v>
+        <v>74.935836</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872857824.42</v>
+        <v>872852472.66</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.215968</v>
+        <v>10.208752</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>452676057.96</v>
+        <v>452356305.34</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.205801</v>
+        <v>14.205480</v>
       </c>
       <c r="E190" s="66">
         <v>145515811.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2067168608.41</v>
+        <v>2067121902.30</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7555.070374</v>
+        <v>7543.731423</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>282997826.07</v>
+        <v>282573091.63</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.915740</v>
+        <v>1.915509</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26221496.54</v>
+        <v>26218326.13</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206108727.74</v>
+        <v>206108733.33</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.331708</v>
+        <v>44.329801</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>564517309.87</v>
+        <v>564493031.05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14895.877404</v>
+        <v>14896.318948</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6208899619.61</v>
+        <v>6209083663.98</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6276.374396</v>
+        <v>6276.763965</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39792213.67</v>
+        <v>39794683.54</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.430626</v>
+        <v>2933.441536</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077575206.30</v>
+        <v>1077579214.07</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223894</v>
+        <v>1.223880</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>523005224.41</v>
+        <v>522999376.50</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323574</v>
+        <v>1.323587</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121768843.09</v>
+        <v>121770002.58</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.365578</v>
+        <v>7.379408</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2810999771.74</v>
+        <v>2816278089.41</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>1002.593851</v>
+        <v>1002.561805</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>449984172.16</v>
+        <v>449969789.18</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2521.841495</v>
+        <v>2524.570290</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>517310389.52</v>
+        <v>517870152.75</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>1.004209</v>
+        <v>1.005024</v>
       </c>
       <c r="E205" s="66">
-        <v>336560675.00</v>
+        <v>364346841.00</v>
       </c>
       <c r="F205" s="65">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="G205" s="66">
-        <v>337977130.08</v>
+        <v>366177200.80</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>0.004393</v>
+        <v>0.004386</v>
       </c>
       <c r="E206" s="66">
         <v>67618383967.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>297074459.03</v>
+        <v>296566891.14</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>20.819633</v>
+        <v>20.819884</v>
       </c>
       <c r="E207" s="66">
         <v>81092133.00</v>
@@ -5788,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>1688308428.81</v>
+        <v>1688328802.92</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>3.358999</v>
+        <v>3.358906</v>
       </c>
       <c r="E208" s="66">
         <v>21323550.00</v>
@@ -5815,12 +5815,12 @@
         <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>71625773.58</v>
+        <v>71623793.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,21 +5833,21 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>7708.340010</v>
+        <v>7710.360421</v>
       </c>
       <c r="E209" s="66">
         <v>197052.47</v>
       </c>
       <c r="F209" s="65">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G209" s="66">
-        <v>1518947469.40</v>
+        <v>1519345596.30</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.844688</v>
+        <v>1.844474</v>
       </c>
       <c r="E210" s="66">
         <v>601179729.00</v>
@@ -5869,12 +5869,12 @@
         <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>1108988813.36</v>
+        <v>1108860356.20</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>20.895862</v>
+        <v>20.999602</v>
       </c>
       <c r="E211" s="66">
         <v>377.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>7877.74</v>
+        <v>7916.85</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.756821</v>
+        <v>1.758693</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>175682.14</v>
+        <v>175869.32</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>1.756980</v>
+        <v>1.758852</v>
       </c>
       <c r="E213" s="66">
         <v>100000.00</v>
@@ -5950,12 +5950,12 @@
         <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>175697.97</v>
+        <v>175885.15</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>61.295160</v>
+        <v>61.290486</v>
       </c>
       <c r="E214" s="66">
         <v>2554914.00</v>
@@ -5977,12 +5977,12 @@
         <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>156603862.67</v>
+        <v>156591921.92</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>15.253237</v>
+        <v>15.256287</v>
       </c>
       <c r="E215" s="66">
         <v>248000220.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>3782806240.76</v>
+        <v>3783562544.28</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>1.801131</v>
+        <v>1.801199</v>
       </c>
       <c r="E216" s="66">
         <v>504995473.00</v>
@@ -6031,12 +6031,12 @@
         <v>8</v>
       </c>
       <c r="G216" s="66">
-        <v>909563081.97</v>
+        <v>909597126.38</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>0.391838</v>
+        <v>0.391459</v>
       </c>
       <c r="E217" s="66">
         <v>402507.00</v>
@@ -6058,12 +6058,12 @@
         <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>157717.51</v>
+        <v>157564.87</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>9.876214</v>
+        <v>9.875620</v>
       </c>
       <c r="E218" s="66">
         <v>27178800.00</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>268423654.58</v>
+        <v>268407488.60</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.612045</v>
+        <v>15.610942</v>
       </c>
       <c r="E219" s="66">
         <v>10371838.00</v>
@@ -6112,12 +6112,12 @@
         <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>161925598.90</v>
+        <v>161914160.79</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>15.323077</v>
+        <v>15.322398</v>
       </c>
       <c r="E220" s="66">
         <v>19475841.00</v>
@@ -6139,12 +6139,12 @@
         <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>298429809.49</v>
+        <v>298416586.08</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>31.075472</v>
+        <v>31.147909</v>
       </c>
       <c r="E221" s="66">
         <v>9712281.00</v>
@@ -6166,12 +6166,12 @@
         <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>301813714.36</v>
+        <v>302517245.25</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>8.070443</v>
+        <v>8.069914</v>
       </c>
       <c r="E222" s="66">
         <v>12818249.00</v>
@@ -6193,12 +6193,12 @@
         <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>103448953.39</v>
+        <v>103442173.27</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>1659.746133</v>
+        <v>1659.740067</v>
       </c>
       <c r="E223" s="66">
         <v>330000.00</v>
@@ -6220,12 +6220,12 @@
         <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>547716223.95</v>
+        <v>547714222.16</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.168690</v>
+        <v>5.170287</v>
       </c>
       <c r="E224" s="66">
         <v>11867933.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>61341661.27</v>
+        <v>61360617.91</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.946747</v>
+        <v>0.946770</v>
       </c>
       <c r="E225" s="66">
         <v>130000000.00</v>
@@ -6274,12 +6274,12 @@
         <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>123077128.42</v>
+        <v>123080042.81</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>5.515319</v>
+        <v>5.515314</v>
       </c>
       <c r="E226" s="66">
         <v>103852814.00</v>
@@ -6301,12 +6301,12 @@
         <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>572781439.93</v>
+        <v>572780859.78</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>6078.70</v>
+        <v>6078.69</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>6.603591</v>
+        <v>6.603103</v>
       </c>
       <c r="E228" s="66">
         <v>11104667.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>73330679.48</v>
+        <v>73325256.31</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>26.503488</v>
+        <v>26.500262</v>
       </c>
       <c r="E229" s="66">
         <v>1038884.00</v>
@@ -6382,12 +6382,12 @@
         <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>27534049.13</v>
+        <v>27530698.37</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.849913</v>
+        <v>0.850244</v>
       </c>
       <c r="E230" s="66">
         <v>73432275.00</v>
@@ -6409,12 +6409,12 @@
         <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>62411020.71</v>
+        <v>62435343.84</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.711690</v>
+        <v>0.711682</v>
       </c>
       <c r="E231" s="66">
         <v>801655137.00</v>
@@ -6436,12 +6436,12 @@
         <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>570530274.44</v>
+        <v>570523173.25</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>12.020056</v>
+        <v>12.020002</v>
       </c>
       <c r="E232" s="66">
         <v>26235742.00</v>
@@ -6463,12 +6463,12 @@
         <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>315355090.32</v>
+        <v>315353668.90</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6490,12 +6490,12 @@
         <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>471.50</v>
+        <v>471.49</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1.560910</v>
+        <v>1.562525</v>
       </c>
       <c r="E234" s="66">
         <v>24022001.00</v>
@@ -6517,12 +6517,12 @@
         <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>37496189.92</v>
+        <v>37534983.34</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>2.572292</v>
+        <v>2.572308</v>
       </c>
       <c r="E235" s="66">
         <v>68085562.00</v>
@@ -6544,12 +6544,12 @@
         <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>175135963.98</v>
+        <v>175137067.02</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1063.123580</v>
+        <v>1064.190903</v>
       </c>
       <c r="E236" s="66">
         <v>20029.00</v>
@@ -6571,12 +6571,12 @@
         <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>21293302.18</v>
+        <v>21314679.59</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>3.248149</v>
+        <v>3.248702</v>
       </c>
       <c r="E237" s="66">
         <v>1427155857.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>4635614382.19</v>
+        <v>4636403886.41</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1697.512384</v>
+        <v>1692.397256</v>
       </c>
       <c r="E238" s="66">
         <v>97333.00</v>
@@ -6625,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>165223972.92</v>
+        <v>164726102.07</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>1.161080</v>
+        <v>1.161050</v>
       </c>
       <c r="E239" s="66">
         <v>1107173943.00</v>
@@ -6652,12 +6652,12 @@
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1285517939.83</v>
+        <v>1285483796.10</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>2.188699</v>
+        <v>2.199156</v>
       </c>
       <c r="E240" s="66">
         <v>296754544.00</v>
@@ -6679,12 +6679,12 @@
         <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>649506242.32</v>
+        <v>652609477.23</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1010.442767</v>
+        <v>1011.545292</v>
       </c>
       <c r="E241" s="66">
         <v>1431712.00</v>
@@ -6706,12 +6706,12 @@
         <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1446663035.44</v>
+        <v>1448241533.47</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>5.004415</v>
+        <v>5.004343</v>
       </c>
       <c r="E242" s="66">
         <v>395532870.00</v>
@@ -6733,12 +6733,12 @@
         <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1979410506.09</v>
+        <v>1979382134.39</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>1303.788516</v>
+        <v>1303.777917</v>
       </c>
       <c r="E243" s="66">
         <v>1467447.00</v>
@@ -6760,12 +6760,12 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1913240545.87</v>
+        <v>1913224993.32</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c t="inlineStr" r="B244">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="D244">
-        <v>26968.610097</v>
+        <v>26970.035277</v>
       </c>
       <c r="E244" s="66">
         <v>40026.00</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="G244" s="66">
-        <v>1079445587.75</v>
+        <v>1079502631.98</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
+++ b/app/fonlar/tarihsel-veriler/gayrimenkul-yatirim-fonlari-tarihsel/data/gayrimenkul-yatirim-fonlari-tarihsel.xlsx
@@ -258,7 +258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B3">
         <is>
@@ -271,21 +271,21 @@
         </is>
       </c>
       <c t="n" r="D3">
-        <v>7724.870121</v>
+        <v>7724.867664</v>
       </c>
       <c r="E3" s="66">
         <v>248003.00</v>
       </c>
       <c r="F3" s="65">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G3" s="66">
-        <v>1915790964.70</v>
+        <v>1915790355.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B4">
         <is>
@@ -298,7 +298,7 @@
         </is>
       </c>
       <c t="n" r="D4">
-        <v>29.266003</v>
+        <v>29.259904</v>
       </c>
       <c r="E4" s="66">
         <v>173821594.00</v>
@@ -307,12 +307,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="66">
-        <v>5087063323.47</v>
+        <v>5086003157.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B5">
         <is>
@@ -325,7 +325,7 @@
         </is>
       </c>
       <c t="n" r="D5">
-        <v>0.572833</v>
+        <v>0.563588</v>
       </c>
       <c r="E5" s="66">
         <v>500000.00</v>
@@ -334,12 +334,12 @@
         <v>1</v>
       </c>
       <c r="G5" s="66">
-        <v>286416.38</v>
+        <v>281794.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B6">
         <is>
@@ -352,7 +352,7 @@
         </is>
       </c>
       <c t="n" r="D6">
-        <v>11308.406849</v>
+        <v>11311.352956</v>
       </c>
       <c r="E6" s="66">
         <v>295014.00</v>
@@ -361,12 +361,12 @@
         <v>5</v>
       </c>
       <c r="G6" s="66">
-        <v>3336138338.02</v>
+        <v>3337007480.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B7">
         <is>
@@ -379,7 +379,7 @@
         </is>
       </c>
       <c t="n" r="D7">
-        <v>5357.000541</v>
+        <v>5357.178904</v>
       </c>
       <c r="E7" s="66">
         <v>9750.00</v>
@@ -388,12 +388,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="66">
-        <v>52230755.27</v>
+        <v>52232494.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B8">
         <is>
@@ -406,7 +406,7 @@
         </is>
       </c>
       <c t="n" r="D8">
-        <v>24466.492493</v>
+        <v>24463.544671</v>
       </c>
       <c r="E8" s="66">
         <v>82700.00</v>
@@ -415,12 +415,12 @@
         <v>1</v>
       </c>
       <c r="G8" s="66">
-        <v>2023378929.16</v>
+        <v>2023135144.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B9">
         <is>
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c t="n" r="D9">
-        <v>9969.193386</v>
+        <v>9969.162210</v>
       </c>
       <c r="E9" s="66">
         <v>7316.00</v>
@@ -442,12 +442,12 @@
         <v>1</v>
       </c>
       <c r="G9" s="66">
-        <v>72934618.81</v>
+        <v>72934390.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B10">
         <is>
@@ -460,21 +460,21 @@
         </is>
       </c>
       <c t="n" r="D10">
-        <v>2.198366</v>
+        <v>2.198246</v>
       </c>
       <c r="E10" s="66">
-        <v>575359508.00</v>
+        <v>575959352.00</v>
       </c>
       <c r="F10" s="65">
         <v>2</v>
       </c>
       <c r="G10" s="66">
-        <v>1264850907.05</v>
+        <v>1266100056.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B11">
         <is>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c t="n" r="D11">
-        <v>1141.405393</v>
+        <v>1141.332847</v>
       </c>
       <c r="E11" s="66">
         <v>783201.00</v>
@@ -496,12 +496,12 @@
         <v>3</v>
       </c>
       <c r="G11" s="66">
-        <v>893949845.16</v>
+        <v>893893027.24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B12">
         <is>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c t="n" r="D12">
-        <v>368.965058</v>
+        <v>369.501818</v>
       </c>
       <c r="E12" s="66">
         <v>1034.00</v>
@@ -523,12 +523,12 @@
         <v>1</v>
       </c>
       <c r="G12" s="66">
-        <v>381509.87</v>
+        <v>382064.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B13">
         <is>
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c t="n" r="D13">
-        <v>23.359149</v>
+        <v>23.357252</v>
       </c>
       <c r="E13" s="66">
         <v>99904380.59</v>
@@ -550,12 +550,12 @@
         <v>15</v>
       </c>
       <c r="G13" s="66">
-        <v>2333681325.88</v>
+        <v>2333491783.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B14">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c t="n" r="D14">
-        <v>24.498343</v>
+        <v>24.493200</v>
       </c>
       <c r="E14" s="66">
         <v>110262355.37</v>
@@ -577,12 +577,12 @@
         <v>10</v>
       </c>
       <c r="G14" s="66">
-        <v>2701245017.87</v>
+        <v>2700677912.10</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B15">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c t="n" r="D15">
-        <v>8.340340</v>
+        <v>8.340684</v>
       </c>
       <c r="E15" s="66">
         <v>11751343.89</v>
@@ -604,12 +604,12 @@
         <v>8</v>
       </c>
       <c r="G15" s="66">
-        <v>98010208.78</v>
+        <v>98014241.86</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B16">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c t="n" r="D16">
-        <v>7.471649</v>
+        <v>7.469092</v>
       </c>
       <c r="E16" s="66">
         <v>73524371.00</v>
@@ -631,12 +631,12 @@
         <v>9</v>
       </c>
       <c r="G16" s="66">
-        <v>549348322.15</v>
+        <v>549160271.13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B17">
         <is>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c t="n" r="D17">
-        <v>10.814158</v>
+        <v>10.813756</v>
       </c>
       <c r="E17" s="66">
         <v>15225510.00</v>
@@ -658,12 +658,12 @@
         <v>1</v>
       </c>
       <c r="G17" s="66">
-        <v>164651064.05</v>
+        <v>164644954.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B18">
         <is>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c t="n" r="D18">
-        <v>965.869355</v>
+        <v>965.321096</v>
       </c>
       <c r="E18" s="66">
         <v>43048.00</v>
@@ -685,12 +685,12 @@
         <v>3</v>
       </c>
       <c r="G18" s="66">
-        <v>41578743.99</v>
+        <v>41555142.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B19">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c t="n" r="D19">
-        <v>1235.029949</v>
+        <v>1236.481469</v>
       </c>
       <c r="E19" s="66">
         <v>9501.00</v>
@@ -712,12 +712,12 @@
         <v>4</v>
       </c>
       <c r="G19" s="66">
-        <v>11734019.55</v>
+        <v>11747810.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B20">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c t="n" r="D20">
-        <v>13.651666</v>
+        <v>13.651479</v>
       </c>
       <c r="E20" s="66">
         <v>114992738.00</v>
@@ -739,12 +739,12 @@
         <v>52</v>
       </c>
       <c r="G20" s="66">
-        <v>1569842396.78</v>
+        <v>1569821002.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B21">
         <is>
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c t="n" r="D21">
-        <v>0.999011</v>
+        <v>0.999928</v>
       </c>
       <c r="E21" s="66">
         <v>100000.00</v>
@@ -766,12 +766,12 @@
         <v>1</v>
       </c>
       <c r="G21" s="66">
-        <v>99901.06</v>
+        <v>99992.82</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B22">
         <is>
@@ -798,7 +798,7 @@
     </row>
     <row r="23">
       <c r="A23" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B23">
         <is>
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c t="n" r="D23">
-        <v>1016.650114</v>
+        <v>1017.691196</v>
       </c>
       <c r="E23" s="66">
         <v>20000.00</v>
@@ -820,12 +820,12 @@
         <v>1</v>
       </c>
       <c r="G23" s="66">
-        <v>20333002.28</v>
+        <v>20353823.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B24">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c t="n" r="D24">
-        <v>724.507915</v>
+        <v>724.492692</v>
       </c>
       <c r="E24" s="66">
         <v>4147266.00</v>
@@ -847,12 +847,12 @@
         <v>1</v>
       </c>
       <c r="G24" s="66">
-        <v>3004727043.14</v>
+        <v>3004663908.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B25">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c t="n" r="D25">
-        <v>1124.413840</v>
+        <v>1124.401725</v>
       </c>
       <c r="E25" s="66">
         <v>2422126.00</v>
@@ -874,12 +874,12 @@
         <v>2</v>
       </c>
       <c r="G25" s="66">
-        <v>2723471997.78</v>
+        <v>2723442651.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B26">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c t="n" r="D26">
-        <v>0.999011</v>
+        <v>0.998901</v>
       </c>
       <c r="E26" s="66">
         <v>100000.00</v>
@@ -901,12 +901,12 @@
         <v>1</v>
       </c>
       <c r="G26" s="66">
-        <v>99901.06</v>
+        <v>99890.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B27">
         <is>
@@ -919,21 +919,21 @@
         </is>
       </c>
       <c t="n" r="D27">
-        <v>1.702707</v>
+        <v>1.724791</v>
       </c>
       <c r="E27" s="66">
-        <v>336949912.00</v>
+        <v>358844290.00</v>
       </c>
       <c r="F27" s="65">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G27" s="66">
-        <v>573726855.24</v>
+        <v>618931224.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B28">
         <is>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c t="n" r="D28">
-        <v>883.623361</v>
+        <v>895.615707</v>
       </c>
       <c r="E28" s="66">
         <v>4999.00</v>
@@ -955,12 +955,12 @@
         <v>1</v>
       </c>
       <c r="G28" s="66">
-        <v>4417233.18</v>
+        <v>4477182.92</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B29">
         <is>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c t="n" r="D29">
-        <v>1197.514081</v>
+        <v>1201.618077</v>
       </c>
       <c r="E29" s="66">
         <v>50000.00</v>
@@ -982,12 +982,12 @@
         <v>2</v>
       </c>
       <c r="G29" s="66">
-        <v>59875704.03</v>
+        <v>60080903.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B30">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c t="n" r="D30">
-        <v>1.808810</v>
+        <v>1.808838</v>
       </c>
       <c r="E30" s="66">
         <v>200000000.00</v>
@@ -1009,12 +1009,12 @@
         <v>2</v>
       </c>
       <c r="G30" s="66">
-        <v>361761977.99</v>
+        <v>361767614.80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B31">
         <is>
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c t="n" r="D31">
-        <v>1374.777188</v>
+        <v>1375.684755</v>
       </c>
       <c r="E31" s="66">
         <v>4000.00</v>
@@ -1036,12 +1036,12 @@
         <v>1</v>
       </c>
       <c r="G31" s="66">
-        <v>5499108.75</v>
+        <v>5502739.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B32">
         <is>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c t="n" r="D32">
-        <v>7321.276432</v>
+        <v>7320.869482</v>
       </c>
       <c r="E32" s="66">
         <v>72885.00</v>
@@ -1063,12 +1063,12 @@
         <v>6</v>
       </c>
       <c r="G32" s="66">
-        <v>533611232.76</v>
+        <v>533581572.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B33">
         <is>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c t="n" r="D33">
-        <v>6974.744292</v>
+        <v>6972.987556</v>
       </c>
       <c r="E33" s="66">
         <v>24833.00</v>
@@ -1090,12 +1090,12 @@
         <v>18</v>
       </c>
       <c r="G33" s="66">
-        <v>173203825.01</v>
+        <v>173160199.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B34">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c t="n" r="D34">
-        <v>20568.035451</v>
+        <v>20568.167986</v>
       </c>
       <c r="E34" s="66">
         <v>16268.00</v>
@@ -1117,12 +1117,12 @@
         <v>6</v>
       </c>
       <c r="G34" s="66">
-        <v>334600800.71</v>
+        <v>334602956.80</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B35">
         <is>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c t="n" r="D35">
-        <v>1167.301662</v>
+        <v>1168.213112</v>
       </c>
       <c r="E35" s="66">
         <v>5000.00</v>
@@ -1144,12 +1144,12 @@
         <v>1</v>
       </c>
       <c r="G35" s="66">
-        <v>5836508.31</v>
+        <v>5841065.56</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B36">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c t="n" r="D36">
-        <v>1166.301664</v>
+        <v>1167.213116</v>
       </c>
       <c r="E36" s="66">
         <v>5000.00</v>
@@ -1171,12 +1171,12 @@
         <v>1</v>
       </c>
       <c r="G36" s="66">
-        <v>5831508.32</v>
+        <v>5836065.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B37">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c t="n" r="D37">
-        <v>1041.537725</v>
+        <v>1040.892301</v>
       </c>
       <c r="E37" s="66">
         <v>25100.00</v>
@@ -1198,12 +1198,12 @@
         <v>1</v>
       </c>
       <c r="G37" s="66">
-        <v>26142596.91</v>
+        <v>26126396.75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B38">
         <is>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c t="n" r="D38">
-        <v>1.694668</v>
+        <v>1.694504</v>
       </c>
       <c r="E38" s="66">
         <v>136670833.00</v>
@@ -1225,12 +1225,12 @@
         <v>76</v>
       </c>
       <c r="G38" s="66">
-        <v>231611630.65</v>
+        <v>231589287.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B39">
         <is>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c t="n" r="D39">
-        <v>1232.775291</v>
+        <v>1235.144874</v>
       </c>
       <c r="E39" s="66">
         <v>266565.00</v>
@@ -1252,12 +1252,12 @@
         <v>23</v>
       </c>
       <c r="G39" s="66">
-        <v>328614745.51</v>
+        <v>329246393.34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B40">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c t="n" r="D40">
-        <v>3618.685915</v>
+        <v>3618.614816</v>
       </c>
       <c r="E40" s="66">
         <v>204000.00</v>
@@ -1279,12 +1279,12 @@
         <v>5</v>
       </c>
       <c r="G40" s="66">
-        <v>738211926.57</v>
+        <v>738197422.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B41">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c t="n" r="D41">
-        <v>3647.345521</v>
+        <v>3595.473811</v>
       </c>
       <c r="E41" s="66">
         <v>70164.00</v>
@@ -1306,12 +1306,12 @@
         <v>1</v>
       </c>
       <c r="G41" s="66">
-        <v>255912351.13</v>
+        <v>252272824.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B42">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c t="n" r="D42">
-        <v>6782.000950</v>
+        <v>6749.675710</v>
       </c>
       <c r="E42" s="66">
         <v>28015.54</v>
@@ -1333,12 +1333,12 @@
         <v>44</v>
       </c>
       <c r="G42" s="66">
-        <v>190001425.67</v>
+        <v>189095816.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B43">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c t="n" r="D43">
-        <v>0.109981</v>
+        <v>0.109953</v>
       </c>
       <c r="E43" s="66">
         <v>315837238.00</v>
@@ -1360,12 +1360,12 @@
         <v>2</v>
       </c>
       <c r="G43" s="66">
-        <v>34736146.91</v>
+        <v>34727191.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B44">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c t="n" r="D44">
-        <v>1.947593</v>
+        <v>1.947546</v>
       </c>
       <c r="E44" s="66">
         <v>124621132.00</v>
@@ -1387,12 +1387,12 @@
         <v>2</v>
       </c>
       <c r="G44" s="66">
-        <v>242711252.27</v>
+        <v>242705445.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B45">
         <is>
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c t="n" r="D45">
-        <v>5.605262</v>
+        <v>5.604860</v>
       </c>
       <c r="E45" s="66">
         <v>10604880.00</v>
@@ -1414,12 +1414,12 @@
         <v>1</v>
       </c>
       <c r="G45" s="66">
-        <v>59443130.75</v>
+        <v>59438867.60</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B46">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c t="n" r="D46">
-        <v>0.465227</v>
+        <v>0.465199</v>
       </c>
       <c r="E46" s="66">
         <v>3551146568.00</v>
@@ -1441,12 +1441,12 @@
         <v>1</v>
       </c>
       <c r="G46" s="66">
-        <v>1652089700.55</v>
+        <v>1651991553.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B47">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c t="n" r="D47">
-        <v>0.008929</v>
+        <v>0.008921</v>
       </c>
       <c r="E47" s="66">
         <v>68030518764.00</v>
@@ -1468,12 +1468,12 @@
         <v>25</v>
       </c>
       <c r="G47" s="66">
-        <v>607424561.99</v>
+        <v>606884163.40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B48">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c t="n" r="D48">
-        <v>0.081614</v>
+        <v>0.069187</v>
       </c>
       <c r="E48" s="66">
         <v>1438792.00</v>
@@ -1495,12 +1495,12 @@
         <v>1</v>
       </c>
       <c r="G48" s="66">
-        <v>117425.00</v>
+        <v>99546.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B49">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c t="n" r="D49">
-        <v>0.443236</v>
+        <v>0.442907</v>
       </c>
       <c r="E49" s="66">
         <v>1367983.00</v>
@@ -1522,12 +1522,12 @@
         <v>2</v>
       </c>
       <c r="G49" s="66">
-        <v>606339.79</v>
+        <v>605888.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B50">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c t="n" r="D50">
-        <v>1777.790804</v>
+        <v>1777.449160</v>
       </c>
       <c r="E50" s="66">
         <v>286951.00</v>
@@ -1549,12 +1549,12 @@
         <v>4</v>
       </c>
       <c r="G50" s="66">
-        <v>510138849.13</v>
+        <v>510040813.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B51">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c t="n" r="D51">
-        <v>16924.315256</v>
+        <v>16925.838266</v>
       </c>
       <c r="E51" s="66">
         <v>21897.00</v>
@@ -1576,12 +1576,12 @@
         <v>3</v>
       </c>
       <c r="G51" s="66">
-        <v>370591731.17</v>
+        <v>370625080.51</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B52">
         <is>
@@ -1594,7 +1594,7 @@
         </is>
       </c>
       <c t="n" r="D52">
-        <v>1.289226</v>
+        <v>1.286805</v>
       </c>
       <c r="E52" s="66">
         <v>10013000.00</v>
@@ -1603,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="G52" s="66">
-        <v>12909019.84</v>
+        <v>12884782.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B53">
         <is>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c t="n" r="D53">
-        <v>7521.562458</v>
+        <v>7520.132636</v>
       </c>
       <c r="E53" s="66">
         <v>5919.00</v>
@@ -1630,12 +1630,12 @@
         <v>1</v>
       </c>
       <c r="G53" s="66">
-        <v>44520128.19</v>
+        <v>44511665.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B54">
         <is>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c t="n" r="D54">
-        <v>7.340113</v>
+        <v>7.343016</v>
       </c>
       <c r="E54" s="66">
         <v>33024184.00</v>
@@ -1657,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="G54" s="66">
-        <v>242401238.28</v>
+        <v>242497096.32</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B55">
         <is>
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c t="n" r="D55">
-        <v>0.016968</v>
+        <v>0.016760</v>
       </c>
       <c r="E55" s="66">
         <v>1130228.00</v>
@@ -1684,12 +1684,12 @@
         <v>1</v>
       </c>
       <c r="G55" s="66">
-        <v>19177.25</v>
+        <v>18942.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B56">
         <is>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c t="n" r="D56">
-        <v>6.392053</v>
+        <v>6.396393</v>
       </c>
       <c r="E56" s="66">
         <v>17232266.00</v>
@@ -1711,12 +1711,12 @@
         <v>2</v>
       </c>
       <c r="G56" s="66">
-        <v>110149550.74</v>
+        <v>110224344.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B57">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c t="n" r="D57">
-        <v>0.990440</v>
+        <v>0.989873</v>
       </c>
       <c r="E57" s="66">
         <v>60000000.00</v>
@@ -1738,12 +1738,12 @@
         <v>1</v>
       </c>
       <c r="G57" s="66">
-        <v>59426370.70</v>
+        <v>59392358.63</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B58">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c t="n" r="D58">
-        <v>1.590895</v>
+        <v>1.590829</v>
       </c>
       <c r="E58" s="66">
         <v>86508523.00</v>
@@ -1765,12 +1765,12 @@
         <v>17</v>
       </c>
       <c r="G58" s="66">
-        <v>137625945.73</v>
+        <v>137620261.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B59">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c t="n" r="D59">
-        <v>8.621948</v>
+        <v>8.621055</v>
       </c>
       <c r="E59" s="66">
         <v>40000000.00</v>
@@ -1792,12 +1792,12 @@
         <v>1</v>
       </c>
       <c r="G59" s="66">
-        <v>344877936.78</v>
+        <v>344842207.24</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B60">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c t="n" r="D60">
-        <v>0.686611</v>
+        <v>0.682994</v>
       </c>
       <c r="E60" s="66">
         <v>1000000.00</v>
@@ -1819,12 +1819,12 @@
         <v>1</v>
       </c>
       <c r="G60" s="66">
-        <v>686611.14</v>
+        <v>682993.73</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B61">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c t="n" r="D61">
-        <v>0.862440</v>
+        <v>0.858303</v>
       </c>
       <c r="E61" s="66">
         <v>863936.00</v>
@@ -1846,12 +1846,12 @@
         <v>1</v>
       </c>
       <c r="G61" s="66">
-        <v>745093.30</v>
+        <v>741518.80</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B62">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c t="n" r="D62">
-        <v>2.244077</v>
+        <v>2.243751</v>
       </c>
       <c r="E62" s="66">
         <v>76018843.00</v>
@@ -1873,12 +1873,12 @@
         <v>9</v>
       </c>
       <c r="G62" s="66">
-        <v>170592147.47</v>
+        <v>170567333.98</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B63">
         <is>
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c t="n" r="D63">
-        <v>5.716899</v>
+        <v>5.717201</v>
       </c>
       <c r="E63" s="66">
         <v>284155337.00</v>
@@ -1900,12 +1900,12 @@
         <v>3</v>
       </c>
       <c r="G63" s="66">
-        <v>1624487430.93</v>
+        <v>1624573136.03</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B64">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c t="n" r="D64">
-        <v>1.355156</v>
+        <v>1.356151</v>
       </c>
       <c r="E64" s="66">
         <v>1972627727.00</v>
@@ -1927,12 +1927,12 @@
         <v>1</v>
       </c>
       <c r="G64" s="66">
-        <v>2673217725.35</v>
+        <v>2675180769.59</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B65">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c t="n" r="D65">
-        <v>1.296191</v>
+        <v>1.296149</v>
       </c>
       <c r="E65" s="66">
         <v>1345904721.00</v>
@@ -1954,12 +1954,12 @@
         <v>3</v>
       </c>
       <c r="G65" s="66">
-        <v>1744549280.93</v>
+        <v>1744493586.31</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B66">
         <is>
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c t="n" r="D66">
-        <v>0.975686</v>
+        <v>0.975742</v>
       </c>
       <c r="E66" s="66">
         <v>157500000.00</v>
@@ -1981,12 +1981,12 @@
         <v>12</v>
       </c>
       <c r="G66" s="66">
-        <v>153670506.32</v>
+        <v>153679335.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B67">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c t="n" r="D67">
-        <v>6.027830</v>
+        <v>6.029482</v>
       </c>
       <c r="E67" s="66">
         <v>1097692477.00</v>
@@ -2008,12 +2008,12 @@
         <v>1</v>
       </c>
       <c r="G67" s="66">
-        <v>6616703945.29</v>
+        <v>6618517530.76</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B68">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c t="n" r="D68">
-        <v>1514.936963</v>
+        <v>1514.873353</v>
       </c>
       <c r="E68" s="66">
         <v>957363.00</v>
@@ -2035,12 +2035,12 @@
         <v>246</v>
       </c>
       <c r="G68" s="66">
-        <v>1450344595.89</v>
+        <v>1450283697.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B69">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c t="n" r="D69">
-        <v>6.172716</v>
+        <v>6.173246</v>
       </c>
       <c r="E69" s="66">
         <v>423364599.00</v>
@@ -2062,12 +2062,12 @@
         <v>2</v>
       </c>
       <c r="G69" s="66">
-        <v>2613309442.15</v>
+        <v>2613533796.56</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B70">
         <is>
@@ -2080,7 +2080,7 @@
         </is>
       </c>
       <c t="n" r="D70">
-        <v>4.098974</v>
+        <v>4.099906</v>
       </c>
       <c r="E70" s="66">
         <v>633560000.00</v>
@@ -2089,12 +2089,12 @@
         <v>1</v>
       </c>
       <c r="G70" s="66">
-        <v>2596946225.94</v>
+        <v>2597536474.18</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B71">
         <is>
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c t="n" r="D71">
-        <v>6.782601</v>
+        <v>6.789155</v>
       </c>
       <c r="E71" s="66">
         <v>47079812.00</v>
@@ -2116,12 +2116,12 @@
         <v>12</v>
       </c>
       <c r="G71" s="66">
-        <v>319323559.01</v>
+        <v>319632127.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B72">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c t="n" r="D72">
-        <v>1.792402</v>
+        <v>1.792353</v>
       </c>
       <c r="E72" s="66">
         <v>248146145.00</v>
@@ -2143,12 +2143,12 @@
         <v>57</v>
       </c>
       <c r="G72" s="66">
-        <v>444777622.78</v>
+        <v>444765490.67</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B73">
         <is>
@@ -2161,7 +2161,7 @@
         </is>
       </c>
       <c t="n" r="D73">
-        <v>18.435615</v>
+        <v>18.430334</v>
       </c>
       <c r="E73" s="66">
         <v>1097845.00</v>
@@ -2170,12 +2170,12 @@
         <v>1</v>
       </c>
       <c r="G73" s="66">
-        <v>20239447.22</v>
+        <v>20233650.22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B74">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c t="n" r="D74">
-        <v>3.161291</v>
+        <v>3.162405</v>
       </c>
       <c r="E74" s="66">
         <v>175276623.00</v>
@@ -2197,12 +2197,12 @@
         <v>1</v>
       </c>
       <c r="G74" s="66">
-        <v>554100410.61</v>
+        <v>554295696.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B75">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c t="n" r="D75">
-        <v>14.600050</v>
+        <v>14.600835</v>
       </c>
       <c r="E75" s="66">
         <v>442255598.00</v>
@@ -2224,12 +2224,12 @@
         <v>90</v>
       </c>
       <c r="G75" s="66">
-        <v>6456953809.85</v>
+        <v>6457300863.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B76">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c t="n" r="D76">
-        <v>6.601109</v>
+        <v>6.601030</v>
       </c>
       <c r="E76" s="66">
         <v>441482336.00</v>
@@ -2251,12 +2251,12 @@
         <v>5</v>
       </c>
       <c r="G76" s="66">
-        <v>2914273122.45</v>
+        <v>2914238292.03</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B77">
         <is>
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c t="n" r="D77">
-        <v>1362.087131</v>
+        <v>1362.124459</v>
       </c>
       <c r="E77" s="66">
         <v>288613.00</v>
@@ -2278,12 +2278,12 @@
         <v>1</v>
       </c>
       <c r="G77" s="66">
-        <v>393116053.17</v>
+        <v>393126826.62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B78">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c t="n" r="D78">
-        <v>5.232403</v>
+        <v>5.232151</v>
       </c>
       <c r="E78" s="66">
         <v>68022200.00</v>
@@ -2305,12 +2305,12 @@
         <v>5</v>
       </c>
       <c r="G78" s="66">
-        <v>355919566.97</v>
+        <v>355902440.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B79">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c t="n" r="D79">
-        <v>438.825200</v>
+        <v>438.163300</v>
       </c>
       <c r="E79" s="66">
         <v>100.00</v>
@@ -2332,12 +2332,12 @@
         <v>1</v>
       </c>
       <c r="G79" s="66">
-        <v>43882.52</v>
+        <v>43816.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B80">
         <is>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
       <c t="n" r="D80">
-        <v>7070.668000</v>
+        <v>7063.671000</v>
       </c>
       <c r="E80" s="66">
         <v>10.00</v>
@@ -2359,12 +2359,12 @@
         <v>1</v>
       </c>
       <c r="G80" s="66">
-        <v>70706.68</v>
+        <v>70636.71</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B81">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c t="n" r="D81">
-        <v>181.683200</v>
+        <v>181.058400</v>
       </c>
       <c r="E81" s="66">
         <v>100.00</v>
@@ -2386,12 +2386,12 @@
         <v>1</v>
       </c>
       <c r="G81" s="66">
-        <v>18168.32</v>
+        <v>18105.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B82">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c t="n" r="D82">
-        <v>46.158611</v>
+        <v>46.160488</v>
       </c>
       <c r="E82" s="66">
         <v>35089.00</v>
@@ -2413,12 +2413,12 @@
         <v>1</v>
       </c>
       <c r="G82" s="66">
-        <v>1619659.49</v>
+        <v>1619725.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B83">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c t="n" r="D83">
-        <v>1225.783250</v>
+        <v>1227.276183</v>
       </c>
       <c r="E83" s="66">
         <v>93000.00</v>
@@ -2440,12 +2440,12 @@
         <v>3</v>
       </c>
       <c r="G83" s="66">
-        <v>113997842.28</v>
+        <v>114136685.06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B84">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c t="n" r="D84">
-        <v>21.021187</v>
+        <v>21.018899</v>
       </c>
       <c r="E84" s="66">
         <v>79504850.00</v>
@@ -2467,12 +2467,12 @@
         <v>13</v>
       </c>
       <c r="G84" s="66">
-        <v>1671286341.60</v>
+        <v>1671104405.60</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B85">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c t="n" r="D85">
-        <v>31.423994</v>
+        <v>31.419918</v>
       </c>
       <c r="E85" s="66">
         <v>31138359.00</v>
@@ -2494,12 +2494,12 @@
         <v>1</v>
       </c>
       <c r="G85" s="66">
-        <v>978491621.69</v>
+        <v>978364671.86</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B86">
         <is>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c t="n" r="D86">
-        <v>46.109441</v>
+        <v>46.108657</v>
       </c>
       <c r="E86" s="66">
         <v>35089.00</v>
@@ -2521,12 +2521,12 @@
         <v>1</v>
       </c>
       <c r="G86" s="66">
-        <v>1617934.19</v>
+        <v>1617906.65</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B87">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c t="n" r="D87">
-        <v>1.090925</v>
+        <v>1.092017</v>
       </c>
       <c r="E87" s="66">
         <v>565000000.00</v>
@@ -2548,12 +2548,12 @@
         <v>4</v>
       </c>
       <c r="G87" s="66">
-        <v>616372645.20</v>
+        <v>616989881.89</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B88">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c t="n" r="D88">
-        <v>20.781445</v>
+        <v>20.799239</v>
       </c>
       <c r="E88" s="66">
         <v>10058783.00</v>
@@ -2575,12 +2575,12 @@
         <v>14</v>
       </c>
       <c r="G88" s="66">
-        <v>209036047.76</v>
+        <v>209215034.20</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B89">
         <is>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c t="n" r="D89">
-        <v>19.751412</v>
+        <v>19.749184</v>
       </c>
       <c r="E89" s="66">
         <v>155910000.00</v>
@@ -2602,12 +2602,12 @@
         <v>2</v>
       </c>
       <c r="G89" s="66">
-        <v>3079442665.30</v>
+        <v>3079095316.45</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B90">
         <is>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c t="n" r="D90">
-        <v>0.015163</v>
+        <v>0.015284</v>
       </c>
       <c r="E90" s="66">
         <v>550686.00</v>
@@ -2629,12 +2629,12 @@
         <v>1</v>
       </c>
       <c r="G90" s="66">
-        <v>8349.94</v>
+        <v>8416.91</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B91">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c t="n" r="D91">
-        <v>5680.440978</v>
+        <v>5681.463651</v>
       </c>
       <c r="E91" s="66">
         <v>956800.00</v>
@@ -2656,12 +2656,12 @@
         <v>7</v>
       </c>
       <c r="G91" s="66">
-        <v>5435045927.49</v>
+        <v>5436024421.19</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B92">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c t="n" r="D92">
-        <v>1.338095</v>
+        <v>1.340173</v>
       </c>
       <c r="E92" s="66">
         <v>162915080.00</v>
@@ -2683,12 +2683,12 @@
         <v>5</v>
       </c>
       <c r="G92" s="66">
-        <v>217995823.47</v>
+        <v>218334409.19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B93">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c t="n" r="D93">
-        <v>0.778908</v>
+        <v>0.778833</v>
       </c>
       <c r="E93" s="66">
         <v>174507033.00</v>
@@ -2710,12 +2710,12 @@
         <v>14</v>
       </c>
       <c r="G93" s="66">
-        <v>135924997.06</v>
+        <v>135911810.14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B94">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c t="n" r="D94">
-        <v>30.631222</v>
+        <v>30.629921</v>
       </c>
       <c r="E94" s="66">
         <v>50650817.00</v>
@@ -2737,12 +2737,12 @@
         <v>2</v>
       </c>
       <c r="G94" s="66">
-        <v>1551496423.34</v>
+        <v>1551430527.14</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B95">
         <is>
@@ -2755,7 +2755,7 @@
         </is>
       </c>
       <c t="n" r="D95">
-        <v>1.091827</v>
+        <v>1.091336</v>
       </c>
       <c r="E95" s="66">
         <v>50691040.00</v>
@@ -2764,12 +2764,12 @@
         <v>2</v>
       </c>
       <c r="G95" s="66">
-        <v>55345824.42</v>
+        <v>55320971.79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B96">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c t="n" r="D96">
-        <v>1.208766</v>
+        <v>1.208690</v>
       </c>
       <c r="E96" s="66">
         <v>247000000.00</v>
@@ -2791,12 +2791,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="66">
-        <v>298565165.79</v>
+        <v>298546531.93</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B97">
         <is>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c t="n" r="D97">
-        <v>0.598921</v>
+        <v>0.598801</v>
       </c>
       <c r="E97" s="66">
         <v>117338256.00</v>
@@ -2818,12 +2818,12 @@
         <v>1</v>
       </c>
       <c r="G97" s="66">
-        <v>70276365.24</v>
+        <v>70262252.19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B98">
         <is>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c t="n" r="D98">
-        <v>52.494749</v>
+        <v>52.488109</v>
       </c>
       <c r="E98" s="66">
         <v>742718.00</v>
@@ -2845,12 +2845,12 @@
         <v>3</v>
       </c>
       <c r="G98" s="66">
-        <v>38988794.73</v>
+        <v>38983863.01</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B99">
         <is>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c t="n" r="D99">
-        <v>19.944438</v>
+        <v>19.943590</v>
       </c>
       <c r="E99" s="66">
         <v>5494644.00</v>
@@ -2872,12 +2872,12 @@
         <v>4</v>
       </c>
       <c r="G99" s="66">
-        <v>109587588.04</v>
+        <v>109582927.60</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B100">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c t="n" r="D100">
-        <v>1007.890899</v>
+        <v>1007.956841</v>
       </c>
       <c r="E100" s="66">
         <v>67591.00</v>
@@ -2899,12 +2899,12 @@
         <v>4</v>
       </c>
       <c r="G100" s="66">
-        <v>68124353.78</v>
+        <v>68128810.84</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B101">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c t="n" r="D101">
-        <v>0.614106</v>
+        <v>0.614291</v>
       </c>
       <c r="E101" s="66">
         <v>2100000.00</v>
@@ -2926,12 +2926,12 @@
         <v>3</v>
       </c>
       <c r="G101" s="66">
-        <v>1289621.87</v>
+        <v>1290011.73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B102">
         <is>
@@ -2953,12 +2953,12 @@
         <v>1</v>
       </c>
       <c r="G102" s="66">
-        <v>1841422922.85</v>
+        <v>1841417019.36</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B103">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c t="n" r="D103">
-        <v>4.974998</v>
+        <v>4.979857</v>
       </c>
       <c r="E103" s="66">
         <v>13403625.00</v>
@@ -2980,12 +2980,12 @@
         <v>4</v>
       </c>
       <c r="G103" s="66">
-        <v>66683011.50</v>
+        <v>66748137.77</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B104">
         <is>
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c t="n" r="D104">
-        <v>13.943752</v>
+        <v>13.943194</v>
       </c>
       <c r="E104" s="66">
         <v>12523539.00</v>
@@ -3007,12 +3007,12 @@
         <v>3</v>
       </c>
       <c r="G104" s="66">
-        <v>174625118.14</v>
+        <v>174618132.24</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B105">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c t="n" r="D105">
-        <v>9.364576</v>
+        <v>9.363853</v>
       </c>
       <c r="E105" s="66">
         <v>8384620.00</v>
@@ -3034,12 +3034,12 @@
         <v>2</v>
       </c>
       <c r="G105" s="66">
-        <v>78518412.89</v>
+        <v>78512345.25</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B106">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c t="n" r="D106">
-        <v>14.405683</v>
+        <v>14.405309</v>
       </c>
       <c r="E106" s="66">
         <v>64798777.00</v>
@@ -3061,12 +3061,12 @@
         <v>1</v>
       </c>
       <c r="G106" s="66">
-        <v>933470614.67</v>
+        <v>933446387.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B107">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c t="n" r="D107">
-        <v>8.808504</v>
+        <v>8.808354</v>
       </c>
       <c r="E107" s="66">
         <v>79280717.00</v>
@@ -3088,12 +3088,12 @@
         <v>1</v>
       </c>
       <c r="G107" s="66">
-        <v>698344521.72</v>
+        <v>698332590.18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B108">
         <is>
@@ -3106,7 +3106,7 @@
         </is>
       </c>
       <c t="n" r="D108">
-        <v>8.940539</v>
+        <v>8.940543</v>
       </c>
       <c r="E108" s="66">
         <v>325576554.00</v>
@@ -3115,12 +3115,12 @@
         <v>2</v>
       </c>
       <c r="G108" s="66">
-        <v>2910829933.95</v>
+        <v>2910831088.02</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B109">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c t="n" r="D109">
-        <v>29.813525</v>
+        <v>29.817981</v>
       </c>
       <c r="E109" s="66">
         <v>22203221.00</v>
@@ -3142,12 +3142,12 @@
         <v>1</v>
       </c>
       <c r="G109" s="66">
-        <v>661956275.78</v>
+        <v>662055231.27</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B110">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c t="n" r="D110">
-        <v>2.791243</v>
+        <v>2.794092</v>
       </c>
       <c r="E110" s="66">
         <v>105924883.00</v>
@@ -3169,12 +3169,12 @@
         <v>8</v>
       </c>
       <c r="G110" s="66">
-        <v>295662063.07</v>
+        <v>295963895.11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B111">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c t="n" r="D111">
-        <v>48.423588</v>
+        <v>48.429938</v>
       </c>
       <c r="E111" s="66">
         <v>38023816.00</v>
@@ -3196,12 +3196,12 @@
         <v>80</v>
       </c>
       <c r="G111" s="66">
-        <v>1841249592.61</v>
+        <v>1841491057.84</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B112">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c t="n" r="D112">
-        <v>11.609661</v>
+        <v>11.609131</v>
       </c>
       <c r="E112" s="66">
         <v>12696866.00</v>
@@ -3223,12 +3223,12 @@
         <v>2</v>
       </c>
       <c r="G112" s="66">
-        <v>147406315.15</v>
+        <v>147399576.10</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B113">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c t="n" r="D113">
-        <v>4.902878</v>
+        <v>4.902661</v>
       </c>
       <c r="E113" s="66">
         <v>178831349.00</v>
@@ -3250,12 +3250,12 @@
         <v>2</v>
       </c>
       <c r="G113" s="66">
-        <v>876788286.40</v>
+        <v>876749455.99</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B114">
         <is>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c t="n" r="D114">
-        <v>39.496113</v>
+        <v>39.513224</v>
       </c>
       <c r="E114" s="66">
         <v>1032754.00</v>
@@ -3277,12 +3277,12 @@
         <v>8</v>
       </c>
       <c r="G114" s="66">
-        <v>40789768.17</v>
+        <v>40807440.04</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B115">
         <is>
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c t="n" r="D115">
-        <v>123.787385</v>
+        <v>120.796711</v>
       </c>
       <c r="E115" s="66">
         <v>3843.00</v>
@@ -3304,12 +3304,12 @@
         <v>2</v>
       </c>
       <c r="G115" s="66">
-        <v>475714.92</v>
+        <v>464221.76</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B116">
         <is>
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c t="n" r="D116">
-        <v>32.082178</v>
+        <v>32.069485</v>
       </c>
       <c r="E116" s="66">
         <v>3000000.00</v>
@@ -3331,12 +3331,12 @@
         <v>3</v>
       </c>
       <c r="G116" s="66">
-        <v>96246534.66</v>
+        <v>96208456.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B117">
         <is>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c t="n" r="D117">
-        <v>0.002315</v>
+        <v>0.002317</v>
       </c>
       <c r="E117" s="66">
         <v>113163507031.00</v>
@@ -3358,12 +3358,12 @@
         <v>1</v>
       </c>
       <c r="G117" s="66">
-        <v>261958280.58</v>
+        <v>262226982.81</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B118">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c t="n" r="D118">
-        <v>31.956297</v>
+        <v>31.955482</v>
       </c>
       <c r="E118" s="66">
         <v>11112484.00</v>
@@ -3385,12 +3385,12 @@
         <v>2</v>
       </c>
       <c r="G118" s="66">
-        <v>355113834.07</v>
+        <v>355104783.94</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B119">
         <is>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c t="n" r="D119">
-        <v>401.161021</v>
+        <v>401.260053</v>
       </c>
       <c r="E119" s="66">
         <v>749472.00</v>
@@ -3412,12 +3412,12 @@
         <v>2</v>
       </c>
       <c r="G119" s="66">
-        <v>300658952.83</v>
+        <v>300733174.24</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B120">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c t="n" r="D120">
-        <v>2.390834</v>
+        <v>2.388945</v>
       </c>
       <c r="E120" s="66">
         <v>206271120.00</v>
@@ -3439,12 +3439,12 @@
         <v>7</v>
       </c>
       <c r="G120" s="66">
-        <v>493159988.44</v>
+        <v>492770276.39</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B121">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c t="n" r="D121">
-        <v>0.912571</v>
+        <v>0.912542</v>
       </c>
       <c r="E121" s="66">
         <v>246086436.00</v>
@@ -3466,12 +3466,12 @@
         <v>3</v>
       </c>
       <c r="G121" s="66">
-        <v>224571262.46</v>
+        <v>224564327.84</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B122">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c t="n" r="D122">
-        <v>1.499747</v>
+        <v>1.499583</v>
       </c>
       <c r="E122" s="66">
         <v>36704937.00</v>
@@ -3493,12 +3493,12 @@
         <v>3</v>
       </c>
       <c r="G122" s="66">
-        <v>55048120.90</v>
+        <v>55042111.24</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B123">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c t="n" r="D123">
-        <v>27.007881</v>
+        <v>27.007835</v>
       </c>
       <c r="E123" s="66">
         <v>14483462.00</v>
@@ -3520,12 +3520,12 @@
         <v>2</v>
       </c>
       <c r="G123" s="66">
-        <v>391167615.32</v>
+        <v>391166945.53</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B124">
         <is>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c t="n" r="D124">
-        <v>2.027908</v>
+        <v>2.027814</v>
       </c>
       <c r="E124" s="66">
         <v>29119928.00</v>
@@ -3547,12 +3547,12 @@
         <v>1</v>
       </c>
       <c r="G124" s="66">
-        <v>59052527.23</v>
+        <v>59049791.04</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B125">
         <is>
@@ -3565,7 +3565,7 @@
         </is>
       </c>
       <c t="n" r="D125">
-        <v>21.743910</v>
+        <v>21.742179</v>
       </c>
       <c r="E125" s="66">
         <v>5510146.00</v>
@@ -3574,12 +3574,12 @@
         <v>1</v>
       </c>
       <c r="G125" s="66">
-        <v>119812116.99</v>
+        <v>119802581.17</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B126">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c t="n" r="D126">
-        <v>7.660289</v>
+        <v>7.658140</v>
       </c>
       <c r="E126" s="66">
         <v>23301113.00</v>
@@ -3601,12 +3601,12 @@
         <v>1</v>
       </c>
       <c r="G126" s="66">
-        <v>178493250.43</v>
+        <v>178443185.15</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B127">
         <is>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c t="n" r="D127">
-        <v>5.022513</v>
+        <v>5.022210</v>
       </c>
       <c r="E127" s="66">
         <v>42689474.00</v>
@@ -3628,12 +3628,12 @@
         <v>2</v>
       </c>
       <c r="G127" s="66">
-        <v>214408450.00</v>
+        <v>214395516.31</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B128">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c t="n" r="D128">
-        <v>2.723022</v>
+        <v>2.722902</v>
       </c>
       <c r="E128" s="66">
         <v>135381703.00</v>
@@ -3655,12 +3655,12 @@
         <v>2</v>
       </c>
       <c r="G128" s="66">
-        <v>368647422.53</v>
+        <v>368631169.20</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B129">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c t="n" r="D129">
-        <v>23.846002</v>
+        <v>23.846013</v>
       </c>
       <c r="E129" s="66">
         <v>18925185.00</v>
@@ -3682,12 +3682,12 @@
         <v>3</v>
       </c>
       <c r="G129" s="66">
-        <v>451289993.65</v>
+        <v>451290214.89</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B130">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c t="n" r="D130">
-        <v>5.407764</v>
+        <v>5.406802</v>
       </c>
       <c r="E130" s="66">
         <v>8172487.00</v>
@@ -3709,12 +3709,12 @@
         <v>1</v>
       </c>
       <c r="G130" s="66">
-        <v>44194883.01</v>
+        <v>44187018.72</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B131">
         <is>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c t="n" r="D131">
-        <v>1.348151</v>
+        <v>1.348130</v>
       </c>
       <c r="E131" s="66">
         <v>757303279.00</v>
@@ -3736,12 +3736,12 @@
         <v>1</v>
       </c>
       <c r="G131" s="66">
-        <v>1020958863.71</v>
+        <v>1020942911.35</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B132">
         <is>
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c t="n" r="D132">
-        <v>0.947341</v>
+        <v>0.947220</v>
       </c>
       <c r="E132" s="66">
         <v>91944333.00</v>
@@ -3763,12 +3763,12 @@
         <v>5</v>
       </c>
       <c r="G132" s="66">
-        <v>87102613.41</v>
+        <v>87091479.13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B133">
         <is>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c t="n" r="D133">
-        <v>12.229126</v>
+        <v>12.229058</v>
       </c>
       <c r="E133" s="66">
         <v>14080750.00</v>
@@ -3790,12 +3790,12 @@
         <v>1</v>
       </c>
       <c r="G133" s="66">
-        <v>172195268.44</v>
+        <v>172194306.26</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B134">
         <is>
@@ -3808,7 +3808,7 @@
         </is>
       </c>
       <c t="n" r="D134">
-        <v>2.219771</v>
+        <v>2.220207</v>
       </c>
       <c r="E134" s="66">
         <v>71202897.00</v>
@@ -3817,12 +3817,12 @@
         <v>1</v>
       </c>
       <c r="G134" s="66">
-        <v>158054099.63</v>
+        <v>158085154.85</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B135">
         <is>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c t="n" r="D135">
-        <v>13.478351</v>
+        <v>13.482243</v>
       </c>
       <c r="E135" s="66">
         <v>7556929.00</v>
@@ -3844,12 +3844,12 @@
         <v>4</v>
       </c>
       <c r="G135" s="66">
-        <v>101854940.18</v>
+        <v>101884355.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B136">
         <is>
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c t="n" r="D136">
-        <v>94.062424</v>
+        <v>94.042646</v>
       </c>
       <c r="E136" s="66">
         <v>258190.00</v>
@@ -3871,12 +3871,12 @@
         <v>3</v>
       </c>
       <c r="G136" s="66">
-        <v>24285977.20</v>
+        <v>24280870.67</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B137">
         <is>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c t="n" r="D137">
-        <v>4.662221</v>
+        <v>4.662594</v>
       </c>
       <c r="E137" s="66">
         <v>91291013.00</v>
@@ -3898,12 +3898,12 @@
         <v>1</v>
       </c>
       <c r="G137" s="66">
-        <v>425618833.70</v>
+        <v>425652913.57</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B138">
         <is>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="139">
       <c r="A139" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B139">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c t="n" r="D139">
-        <v>18.239531</v>
+        <v>18.240571</v>
       </c>
       <c r="E139" s="66">
         <v>24020000.00</v>
@@ -3952,12 +3952,12 @@
         <v>2</v>
       </c>
       <c r="G139" s="66">
-        <v>438113534.56</v>
+        <v>438138509.63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B140">
         <is>
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c t="n" r="D140">
-        <v>27605.149960</v>
+        <v>27603.637347</v>
       </c>
       <c r="E140" s="66">
         <v>4534.00</v>
@@ -3979,12 +3979,12 @@
         <v>2</v>
       </c>
       <c r="G140" s="66">
-        <v>125161749.92</v>
+        <v>125154891.73</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B141">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c t="n" r="D141">
-        <v>4857.704413</v>
+        <v>4857.545455</v>
       </c>
       <c r="E141" s="66">
         <v>709751.00</v>
@@ -4006,12 +4006,12 @@
         <v>6</v>
       </c>
       <c r="G141" s="66">
-        <v>3447760564.72</v>
+        <v>3447647744.48</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B142">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c t="n" r="D142">
-        <v>0.191951</v>
+        <v>0.187751</v>
       </c>
       <c r="E142" s="66">
         <v>1000000.00</v>
@@ -4033,12 +4033,12 @@
         <v>1</v>
       </c>
       <c r="G142" s="66">
-        <v>191950.72</v>
+        <v>187750.51</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B143">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c t="n" r="D143">
-        <v>1.388473</v>
+        <v>1.388895</v>
       </c>
       <c r="E143" s="66">
         <v>108161193.00</v>
@@ -4060,12 +4060,12 @@
         <v>1</v>
       </c>
       <c r="G143" s="66">
-        <v>150178889.69</v>
+        <v>150224572.74</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B144">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c t="n" r="D144">
-        <v>15.920663</v>
+        <v>15.921113</v>
       </c>
       <c r="E144" s="66">
         <v>72648058.00</v>
@@ -4087,12 +4087,12 @@
         <v>26</v>
       </c>
       <c r="G144" s="66">
-        <v>1156605238.87</v>
+        <v>1156637973.35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B145">
         <is>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c t="n" r="D145">
-        <v>16.089645</v>
+        <v>16.089442</v>
       </c>
       <c r="E145" s="66">
         <v>357011459.00</v>
@@ -4114,12 +4114,12 @@
         <v>3</v>
       </c>
       <c r="G145" s="66">
-        <v>5744187469.74</v>
+        <v>5744115028.43</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B146">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c t="n" r="D146">
-        <v>3293.653612</v>
+        <v>3293.587476</v>
       </c>
       <c r="E146" s="66">
         <v>58813.00</v>
@@ -4141,12 +4141,12 @@
         <v>16</v>
       </c>
       <c r="G146" s="66">
-        <v>193709649.87</v>
+        <v>193705760.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B147">
         <is>
@@ -4168,12 +4168,12 @@
         <v>1</v>
       </c>
       <c r="G147" s="66">
-        <v>421460087.95</v>
+        <v>421460426.97</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B148">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c t="n" r="D148">
-        <v>1.324176</v>
+        <v>1.325692</v>
       </c>
       <c r="E148" s="66">
         <v>400397252.00</v>
@@ -4195,12 +4195,12 @@
         <v>1</v>
       </c>
       <c r="G148" s="66">
-        <v>530196485.28</v>
+        <v>530803451.94</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B149">
         <is>
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c t="n" r="D149">
-        <v>1.034921</v>
+        <v>1.034490</v>
       </c>
       <c r="E149" s="66">
         <v>13036720861.00</v>
@@ -4222,12 +4222,12 @@
         <v>1</v>
       </c>
       <c r="G149" s="66">
-        <v>13491981710.71</v>
+        <v>13486363234.15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B150">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c t="n" r="D150">
-        <v>0.920512</v>
+        <v>0.920013</v>
       </c>
       <c r="E150" s="66">
         <v>14795862971.00</v>
@@ -4249,12 +4249,12 @@
         <v>1</v>
       </c>
       <c r="G150" s="66">
-        <v>13619766257.08</v>
+        <v>13612384650.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B151">
         <is>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="152">
       <c r="A152" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B152">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c t="n" r="D152">
-        <v>1926.304169</v>
+        <v>1926.271886</v>
       </c>
       <c r="E152" s="66">
         <v>21287.75</v>
@@ -4303,12 +4303,12 @@
         <v>3</v>
       </c>
       <c r="G152" s="66">
-        <v>41006677.73</v>
+        <v>41005990.49</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B153">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c t="n" r="D153">
-        <v>1.584047</v>
+        <v>1.583311</v>
       </c>
       <c r="E153" s="66">
         <v>38469511.00</v>
@@ -4330,12 +4330,12 @@
         <v>6</v>
       </c>
       <c r="G153" s="66">
-        <v>60937500.99</v>
+        <v>60909196.11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B154">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c t="n" r="D154">
-        <v>6766.391577</v>
+        <v>6766.439636</v>
       </c>
       <c r="E154" s="66">
         <v>142550.00</v>
@@ -4357,12 +4357,12 @@
         <v>6</v>
       </c>
       <c r="G154" s="66">
-        <v>964549119.27</v>
+        <v>964555970.18</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B155">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c t="n" r="D155">
-        <v>1926.198485</v>
+        <v>1926.194593</v>
       </c>
       <c r="E155" s="66">
         <v>175337.00</v>
@@ -4384,12 +4384,12 @@
         <v>4</v>
       </c>
       <c r="G155" s="66">
-        <v>337733863.76</v>
+        <v>337733181.41</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B156">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c t="n" r="D156">
-        <v>17340.079395</v>
+        <v>17340.873473</v>
       </c>
       <c r="E156" s="66">
         <v>144465.00</v>
@@ -4411,12 +4411,12 @@
         <v>2</v>
       </c>
       <c r="G156" s="66">
-        <v>2505034569.81</v>
+        <v>2505149286.31</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B157">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c t="n" r="D157">
-        <v>20309.778187</v>
+        <v>20310.501745</v>
       </c>
       <c r="E157" s="66">
         <v>9114.00</v>
@@ -4438,12 +4438,12 @@
         <v>5</v>
       </c>
       <c r="G157" s="66">
-        <v>185103318.40</v>
+        <v>185109912.90</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B158">
         <is>
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c t="n" r="D158">
-        <v>15350.434916</v>
+        <v>15350.528134</v>
       </c>
       <c r="E158" s="66">
         <v>20870.00</v>
@@ -4465,12 +4465,12 @@
         <v>1</v>
       </c>
       <c r="G158" s="66">
-        <v>320363576.70</v>
+        <v>320365522.15</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B159">
         <is>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c t="n" r="D159">
-        <v>1163.238104</v>
+        <v>1164.573819</v>
       </c>
       <c r="E159" s="66">
         <v>5091.00</v>
@@ -4492,12 +4492,12 @@
         <v>1</v>
       </c>
       <c r="G159" s="66">
-        <v>5922045.19</v>
+        <v>5928845.31</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B160">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c t="n" r="D160">
-        <v>3675.755082</v>
+        <v>3675.828998</v>
       </c>
       <c r="E160" s="66">
         <v>195651.00</v>
@@ -4519,12 +4519,12 @@
         <v>1</v>
       </c>
       <c r="G160" s="66">
-        <v>719165157.53</v>
+        <v>719179619.32</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B161">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c t="n" r="D161">
-        <v>200850.455652</v>
+        <v>200850.229663</v>
       </c>
       <c r="E161" s="66">
         <v>22913.00</v>
@@ -4546,12 +4546,12 @@
         <v>115</v>
       </c>
       <c r="G161" s="66">
-        <v>4602086490.36</v>
+        <v>4602081312.26</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B162">
         <is>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c t="n" r="D162">
-        <v>33.532089</v>
+        <v>33.548981</v>
       </c>
       <c r="E162" s="66">
         <v>18098207.00</v>
@@ -4573,12 +4573,12 @@
         <v>27</v>
       </c>
       <c r="G162" s="66">
-        <v>606870683.24</v>
+        <v>607176404.42</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B163">
         <is>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c t="n" r="D163">
-        <v>80.485020</v>
+        <v>80.482339</v>
       </c>
       <c r="E163" s="66">
         <v>4925427.00</v>
@@ -4600,12 +4600,12 @@
         <v>5</v>
       </c>
       <c r="G163" s="66">
-        <v>396423092.51</v>
+        <v>396409887.50</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B164">
         <is>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c t="n" r="D164">
-        <v>1.400902</v>
+        <v>1.400956</v>
       </c>
       <c r="E164" s="66">
         <v>110231749.00</v>
@@ -4627,12 +4627,12 @@
         <v>3</v>
       </c>
       <c r="G164" s="66">
-        <v>154423870.38</v>
+        <v>154429788.01</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B165">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c t="n" r="D165">
-        <v>2579.690257</v>
+        <v>2579.712593</v>
       </c>
       <c r="E165" s="66">
         <v>170001.00</v>
@@ -4654,12 +4654,12 @@
         <v>1</v>
       </c>
       <c r="G165" s="66">
-        <v>438549923.43</v>
+        <v>438553720.54</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B166">
         <is>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c t="n" r="D166">
-        <v>1678.731304</v>
+        <v>1678.731306</v>
       </c>
       <c r="E166" s="66">
         <v>552258.00</v>
@@ -4681,12 +4681,12 @@
         <v>6</v>
       </c>
       <c r="G166" s="66">
-        <v>927092792.44</v>
+        <v>927092793.67</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B167">
         <is>
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c t="n" r="D167">
-        <v>1.027103</v>
+        <v>1.027069</v>
       </c>
       <c r="E167" s="66">
         <v>944992367.00</v>
@@ -4708,12 +4708,12 @@
         <v>2</v>
       </c>
       <c r="G167" s="66">
-        <v>970604714.32</v>
+        <v>970572197.72</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B168">
         <is>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c t="n" r="D168">
-        <v>1046.654739</v>
+        <v>1046.567290</v>
       </c>
       <c r="E168" s="66">
         <v>109317.00</v>
@@ -4735,12 +4735,12 @@
         <v>1</v>
       </c>
       <c r="G168" s="66">
-        <v>114417156.11</v>
+        <v>114407596.46</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B169">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c t="n" r="D169">
-        <v>75.922819</v>
+        <v>75.926587</v>
       </c>
       <c r="E169" s="66">
         <v>868659.00</v>
@@ -4762,12 +4762,12 @@
         <v>20</v>
       </c>
       <c r="G169" s="66">
-        <v>65951040.40</v>
+        <v>65954313.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B170">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c t="n" r="D170">
-        <v>3.188014</v>
+        <v>3.187956</v>
       </c>
       <c r="E170" s="66">
         <v>306482075.00</v>
@@ -4789,12 +4789,12 @@
         <v>1</v>
       </c>
       <c r="G170" s="66">
-        <v>977069119.47</v>
+        <v>977051375.56</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B171">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c t="n" r="D171">
-        <v>2980.355790</v>
+        <v>2980.338379</v>
       </c>
       <c r="E171" s="66">
         <v>698493.00</v>
@@ -4816,12 +4816,12 @@
         <v>4</v>
       </c>
       <c r="G171" s="66">
-        <v>2081757657.08</v>
+        <v>2081745495.47</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B172">
         <is>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c t="n" r="D172">
-        <v>4369.622158</v>
+        <v>4367.116813</v>
       </c>
       <c r="E172" s="66">
         <v>4440.00</v>
@@ -4843,12 +4843,12 @@
         <v>2</v>
       </c>
       <c r="G172" s="66">
-        <v>19401122.38</v>
+        <v>19389998.65</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B173">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c t="n" r="D173">
-        <v>63235.105294</v>
+        <v>63234.017071</v>
       </c>
       <c r="E173" s="66">
         <v>18709.00</v>
@@ -4870,12 +4870,12 @@
         <v>1</v>
       </c>
       <c r="G173" s="66">
-        <v>1183065584.94</v>
+        <v>1183045225.38</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B174">
         <is>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c t="n" r="D174">
-        <v>8193.100788</v>
+        <v>8192.953604</v>
       </c>
       <c r="E174" s="66">
         <v>18183.00</v>
@@ -4897,12 +4897,12 @@
         <v>1</v>
       </c>
       <c r="G174" s="66">
-        <v>148975151.63</v>
+        <v>148972475.39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B175">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c t="n" r="D175">
-        <v>46173.667364</v>
+        <v>46166.543456</v>
       </c>
       <c r="E175" s="66">
         <v>65463.00</v>
@@ -4924,12 +4924,12 @@
         <v>11</v>
       </c>
       <c r="G175" s="66">
-        <v>3022666786.62</v>
+        <v>3022200434.29</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B176">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c t="n" r="D176">
-        <v>11590.451031</v>
+        <v>11590.175352</v>
       </c>
       <c r="E176" s="66">
         <v>230830.00</v>
@@ -4951,12 +4951,12 @@
         <v>1</v>
       </c>
       <c r="G176" s="66">
-        <v>2675423811.49</v>
+        <v>2675360176.51</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B177">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c t="n" r="D177">
-        <v>2487.009457</v>
+        <v>2486.579456</v>
       </c>
       <c r="E177" s="66">
         <v>37355.00</v>
@@ -4978,12 +4978,12 @@
         <v>217</v>
       </c>
       <c r="G177" s="66">
-        <v>92902238.27</v>
+        <v>92886175.57</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B178">
         <is>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c t="n" r="D178">
-        <v>2705.598475</v>
+        <v>2705.289250</v>
       </c>
       <c r="E178" s="66">
         <v>169888.00</v>
@@ -5005,12 +5005,12 @@
         <v>3</v>
       </c>
       <c r="G178" s="66">
-        <v>459648713.77</v>
+        <v>459596180.17</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B179">
         <is>
@@ -5023,7 +5023,7 @@
         </is>
       </c>
       <c t="n" r="D179">
-        <v>3495.720332</v>
+        <v>3495.402230</v>
       </c>
       <c r="E179" s="66">
         <v>5937.00</v>
@@ -5032,12 +5032,12 @@
         <v>1</v>
       </c>
       <c r="G179" s="66">
-        <v>20754091.61</v>
+        <v>20752203.04</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B180">
         <is>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c t="n" r="D180">
-        <v>3296.258670</v>
+        <v>3296.189489</v>
       </c>
       <c r="E180" s="66">
         <v>2079318.00</v>
@@ -5059,12 +5059,12 @@
         <v>1118</v>
       </c>
       <c r="G180" s="66">
-        <v>6853969984.50</v>
+        <v>6853826135.75</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B181">
         <is>
@@ -5077,7 +5077,7 @@
         </is>
       </c>
       <c t="n" r="D181">
-        <v>0.994632</v>
+        <v>0.994575</v>
       </c>
       <c r="E181" s="66">
         <v>933394761.00</v>
@@ -5086,12 +5086,12 @@
         <v>3</v>
       </c>
       <c r="G181" s="66">
-        <v>928384580.83</v>
+        <v>928331049.55</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B182">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c t="n" r="D182">
-        <v>4660.849645</v>
+        <v>4660.760261</v>
       </c>
       <c r="E182" s="66">
         <v>15074.00</v>
@@ -5113,12 +5113,12 @@
         <v>2</v>
       </c>
       <c r="G182" s="66">
-        <v>70257647.55</v>
+        <v>70256300.17</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B183">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c t="n" r="D183">
-        <v>1.182444</v>
+        <v>1.182239</v>
       </c>
       <c r="E183" s="66">
         <v>2023351.00</v>
@@ -5140,12 +5140,12 @@
         <v>484</v>
       </c>
       <c r="G183" s="66">
-        <v>2392498.92</v>
+        <v>2392083.48</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B184">
         <is>
@@ -5158,7 +5158,7 @@
         </is>
       </c>
       <c t="n" r="D184">
-        <v>3592.702173</v>
+        <v>3592.697062</v>
       </c>
       <c r="E184" s="66">
         <v>255307.00</v>
@@ -5167,12 +5167,12 @@
         <v>8</v>
       </c>
       <c r="G184" s="66">
-        <v>917242013.56</v>
+        <v>917240708.82</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B185">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c t="n" r="D185">
-        <v>1.211376</v>
+        <v>1.211317</v>
       </c>
       <c r="E185" s="66">
         <v>187067481.00</v>
@@ -5194,12 +5194,12 @@
         <v>2</v>
       </c>
       <c r="G185" s="66">
-        <v>226608967.14</v>
+        <v>226598055.22</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B186">
         <is>
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c t="n" r="D186">
-        <v>1331.377030</v>
+        <v>1331.387089</v>
       </c>
       <c r="E186" s="66">
         <v>377509.00</v>
@@ -5221,12 +5221,12 @@
         <v>1</v>
       </c>
       <c r="G186" s="66">
-        <v>502606811.29</v>
+        <v>502610608.48</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B187">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c t="n" r="D187">
-        <v>1109.270776</v>
+        <v>1109.250749</v>
       </c>
       <c r="E187" s="66">
         <v>1551508.00</v>
@@ -5248,12 +5248,12 @@
         <v>1</v>
       </c>
       <c r="G187" s="66">
-        <v>1721042482.64</v>
+        <v>1721011411.20</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B188">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c t="n" r="D188">
-        <v>74.935836</v>
+        <v>74.934849</v>
       </c>
       <c r="E188" s="66">
         <v>11647998.00</v>
@@ -5275,12 +5275,12 @@
         <v>3</v>
       </c>
       <c r="G188" s="66">
-        <v>872852472.66</v>
+        <v>872840966.50</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B189">
         <is>
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c t="n" r="D189">
-        <v>10.208752</v>
+        <v>10.189481</v>
       </c>
       <c r="E189" s="66">
         <v>44310637.00</v>
@@ -5302,12 +5302,12 @@
         <v>40</v>
       </c>
       <c r="G189" s="66">
-        <v>452356305.34</v>
+        <v>451502411.82</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B190">
         <is>
@@ -5320,7 +5320,7 @@
         </is>
       </c>
       <c t="n" r="D190">
-        <v>14.205480</v>
+        <v>14.210713</v>
       </c>
       <c r="E190" s="66">
         <v>145515811.00</v>
@@ -5329,12 +5329,12 @@
         <v>3</v>
       </c>
       <c r="G190" s="66">
-        <v>2067121902.30</v>
+        <v>2067883397.53</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B191">
         <is>
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c t="n" r="D191">
-        <v>7543.731423</v>
+        <v>7518.397827</v>
       </c>
       <c r="E191" s="66">
         <v>37458.00</v>
@@ -5356,12 +5356,12 @@
         <v>19</v>
       </c>
       <c r="G191" s="66">
-        <v>282573091.63</v>
+        <v>281624145.81</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B192">
         <is>
@@ -5374,7 +5374,7 @@
         </is>
       </c>
       <c t="n" r="D192">
-        <v>1.915509</v>
+        <v>1.916145</v>
       </c>
       <c r="E192" s="66">
         <v>13687396.00</v>
@@ -5383,12 +5383,12 @@
         <v>4</v>
       </c>
       <c r="G192" s="66">
-        <v>26218326.13</v>
+        <v>26227035.91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B193">
         <is>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c t="n" r="D193">
-        <v>2.441727</v>
+        <v>2.441671</v>
       </c>
       <c r="E193" s="66">
         <v>84411053.00</v>
@@ -5410,12 +5410,12 @@
         <v>4</v>
       </c>
       <c r="G193" s="66">
-        <v>206108733.33</v>
+        <v>206103983.12</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B194">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c t="n" r="D194">
-        <v>44.329801</v>
+        <v>44.326117</v>
       </c>
       <c r="E194" s="66">
         <v>12733940.00</v>
@@ -5437,12 +5437,12 @@
         <v>5</v>
       </c>
       <c r="G194" s="66">
-        <v>564493031.05</v>
+        <v>564446117.32</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B195">
         <is>
@@ -5455,7 +5455,7 @@
         </is>
       </c>
       <c t="n" r="D195">
-        <v>14896.318948</v>
+        <v>14880.638864</v>
       </c>
       <c r="E195" s="66">
         <v>416820.00</v>
@@ -5464,12 +5464,12 @@
         <v>5</v>
       </c>
       <c r="G195" s="66">
-        <v>6209083663.98</v>
+        <v>6202547891.31</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B196">
         <is>
@@ -5482,7 +5482,7 @@
         </is>
       </c>
       <c t="n" r="D196">
-        <v>6276.763965</v>
+        <v>6277.146270</v>
       </c>
       <c r="E196" s="66">
         <v>6340.00</v>
@@ -5491,12 +5491,12 @@
         <v>1</v>
       </c>
       <c r="G196" s="66">
-        <v>39794683.54</v>
+        <v>39797107.35</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B197">
         <is>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="198">
       <c r="A198" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B198">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c t="n" r="D198">
-        <v>2933.441536</v>
+        <v>2933.435261</v>
       </c>
       <c r="E198" s="66">
         <v>367343.00</v>
@@ -5545,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="G198" s="66">
-        <v>1077579214.07</v>
+        <v>1077576909.15</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B199">
         <is>
@@ -5577,7 +5577,7 @@
     </row>
     <row r="200">
       <c r="A200" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B200">
         <is>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c t="n" r="D200">
-        <v>1.223880</v>
+        <v>1.223851</v>
       </c>
       <c r="E200" s="66">
         <v>427328964.00</v>
@@ -5599,12 +5599,12 @@
         <v>3</v>
       </c>
       <c r="G200" s="66">
-        <v>522999376.50</v>
+        <v>522986857.04</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B201">
         <is>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c t="n" r="D201">
-        <v>1.323587</v>
+        <v>1.323534</v>
       </c>
       <c r="E201" s="66">
         <v>92000000.00</v>
@@ -5626,12 +5626,12 @@
         <v>1</v>
       </c>
       <c r="G201" s="66">
-        <v>121770002.58</v>
+        <v>121765129.65</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B202">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c t="n" r="D202">
-        <v>7.379408</v>
+        <v>7.389111</v>
       </c>
       <c r="E202" s="66">
         <v>381640102.00</v>
@@ -5653,12 +5653,12 @@
         <v>2</v>
       </c>
       <c r="G202" s="66">
-        <v>2816278089.41</v>
+        <v>2819981038.55</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B203">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c t="n" r="D203">
-        <v>1002.561805</v>
+        <v>1002.492242</v>
       </c>
       <c r="E203" s="66">
         <v>448820.00</v>
@@ -5680,12 +5680,12 @@
         <v>2</v>
       </c>
       <c r="G203" s="66">
-        <v>449969789.18</v>
+        <v>449938568.11</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B204">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c t="n" r="D204">
-        <v>2524.570290</v>
+        <v>2528.392499</v>
       </c>
       <c r="E204" s="66">
         <v>205132.00</v>
@@ -5707,12 +5707,12 @@
         <v>4</v>
       </c>
       <c r="G204" s="66">
-        <v>517870152.75</v>
+        <v>518654210.19</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B205">
         <is>
@@ -5725,21 +5725,21 @@
         </is>
       </c>
       <c t="n" r="D205">
-        <v>1.005024</v>
+        <v>1.005269</v>
       </c>
       <c r="E205" s="66">
-        <v>364346841.00</v>
+        <v>385317664.00</v>
       </c>
       <c r="F205" s="65">
-        <v>304</v>
+        <v>416</v>
       </c>
       <c r="G205" s="66">
-        <v>366177200.80</v>
+        <v>387347733.74</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B206">
         <is>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c t="n" r="D206">
-        <v>0.004386</v>
+        <v>0.004384</v>
       </c>
       <c r="E206" s="66">
         <v>67618383967.00</v>
@@ -5761,12 +5761,12 @@
         <v>1</v>
       </c>
       <c r="G206" s="66">
-        <v>296566891.14</v>
+        <v>296425821.72</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B207">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c t="n" r="D207">
-        <v>20.819884</v>
+        <v>20.817989</v>
       </c>
       <c r="E207" s="66">
         <v>81092133.00</v>
@@ -5788,12 +5788,12 @@
         <v>1</v>
       </c>
       <c r="G207" s="66">
-        <v>1688328802.92</v>
+        <v>1688175151.16</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B208">
         <is>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c t="n" r="D208">
-        <v>3.358906</v>
+        <v>3.359028</v>
       </c>
       <c r="E208" s="66">
         <v>21323550.00</v>
@@ -5815,12 +5815,12 @@
         <v>2</v>
       </c>
       <c r="G208" s="66">
-        <v>71623793.28</v>
+        <v>71626404.58</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B209">
         <is>
@@ -5833,21 +5833,21 @@
         </is>
       </c>
       <c t="n" r="D209">
-        <v>7710.360421</v>
+        <v>7711.854832</v>
       </c>
       <c r="E209" s="66">
         <v>197052.47</v>
       </c>
       <c r="F209" s="65">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G209" s="66">
-        <v>1519345596.30</v>
+        <v>1519640073.81</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B210">
         <is>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c t="n" r="D210">
-        <v>1.844474</v>
+        <v>1.844339</v>
       </c>
       <c r="E210" s="66">
         <v>601179729.00</v>
@@ -5869,12 +5869,12 @@
         <v>16</v>
       </c>
       <c r="G210" s="66">
-        <v>1108860356.20</v>
+        <v>1108779422.87</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B211">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c t="n" r="D211">
-        <v>20.999602</v>
+        <v>21.102838</v>
       </c>
       <c r="E211" s="66">
         <v>377.00</v>
@@ -5896,12 +5896,12 @@
         <v>1</v>
       </c>
       <c r="G211" s="66">
-        <v>7916.85</v>
+        <v>7955.77</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B212">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c t="n" r="D212">
-        <v>1.758693</v>
+        <v>1.760661</v>
       </c>
       <c r="E212" s="66">
         <v>100000.00</v>
@@ -5923,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="G212" s="66">
-        <v>175869.32</v>
+        <v>176066.07</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B213">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c t="n" r="D213">
-        <v>1.758852</v>
+        <v>1.760819</v>
       </c>
       <c r="E213" s="66">
         <v>100000.00</v>
@@ -5950,12 +5950,12 @@
         <v>1</v>
       </c>
       <c r="G213" s="66">
-        <v>175885.15</v>
+        <v>176081.90</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B214">
         <is>
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c t="n" r="D214">
-        <v>61.290486</v>
+        <v>61.280723</v>
       </c>
       <c r="E214" s="66">
         <v>2554914.00</v>
@@ -5977,12 +5977,12 @@
         <v>9</v>
       </c>
       <c r="G214" s="66">
-        <v>156591921.92</v>
+        <v>156566976.90</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B215">
         <is>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c t="n" r="D215">
-        <v>15.256287</v>
+        <v>15.259102</v>
       </c>
       <c r="E215" s="66">
         <v>248000220.00</v>
@@ -6004,12 +6004,12 @@
         <v>2</v>
       </c>
       <c r="G215" s="66">
-        <v>3783562544.28</v>
+        <v>3784260739.96</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B216">
         <is>
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c t="n" r="D216">
-        <v>1.801199</v>
+        <v>1.800200</v>
       </c>
       <c r="E216" s="66">
         <v>504995473.00</v>
@@ -6031,12 +6031,12 @@
         <v>8</v>
       </c>
       <c r="G216" s="66">
-        <v>909597126.38</v>
+        <v>909093009.62</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B217">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c t="n" r="D217">
-        <v>0.391459</v>
+        <v>0.392320</v>
       </c>
       <c r="E217" s="66">
         <v>402507.00</v>
@@ -6058,12 +6058,12 @@
         <v>2</v>
       </c>
       <c r="G217" s="66">
-        <v>157564.87</v>
+        <v>157911.55</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B218">
         <is>
@@ -6076,7 +6076,7 @@
         </is>
       </c>
       <c t="n" r="D218">
-        <v>9.875620</v>
+        <v>9.874419</v>
       </c>
       <c r="E218" s="66">
         <v>27178800.00</v>
@@ -6085,12 +6085,12 @@
         <v>1</v>
       </c>
       <c r="G218" s="66">
-        <v>268407488.60</v>
+        <v>268374853.90</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B219">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c t="n" r="D219">
-        <v>15.610942</v>
+        <v>15.608920</v>
       </c>
       <c r="E219" s="66">
         <v>10371838.00</v>
@@ -6112,12 +6112,12 @@
         <v>34</v>
       </c>
       <c r="G219" s="66">
-        <v>161914160.79</v>
+        <v>161893192.58</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B220">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c t="n" r="D220">
-        <v>15.322398</v>
+        <v>15.320890</v>
       </c>
       <c r="E220" s="66">
         <v>19475841.00</v>
@@ -6139,12 +6139,12 @@
         <v>26</v>
       </c>
       <c r="G220" s="66">
-        <v>298416586.08</v>
+        <v>298387216.26</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B221">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c t="n" r="D221">
-        <v>31.147909</v>
+        <v>31.143642</v>
       </c>
       <c r="E221" s="66">
         <v>9712281.00</v>
@@ -6166,12 +6166,12 @@
         <v>13</v>
       </c>
       <c r="G221" s="66">
-        <v>302517245.25</v>
+        <v>302475803.67</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B222">
         <is>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c t="n" r="D222">
-        <v>8.069914</v>
+        <v>8.070343</v>
       </c>
       <c r="E222" s="66">
         <v>12818249.00</v>
@@ -6193,12 +6193,12 @@
         <v>23</v>
       </c>
       <c r="G222" s="66">
-        <v>103442173.27</v>
+        <v>103447665.05</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B223">
         <is>
@@ -6211,7 +6211,7 @@
         </is>
       </c>
       <c t="n" r="D223">
-        <v>1659.740067</v>
+        <v>1659.727935</v>
       </c>
       <c r="E223" s="66">
         <v>330000.00</v>
@@ -6220,12 +6220,12 @@
         <v>2</v>
       </c>
       <c r="G223" s="66">
-        <v>547714222.16</v>
+        <v>547710218.60</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B224">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c t="n" r="D224">
-        <v>5.170287</v>
+        <v>5.170162</v>
       </c>
       <c r="E224" s="66">
         <v>11867933.00</v>
@@ -6247,12 +6247,12 @@
         <v>3</v>
       </c>
       <c r="G224" s="66">
-        <v>61360617.91</v>
+        <v>61359130.55</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B225">
         <is>
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c t="n" r="D225">
-        <v>0.946770</v>
+        <v>0.946785</v>
       </c>
       <c r="E225" s="66">
         <v>130000000.00</v>
@@ -6274,12 +6274,12 @@
         <v>3</v>
       </c>
       <c r="G225" s="66">
-        <v>123080042.81</v>
+        <v>123082008.10</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B226">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c t="n" r="D226">
-        <v>5.515314</v>
+        <v>5.515293</v>
       </c>
       <c r="E226" s="66">
         <v>103852814.00</v>
@@ -6301,12 +6301,12 @@
         <v>29</v>
       </c>
       <c r="G226" s="66">
-        <v>572780859.78</v>
+        <v>572778689.61</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B227">
         <is>
@@ -6328,12 +6328,12 @@
         <v>2</v>
       </c>
       <c r="G227" s="66">
-        <v>6078.69</v>
+        <v>6078.67</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B228">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c t="n" r="D228">
-        <v>6.603103</v>
+        <v>6.602126</v>
       </c>
       <c r="E228" s="66">
         <v>11104667.00</v>
@@ -6355,12 +6355,12 @@
         <v>2</v>
       </c>
       <c r="G228" s="66">
-        <v>73325256.31</v>
+        <v>73314409.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B229">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c t="n" r="D229">
-        <v>26.500262</v>
+        <v>26.495427</v>
       </c>
       <c r="E229" s="66">
         <v>1038884.00</v>
@@ -6382,12 +6382,12 @@
         <v>2</v>
       </c>
       <c r="G229" s="66">
-        <v>27530698.37</v>
+        <v>27525674.87</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B230">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c t="n" r="D230">
-        <v>0.850244</v>
+        <v>0.850085</v>
       </c>
       <c r="E230" s="66">
         <v>73432275.00</v>
@@ -6409,12 +6409,12 @@
         <v>4</v>
       </c>
       <c r="G230" s="66">
-        <v>62435343.84</v>
+        <v>62423640.85</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B231">
         <is>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c t="n" r="D231">
-        <v>0.711682</v>
+        <v>0.717703</v>
       </c>
       <c r="E231" s="66">
         <v>801655137.00</v>
@@ -6436,12 +6436,12 @@
         <v>28</v>
       </c>
       <c r="G231" s="66">
-        <v>570523173.25</v>
+        <v>575350303.12</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B232">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c t="n" r="D232">
-        <v>12.020002</v>
+        <v>12.020084</v>
       </c>
       <c r="E232" s="66">
         <v>26235742.00</v>
@@ -6463,12 +6463,12 @@
         <v>5</v>
       </c>
       <c r="G232" s="66">
-        <v>315353668.90</v>
+        <v>315355826.06</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B233">
         <is>
@@ -6490,12 +6490,12 @@
         <v>1</v>
       </c>
       <c r="G233" s="66">
-        <v>471.49</v>
+        <v>471.47</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B234">
         <is>
@@ -6508,7 +6508,7 @@
         </is>
       </c>
       <c t="n" r="D234">
-        <v>1.562525</v>
+        <v>1.564077</v>
       </c>
       <c r="E234" s="66">
         <v>24022001.00</v>
@@ -6517,12 +6517,12 @@
         <v>2</v>
       </c>
       <c r="G234" s="66">
-        <v>37534983.34</v>
+        <v>37572261.28</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B235">
         <is>
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c t="n" r="D235">
-        <v>2.572308</v>
+        <v>2.572168</v>
       </c>
       <c r="E235" s="66">
         <v>68085562.00</v>
@@ -6544,12 +6544,12 @@
         <v>6</v>
       </c>
       <c r="G235" s="66">
-        <v>175137067.02</v>
+        <v>175127535.41</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B236">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c t="n" r="D236">
-        <v>1064.190903</v>
+        <v>1066.299853</v>
       </c>
       <c r="E236" s="66">
         <v>20029.00</v>
@@ -6571,12 +6571,12 @@
         <v>1</v>
       </c>
       <c r="G236" s="66">
-        <v>21314679.59</v>
+        <v>21356919.76</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B237">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c t="n" r="D237">
-        <v>3.248702</v>
+        <v>3.249147</v>
       </c>
       <c r="E237" s="66">
         <v>1427155857.00</v>
@@ -6598,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="G237" s="66">
-        <v>4636403886.41</v>
+        <v>4637038503.24</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B238">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c t="n" r="D238">
-        <v>1692.397256</v>
+        <v>1690.368479</v>
       </c>
       <c r="E238" s="66">
         <v>97333.00</v>
@@ -6625,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="G238" s="66">
-        <v>164726102.07</v>
+        <v>164528635.17</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B239">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c t="n" r="D239">
-        <v>1.161050</v>
+        <v>1.160985</v>
       </c>
       <c r="E239" s="66">
         <v>1107173943.00</v>
@@ -6652,12 +6652,12 @@
         <v>3</v>
       </c>
       <c r="G239" s="66">
-        <v>1285483796.10</v>
+        <v>1285412344.31</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B240">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c t="n" r="D240">
-        <v>2.199156</v>
+        <v>2.202585</v>
       </c>
       <c r="E240" s="66">
         <v>296754544.00</v>
@@ -6679,12 +6679,12 @@
         <v>3</v>
       </c>
       <c r="G240" s="66">
-        <v>652609477.23</v>
+        <v>653626997.26</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B241">
         <is>
@@ -6697,7 +6697,7 @@
         </is>
       </c>
       <c t="n" r="D241">
-        <v>1011.545292</v>
+        <v>1012.552322</v>
       </c>
       <c r="E241" s="66">
         <v>1431712.00</v>
@@ -6706,12 +6706,12 @@
         <v>260</v>
       </c>
       <c r="G241" s="66">
-        <v>1448241533.47</v>
+        <v>1449683310.40</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B242">
         <is>
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c t="n" r="D242">
-        <v>5.004343</v>
+        <v>5.004185</v>
       </c>
       <c r="E242" s="66">
         <v>395532870.00</v>
@@ -6733,12 +6733,12 @@
         <v>5</v>
       </c>
       <c r="G242" s="66">
-        <v>1979382134.39</v>
+        <v>1979319742.62</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B243">
         <is>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c t="n" r="D243">
-        <v>1303.777917</v>
+        <v>1303.756752</v>
       </c>
       <c r="E243" s="66">
         <v>1467447.00</v>
@@ -6760,12 +6760,12 @@
         <v>1</v>
       </c>
       <c r="G243" s="66">
-        <v>1913224993.32</v>
+        <v>1913193935.13</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="67">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c t="inlineStr" r="B244">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c t="n" r="D244">
-        <v>26970.035277</v>
+        <v>26971.129499</v>
       </c>
       <c r="E244" s="66">
         <v>40026.00</v>
@@ -6787,7 +6787,7 @@
         <v>1</v>
       </c>
       <c r="G244" s="66">
-        <v>1079502631.98</v>
+        <v>1079546429.34</v>
       </c>
     </row>
   </sheetData>
